--- a/raw_data/authoritative_workbook_R2.xlsx
+++ b/raw_data/authoritative_workbook_R2.xlsx
@@ -7106,7 +7106,7 @@
       </c>
       <c r="U35" s="42" t="n">
         <f aca="false">J35*Assumptions!$B$59*1000/8760/'Load profile'!AO75</f>
-        <v>47.7278157428338</v>
+        <v>47.7278157428337</v>
       </c>
       <c r="V35" s="42" t="n">
         <f aca="false">(D35+E35)*Assumptions!$B$64*Assumptions!$B$65*Assumptions!$B$66/1000000</f>
@@ -24907,147 +24907,147 @@
         <v>234</v>
       </c>
       <c r="J50" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$5:$F$5,TRANSPOSE(J$45:J$49))</f>
-        <v>0.0746724171146181</v>
+        <f aca="false">$B5*J$45+$C5*J$46+$D5*J$47+$E5*J$48+$F5*J$49</f>
+        <v>0.074672417114618</v>
       </c>
       <c r="K50" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$5:$F$5,TRANSPOSE(K$45:K$49))</f>
+        <f aca="false">$B5*K$45+$C5*K$46+$D5*K$47+$E5*K$48+$F5*K$49</f>
         <v>0.0738504073539834</v>
       </c>
       <c r="L50" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$5:$F$5,TRANSPOSE(L$45:L$49))</f>
+        <f aca="false">$B5*L$45+$C5*L$46+$D5*L$47+$E5*L$48+$F5*L$49</f>
         <v>0.0730283474493624</v>
       </c>
       <c r="M50" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$5:$F$5,TRANSPOSE(M$45:M$49))</f>
+        <f aca="false">$B5*M$45+$C5*M$46+$D5*M$47+$E5*M$48+$F5*M$49</f>
         <v>0.0722076889095901</v>
       </c>
       <c r="N50" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$5:$F$5,TRANSPOSE(N$45:N$49))</f>
+        <f aca="false">$B5*N$45+$C5*N$46+$D5*N$47+$E5*N$48+$F5*N$49</f>
         <v>0.0713900422567302</v>
       </c>
       <c r="O50" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$5:$F$5,TRANSPOSE(O$45:O$49))</f>
+        <f aca="false">$B5*O$45+$C5*O$46+$D5*O$47+$E5*O$48+$F5*O$49</f>
         <v>0.070577217435329</v>
       </c>
       <c r="P50" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$5:$F$5,TRANSPOSE(P$45:P$49))</f>
+        <f aca="false">$B5*P$45+$C5*P$46+$D5*P$47+$E5*P$48+$F5*P$49</f>
         <v>0.069771275719457</v>
       </c>
       <c r="Q50" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$5:$F$5,TRANSPOSE(Q$45:Q$49))</f>
+        <f aca="false">$B5*Q$45+$C5*Q$46+$D5*Q$47+$E5*Q$48+$F5*Q$49</f>
         <v>0.0689745952097068</v>
       </c>
       <c r="R50" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$5:$F$5,TRANSPOSE(R$45:R$49))</f>
+        <f aca="false">$B5*R$45+$C5*R$46+$D5*R$47+$E5*R$48+$F5*R$49</f>
         <v>0.0681899518382093</v>
       </c>
       <c r="S50" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$5:$F$5,TRANSPOSE(S$45:S$49))</f>
+        <f aca="false">$B5*S$45+$C5*S$46+$D5*S$47+$E5*S$48+$F5*S$49</f>
         <v>0.0674206171774841</v>
       </c>
       <c r="T50" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$5:$F$5,TRANSPOSE(T$45:T$49))</f>
+        <f aca="false">$B5*T$45+$C5*T$46+$D5*T$47+$E5*T$48+$F5*T$49</f>
         <v>0.0666704729800515</v>
       </c>
       <c r="U50" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$5:$F$5,TRANSPOSE(U$45:U$49))</f>
+        <f aca="false">$B5*U$45+$C5*U$46+$D5*U$47+$E5*U$48+$F5*U$49</f>
         <v>0.0659441398464553</v>
       </c>
       <c r="V50" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$5:$F$5,TRANSPOSE(V$45:V$49))</f>
+        <f aca="false">$B5*V$45+$C5*V$46+$D5*V$47+$E5*V$48+$F5*V$49</f>
         <v>0.0652471132181326</v>
       </c>
       <c r="W50" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$5:$F$5,TRANSPOSE(W$45:W$49))</f>
+        <f aca="false">$B5*W$45+$C5*W$46+$D5*W$47+$E5*W$48+$F5*W$49</f>
         <v>0.0645858935090579</v>
       </c>
       <c r="X50" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$5:$F$5,TRANSPOSE(X$45:X$49))</f>
+        <f aca="false">$B5*X$45+$C5*X$46+$D5*X$47+$E5*X$48+$F5*X$49</f>
         <v>0.0639680883760655</v>
       </c>
       <c r="Y50" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$5:$F$5,TRANSPOSE(Y$45:Y$49))</f>
-        <v>0.0634024543793252</v>
+        <f aca="false">$B5*Y$45+$C5*Y$46+$D5*Y$47+$E5*Y$48+$F5*Y$49</f>
+        <v>0.0634024543793253</v>
       </c>
       <c r="Z50" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$5:$F$5,TRANSPOSE(Z$45:Z$49))</f>
+        <f aca="false">$B5*Z$45+$C5*Z$46+$D5*Z$47+$E5*Z$48+$F5*Z$49</f>
         <v>0.0628988345471524</v>
       </c>
       <c r="AA50" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$5:$F$5,TRANSPOSE(AA$45:AA$49))</f>
+        <f aca="false">$B5*AA$45+$C5*AA$46+$D5*AA$47+$E5*AA$48+$F5*AA$49</f>
         <v>0.0624679416484595</v>
       </c>
       <c r="AB50" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$5:$F$5,TRANSPOSE(AB$45:AB$49))</f>
+        <f aca="false">$B5*AB$45+$C5*AB$46+$D5*AB$47+$E5*AB$48+$F5*AB$49</f>
         <v>0.0621209401826656</v>
       </c>
       <c r="AC50" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$5:$F$5,TRANSPOSE(AC$45:AC$49))</f>
+        <f aca="false">$B5*AC$45+$C5*AC$46+$D5*AC$47+$E5*AC$48+$F5*AC$49</f>
         <v>0.0618687990202628</v>
       </c>
       <c r="AD50" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$5:$F$5,TRANSPOSE(AD$45:AD$49))</f>
+        <f aca="false">$B5*AD$45+$C5*AD$46+$D5*AD$47+$E5*AD$48+$F5*AD$49</f>
         <v>0.0617214231521614</v>
       </c>
       <c r="AE50" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$5:$F$5,TRANSPOSE(AE$45:AE$49))</f>
+        <f aca="false">$B5*AE$45+$C5*AE$46+$D5*AE$47+$E5*AE$48+$F5*AE$49</f>
         <v>0.0616866217378462</v>
       </c>
       <c r="AF50" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$5:$F$5,TRANSPOSE(AF$45:AF$49))</f>
+        <f aca="false">$B5*AF$45+$C5*AF$46+$D5*AF$47+$E5*AF$48+$F5*AF$49</f>
         <v>0.0617690191061722</v>
       </c>
       <c r="AG50" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$5:$F$5,TRANSPOSE(AG$45:AG$49))</f>
+        <f aca="false">$B5*AG$45+$C5*AG$46+$D5*AG$47+$E5*AG$48+$F5*AG$49</f>
         <v>0.0619690545798268</v>
       </c>
       <c r="AH50" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$5:$F$5,TRANSPOSE(AH$45:AH$49))</f>
+        <f aca="false">$B5*AH$45+$C5*AH$46+$D5*AH$47+$E5*AH$48+$F5*AH$49</f>
         <v>0.0622822403500403</v>
       </c>
       <c r="AI50" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$5:$F$5,TRANSPOSE(AI$45:AI$49))</f>
+        <f aca="false">$B5*AI$45+$C5*AI$46+$D5*AI$47+$E5*AI$48+$F5*AI$49</f>
         <v>0.0626988489619953</v>
       </c>
       <c r="AJ50" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$5:$F$5,TRANSPOSE(AJ$45:AJ$49))</f>
+        <f aca="false">$B5*AJ$45+$C5*AJ$46+$D5*AJ$47+$E5*AJ$48+$F5*AJ$49</f>
         <v>0.0632041699504232</v>
       </c>
       <c r="AK50" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$5:$F$5,TRANSPOSE(AK$45:AK$49))</f>
+        <f aca="false">$B5*AK$45+$C5*AK$46+$D5*AK$47+$E5*AK$48+$F5*AK$49</f>
         <v>0.0637793926659979</v>
       </c>
       <c r="AL50" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$5:$F$5,TRANSPOSE(AL$45:AL$49))</f>
+        <f aca="false">$B5*AL$45+$C5*AL$46+$D5*AL$47+$E5*AL$48+$F5*AL$49</f>
         <v>0.0644030426356731</v>
       </c>
       <c r="AM50" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$5:$F$5,TRANSPOSE(AM$45:AM$49))</f>
+        <f aca="false">$B5*AM$45+$C5*AM$46+$D5*AM$47+$E5*AM$48+$F5*AM$49</f>
         <v>0.0650527596648829</v>
       </c>
       <c r="AN50" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$5:$F$5,TRANSPOSE(AN$45:AN$49))</f>
+        <f aca="false">$B5*AN$45+$C5*AN$46+$D5*AN$47+$E5*AN$48+$F5*AN$49</f>
         <v>0.0657071148168149</v>
       </c>
       <c r="AO50" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$5:$F$5,TRANSPOSE(AO$45:AO$49))</f>
+        <f aca="false">$B5*AO$45+$C5*AO$46+$D5*AO$47+$E5*AO$48+$F5*AO$49</f>
         <v>0.066347161693678</v>
       </c>
       <c r="AP50" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$5:$F$5,TRANSPOSE(AP$45:AP$49))</f>
+        <f aca="false">$B5*AP$45+$C5*AP$46+$D5*AP$47+$E5*AP$48+$F5*AP$49</f>
         <v>0.0669575038817295</v>
       </c>
       <c r="AQ50" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$5:$F$5,TRANSPOSE(AQ$45:AQ$49))</f>
+        <f aca="false">$B5*AQ$45+$C5*AQ$46+$D5*AQ$47+$E5*AQ$48+$F5*AQ$49</f>
         <v>0.0675267947190303</v>
       </c>
       <c r="AR50" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$5:$F$5,TRANSPOSE(AR$45:AR$49))</f>
+        <f aca="false">$B5*AR$45+$C5*AR$46+$D5*AR$47+$E5*AR$48+$F5*AR$49</f>
         <v>0.0680477147256546</v>
       </c>
       <c r="AS50" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$5:$F$5,TRANSPOSE(AS$45:AS$49))</f>
+        <f aca="false">$B5*AS$45+$C5*AS$46+$D5*AS$47+$E5*AS$48+$F5*AS$49</f>
         <v>0.0685165578021</v>
       </c>
     </row>
@@ -25056,147 +25056,147 @@
         <v>235</v>
       </c>
       <c r="J51" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$6:$F$6,TRANSPOSE(J$45:J$49))</f>
-        <v>0.0746724171146181</v>
+        <f aca="false">$B6*J$45+$C6*J$46+$D6*J$47+$E6*J$48+$F6*J$49</f>
+        <v>0.074672417114618</v>
       </c>
       <c r="K51" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$6:$F$6,TRANSPOSE(K$45:K$49))</f>
+        <f aca="false">$B6*K$45+$C6*K$46+$D6*K$47+$E6*K$48+$F6*K$49</f>
         <v>0.0738504073539834</v>
       </c>
       <c r="L51" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$6:$F$6,TRANSPOSE(L$45:L$49))</f>
+        <f aca="false">$B6*L$45+$C6*L$46+$D6*L$47+$E6*L$48+$F6*L$49</f>
         <v>0.0730283474493624</v>
       </c>
       <c r="M51" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$6:$F$6,TRANSPOSE(M$45:M$49))</f>
+        <f aca="false">$B6*M$45+$C6*M$46+$D6*M$47+$E6*M$48+$F6*M$49</f>
         <v>0.0722076889095901</v>
       </c>
       <c r="N51" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$6:$F$6,TRANSPOSE(N$45:N$49))</f>
+        <f aca="false">$B6*N$45+$C6*N$46+$D6*N$47+$E6*N$48+$F6*N$49</f>
         <v>0.0713900422567302</v>
       </c>
       <c r="O51" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$6:$F$6,TRANSPOSE(O$45:O$49))</f>
+        <f aca="false">$B6*O$45+$C6*O$46+$D6*O$47+$E6*O$48+$F6*O$49</f>
         <v>0.070577217435329</v>
       </c>
       <c r="P51" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$6:$F$6,TRANSPOSE(P$45:P$49))</f>
+        <f aca="false">$B6*P$45+$C6*P$46+$D6*P$47+$E6*P$48+$F6*P$49</f>
         <v>0.069771275719457</v>
       </c>
       <c r="Q51" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$6:$F$6,TRANSPOSE(Q$45:Q$49))</f>
+        <f aca="false">$B6*Q$45+$C6*Q$46+$D6*Q$47+$E6*Q$48+$F6*Q$49</f>
         <v>0.0689745952097068</v>
       </c>
       <c r="R51" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$6:$F$6,TRANSPOSE(R$45:R$49))</f>
+        <f aca="false">$B6*R$45+$C6*R$46+$D6*R$47+$E6*R$48+$F6*R$49</f>
         <v>0.0681899518382093</v>
       </c>
       <c r="S51" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$6:$F$6,TRANSPOSE(S$45:S$49))</f>
+        <f aca="false">$B6*S$45+$C6*S$46+$D6*S$47+$E6*S$48+$F6*S$49</f>
         <v>0.0674206171774841</v>
       </c>
       <c r="T51" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$6:$F$6,TRANSPOSE(T$45:T$49))</f>
+        <f aca="false">$B6*T$45+$C6*T$46+$D6*T$47+$E6*T$48+$F6*T$49</f>
         <v>0.0666704729800515</v>
       </c>
       <c r="U51" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$6:$F$6,TRANSPOSE(U$45:U$49))</f>
+        <f aca="false">$B6*U$45+$C6*U$46+$D6*U$47+$E6*U$48+$F6*U$49</f>
         <v>0.0659441398464553</v>
       </c>
       <c r="V51" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$6:$F$6,TRANSPOSE(V$45:V$49))</f>
+        <f aca="false">$B6*V$45+$C6*V$46+$D6*V$47+$E6*V$48+$F6*V$49</f>
         <v>0.0652471132181326</v>
       </c>
       <c r="W51" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$6:$F$6,TRANSPOSE(W$45:W$49))</f>
+        <f aca="false">$B6*W$45+$C6*W$46+$D6*W$47+$E6*W$48+$F6*W$49</f>
         <v>0.0645858935090579</v>
       </c>
       <c r="X51" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$6:$F$6,TRANSPOSE(X$45:X$49))</f>
+        <f aca="false">$B6*X$45+$C6*X$46+$D6*X$47+$E6*X$48+$F6*X$49</f>
         <v>0.0639680883760655</v>
       </c>
       <c r="Y51" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$6:$F$6,TRANSPOSE(Y$45:Y$49))</f>
-        <v>0.0634024543793252</v>
+        <f aca="false">$B6*Y$45+$C6*Y$46+$D6*Y$47+$E6*Y$48+$F6*Y$49</f>
+        <v>0.0634024543793253</v>
       </c>
       <c r="Z51" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$6:$F$6,TRANSPOSE(Z$45:Z$49))</f>
+        <f aca="false">$B6*Z$45+$C6*Z$46+$D6*Z$47+$E6*Z$48+$F6*Z$49</f>
         <v>0.0628988345471524</v>
       </c>
       <c r="AA51" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$6:$F$6,TRANSPOSE(AA$45:AA$49))</f>
+        <f aca="false">$B6*AA$45+$C6*AA$46+$D6*AA$47+$E6*AA$48+$F6*AA$49</f>
         <v>0.0624679416484595</v>
       </c>
       <c r="AB51" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$6:$F$6,TRANSPOSE(AB$45:AB$49))</f>
+        <f aca="false">$B6*AB$45+$C6*AB$46+$D6*AB$47+$E6*AB$48+$F6*AB$49</f>
         <v>0.0621209401826656</v>
       </c>
       <c r="AC51" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$6:$F$6,TRANSPOSE(AC$45:AC$49))</f>
+        <f aca="false">$B6*AC$45+$C6*AC$46+$D6*AC$47+$E6*AC$48+$F6*AC$49</f>
         <v>0.0618687990202628</v>
       </c>
       <c r="AD51" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$6:$F$6,TRANSPOSE(AD$45:AD$49))</f>
+        <f aca="false">$B6*AD$45+$C6*AD$46+$D6*AD$47+$E6*AD$48+$F6*AD$49</f>
         <v>0.0617214231521614</v>
       </c>
       <c r="AE51" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$6:$F$6,TRANSPOSE(AE$45:AE$49))</f>
+        <f aca="false">$B6*AE$45+$C6*AE$46+$D6*AE$47+$E6*AE$48+$F6*AE$49</f>
         <v>0.0616866217378462</v>
       </c>
       <c r="AF51" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$6:$F$6,TRANSPOSE(AF$45:AF$49))</f>
+        <f aca="false">$B6*AF$45+$C6*AF$46+$D6*AF$47+$E6*AF$48+$F6*AF$49</f>
         <v>0.0617690191061722</v>
       </c>
       <c r="AG51" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$6:$F$6,TRANSPOSE(AG$45:AG$49))</f>
+        <f aca="false">$B6*AG$45+$C6*AG$46+$D6*AG$47+$E6*AG$48+$F6*AG$49</f>
         <v>0.0619690545798268</v>
       </c>
       <c r="AH51" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$6:$F$6,TRANSPOSE(AH$45:AH$49))</f>
+        <f aca="false">$B6*AH$45+$C6*AH$46+$D6*AH$47+$E6*AH$48+$F6*AH$49</f>
         <v>0.0622822403500403</v>
       </c>
       <c r="AI51" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$6:$F$6,TRANSPOSE(AI$45:AI$49))</f>
+        <f aca="false">$B6*AI$45+$C6*AI$46+$D6*AI$47+$E6*AI$48+$F6*AI$49</f>
         <v>0.0626988489619953</v>
       </c>
       <c r="AJ51" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$6:$F$6,TRANSPOSE(AJ$45:AJ$49))</f>
+        <f aca="false">$B6*AJ$45+$C6*AJ$46+$D6*AJ$47+$E6*AJ$48+$F6*AJ$49</f>
         <v>0.0632041699504232</v>
       </c>
       <c r="AK51" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$6:$F$6,TRANSPOSE(AK$45:AK$49))</f>
+        <f aca="false">$B6*AK$45+$C6*AK$46+$D6*AK$47+$E6*AK$48+$F6*AK$49</f>
         <v>0.0637793926659979</v>
       </c>
       <c r="AL51" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$6:$F$6,TRANSPOSE(AL$45:AL$49))</f>
+        <f aca="false">$B6*AL$45+$C6*AL$46+$D6*AL$47+$E6*AL$48+$F6*AL$49</f>
         <v>0.0644030426356731</v>
       </c>
       <c r="AM51" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$6:$F$6,TRANSPOSE(AM$45:AM$49))</f>
+        <f aca="false">$B6*AM$45+$C6*AM$46+$D6*AM$47+$E6*AM$48+$F6*AM$49</f>
         <v>0.0650527596648829</v>
       </c>
       <c r="AN51" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$6:$F$6,TRANSPOSE(AN$45:AN$49))</f>
+        <f aca="false">$B6*AN$45+$C6*AN$46+$D6*AN$47+$E6*AN$48+$F6*AN$49</f>
         <v>0.0657071148168149</v>
       </c>
       <c r="AO51" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$6:$F$6,TRANSPOSE(AO$45:AO$49))</f>
+        <f aca="false">$B6*AO$45+$C6*AO$46+$D6*AO$47+$E6*AO$48+$F6*AO$49</f>
         <v>0.066347161693678</v>
       </c>
       <c r="AP51" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$6:$F$6,TRANSPOSE(AP$45:AP$49))</f>
+        <f aca="false">$B6*AP$45+$C6*AP$46+$D6*AP$47+$E6*AP$48+$F6*AP$49</f>
         <v>0.0669575038817295</v>
       </c>
       <c r="AQ51" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$6:$F$6,TRANSPOSE(AQ$45:AQ$49))</f>
+        <f aca="false">$B6*AQ$45+$C6*AQ$46+$D6*AQ$47+$E6*AQ$48+$F6*AQ$49</f>
         <v>0.0675267947190303</v>
       </c>
       <c r="AR51" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$6:$F$6,TRANSPOSE(AR$45:AR$49))</f>
+        <f aca="false">$B6*AR$45+$C6*AR$46+$D6*AR$47+$E6*AR$48+$F6*AR$49</f>
         <v>0.0680477147256546</v>
       </c>
       <c r="AS51" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$6:$F$6,TRANSPOSE(AS$45:AS$49))</f>
+        <f aca="false">$B6*AS$45+$C6*AS$46+$D6*AS$47+$E6*AS$48+$F6*AS$49</f>
         <v>0.0685165578021</v>
       </c>
     </row>
@@ -25205,147 +25205,147 @@
         <v>236</v>
       </c>
       <c r="J52" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$7:$F$7,TRANSPOSE(J$45:J$49))</f>
-        <v>0.0746724171146181</v>
+        <f aca="false">$B7*J$45+$C7*J$46+$D7*J$47+$E7*J$48+$F7*J$49</f>
+        <v>0.074672417114618</v>
       </c>
       <c r="K52" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$7:$F$7,TRANSPOSE(K$45:K$49))</f>
+        <f aca="false">$B7*K$45+$C7*K$46+$D7*K$47+$E7*K$48+$F7*K$49</f>
         <v>0.0738504073539834</v>
       </c>
       <c r="L52" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$7:$F$7,TRANSPOSE(L$45:L$49))</f>
+        <f aca="false">$B7*L$45+$C7*L$46+$D7*L$47+$E7*L$48+$F7*L$49</f>
         <v>0.0730283474493624</v>
       </c>
       <c r="M52" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$7:$F$7,TRANSPOSE(M$45:M$49))</f>
+        <f aca="false">$B7*M$45+$C7*M$46+$D7*M$47+$E7*M$48+$F7*M$49</f>
         <v>0.0722076889095901</v>
       </c>
       <c r="N52" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$7:$F$7,TRANSPOSE(N$45:N$49))</f>
+        <f aca="false">$B7*N$45+$C7*N$46+$D7*N$47+$E7*N$48+$F7*N$49</f>
         <v>0.0713900422567302</v>
       </c>
       <c r="O52" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$7:$F$7,TRANSPOSE(O$45:O$49))</f>
+        <f aca="false">$B7*O$45+$C7*O$46+$D7*O$47+$E7*O$48+$F7*O$49</f>
         <v>0.070577217435329</v>
       </c>
       <c r="P52" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$7:$F$7,TRANSPOSE(P$45:P$49))</f>
+        <f aca="false">$B7*P$45+$C7*P$46+$D7*P$47+$E7*P$48+$F7*P$49</f>
         <v>0.069771275719457</v>
       </c>
       <c r="Q52" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$7:$F$7,TRANSPOSE(Q$45:Q$49))</f>
+        <f aca="false">$B7*Q$45+$C7*Q$46+$D7*Q$47+$E7*Q$48+$F7*Q$49</f>
         <v>0.0689745952097068</v>
       </c>
       <c r="R52" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$7:$F$7,TRANSPOSE(R$45:R$49))</f>
+        <f aca="false">$B7*R$45+$C7*R$46+$D7*R$47+$E7*R$48+$F7*R$49</f>
         <v>0.0681899518382093</v>
       </c>
       <c r="S52" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$7:$F$7,TRANSPOSE(S$45:S$49))</f>
+        <f aca="false">$B7*S$45+$C7*S$46+$D7*S$47+$E7*S$48+$F7*S$49</f>
         <v>0.0674206171774841</v>
       </c>
       <c r="T52" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$7:$F$7,TRANSPOSE(T$45:T$49))</f>
+        <f aca="false">$B7*T$45+$C7*T$46+$D7*T$47+$E7*T$48+$F7*T$49</f>
         <v>0.0666704729800515</v>
       </c>
       <c r="U52" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$7:$F$7,TRANSPOSE(U$45:U$49))</f>
+        <f aca="false">$B7*U$45+$C7*U$46+$D7*U$47+$E7*U$48+$F7*U$49</f>
         <v>0.0659441398464553</v>
       </c>
       <c r="V52" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$7:$F$7,TRANSPOSE(V$45:V$49))</f>
+        <f aca="false">$B7*V$45+$C7*V$46+$D7*V$47+$E7*V$48+$F7*V$49</f>
         <v>0.0652471132181326</v>
       </c>
       <c r="W52" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$7:$F$7,TRANSPOSE(W$45:W$49))</f>
+        <f aca="false">$B7*W$45+$C7*W$46+$D7*W$47+$E7*W$48+$F7*W$49</f>
         <v>0.0645858935090579</v>
       </c>
       <c r="X52" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$7:$F$7,TRANSPOSE(X$45:X$49))</f>
+        <f aca="false">$B7*X$45+$C7*X$46+$D7*X$47+$E7*X$48+$F7*X$49</f>
         <v>0.0639680883760655</v>
       </c>
       <c r="Y52" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$7:$F$7,TRANSPOSE(Y$45:Y$49))</f>
-        <v>0.0634024543793252</v>
+        <f aca="false">$B7*Y$45+$C7*Y$46+$D7*Y$47+$E7*Y$48+$F7*Y$49</f>
+        <v>0.0634024543793253</v>
       </c>
       <c r="Z52" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$7:$F$7,TRANSPOSE(Z$45:Z$49))</f>
+        <f aca="false">$B7*Z$45+$C7*Z$46+$D7*Z$47+$E7*Z$48+$F7*Z$49</f>
         <v>0.0628988345471524</v>
       </c>
       <c r="AA52" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$7:$F$7,TRANSPOSE(AA$45:AA$49))</f>
+        <f aca="false">$B7*AA$45+$C7*AA$46+$D7*AA$47+$E7*AA$48+$F7*AA$49</f>
         <v>0.0624679416484595</v>
       </c>
       <c r="AB52" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$7:$F$7,TRANSPOSE(AB$45:AB$49))</f>
+        <f aca="false">$B7*AB$45+$C7*AB$46+$D7*AB$47+$E7*AB$48+$F7*AB$49</f>
         <v>0.0621209401826656</v>
       </c>
       <c r="AC52" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$7:$F$7,TRANSPOSE(AC$45:AC$49))</f>
+        <f aca="false">$B7*AC$45+$C7*AC$46+$D7*AC$47+$E7*AC$48+$F7*AC$49</f>
         <v>0.0618687990202628</v>
       </c>
       <c r="AD52" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$7:$F$7,TRANSPOSE(AD$45:AD$49))</f>
+        <f aca="false">$B7*AD$45+$C7*AD$46+$D7*AD$47+$E7*AD$48+$F7*AD$49</f>
         <v>0.0617214231521614</v>
       </c>
       <c r="AE52" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$7:$F$7,TRANSPOSE(AE$45:AE$49))</f>
+        <f aca="false">$B7*AE$45+$C7*AE$46+$D7*AE$47+$E7*AE$48+$F7*AE$49</f>
         <v>0.0616866217378462</v>
       </c>
       <c r="AF52" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$7:$F$7,TRANSPOSE(AF$45:AF$49))</f>
+        <f aca="false">$B7*AF$45+$C7*AF$46+$D7*AF$47+$E7*AF$48+$F7*AF$49</f>
         <v>0.0617690191061722</v>
       </c>
       <c r="AG52" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$7:$F$7,TRANSPOSE(AG$45:AG$49))</f>
+        <f aca="false">$B7*AG$45+$C7*AG$46+$D7*AG$47+$E7*AG$48+$F7*AG$49</f>
         <v>0.0619690545798268</v>
       </c>
       <c r="AH52" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$7:$F$7,TRANSPOSE(AH$45:AH$49))</f>
+        <f aca="false">$B7*AH$45+$C7*AH$46+$D7*AH$47+$E7*AH$48+$F7*AH$49</f>
         <v>0.0622822403500403</v>
       </c>
       <c r="AI52" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$7:$F$7,TRANSPOSE(AI$45:AI$49))</f>
+        <f aca="false">$B7*AI$45+$C7*AI$46+$D7*AI$47+$E7*AI$48+$F7*AI$49</f>
         <v>0.0626988489619953</v>
       </c>
       <c r="AJ52" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$7:$F$7,TRANSPOSE(AJ$45:AJ$49))</f>
+        <f aca="false">$B7*AJ$45+$C7*AJ$46+$D7*AJ$47+$E7*AJ$48+$F7*AJ$49</f>
         <v>0.0632041699504232</v>
       </c>
       <c r="AK52" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$7:$F$7,TRANSPOSE(AK$45:AK$49))</f>
+        <f aca="false">$B7*AK$45+$C7*AK$46+$D7*AK$47+$E7*AK$48+$F7*AK$49</f>
         <v>0.0637793926659979</v>
       </c>
       <c r="AL52" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$7:$F$7,TRANSPOSE(AL$45:AL$49))</f>
+        <f aca="false">$B7*AL$45+$C7*AL$46+$D7*AL$47+$E7*AL$48+$F7*AL$49</f>
         <v>0.0644030426356731</v>
       </c>
       <c r="AM52" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$7:$F$7,TRANSPOSE(AM$45:AM$49))</f>
+        <f aca="false">$B7*AM$45+$C7*AM$46+$D7*AM$47+$E7*AM$48+$F7*AM$49</f>
         <v>0.0650527596648829</v>
       </c>
       <c r="AN52" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$7:$F$7,TRANSPOSE(AN$45:AN$49))</f>
+        <f aca="false">$B7*AN$45+$C7*AN$46+$D7*AN$47+$E7*AN$48+$F7*AN$49</f>
         <v>0.0657071148168149</v>
       </c>
       <c r="AO52" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$7:$F$7,TRANSPOSE(AO$45:AO$49))</f>
+        <f aca="false">$B7*AO$45+$C7*AO$46+$D7*AO$47+$E7*AO$48+$F7*AO$49</f>
         <v>0.066347161693678</v>
       </c>
       <c r="AP52" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$7:$F$7,TRANSPOSE(AP$45:AP$49))</f>
+        <f aca="false">$B7*AP$45+$C7*AP$46+$D7*AP$47+$E7*AP$48+$F7*AP$49</f>
         <v>0.0669575038817295</v>
       </c>
       <c r="AQ52" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$7:$F$7,TRANSPOSE(AQ$45:AQ$49))</f>
+        <f aca="false">$B7*AQ$45+$C7*AQ$46+$D7*AQ$47+$E7*AQ$48+$F7*AQ$49</f>
         <v>0.0675267947190303</v>
       </c>
       <c r="AR52" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$7:$F$7,TRANSPOSE(AR$45:AR$49))</f>
+        <f aca="false">$B7*AR$45+$C7*AR$46+$D7*AR$47+$E7*AR$48+$F7*AR$49</f>
         <v>0.0680477147256546</v>
       </c>
       <c r="AS52" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$7:$F$7,TRANSPOSE(AS$45:AS$49))</f>
+        <f aca="false">$B7*AS$45+$C7*AS$46+$D7*AS$47+$E7*AS$48+$F7*AS$49</f>
         <v>0.0685165578021</v>
       </c>
     </row>
@@ -25354,147 +25354,147 @@
         <v>237</v>
       </c>
       <c r="J53" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$8:$F$8,TRANSPOSE(J$45:J$49))</f>
-        <v>0.0746724171146181</v>
+        <f aca="false">$B8*J$45+$C8*J$46+$D8*J$47+$E8*J$48+$F8*J$49</f>
+        <v>0.074672417114618</v>
       </c>
       <c r="K53" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$8:$F$8,TRANSPOSE(K$45:K$49))</f>
+        <f aca="false">$B8*K$45+$C8*K$46+$D8*K$47+$E8*K$48+$F8*K$49</f>
         <v>0.0738504073539834</v>
       </c>
       <c r="L53" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$8:$F$8,TRANSPOSE(L$45:L$49))</f>
+        <f aca="false">$B8*L$45+$C8*L$46+$D8*L$47+$E8*L$48+$F8*L$49</f>
         <v>0.0730283474493624</v>
       </c>
       <c r="M53" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$8:$F$8,TRANSPOSE(M$45:M$49))</f>
+        <f aca="false">$B8*M$45+$C8*M$46+$D8*M$47+$E8*M$48+$F8*M$49</f>
         <v>0.0722076889095901</v>
       </c>
       <c r="N53" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$8:$F$8,TRANSPOSE(N$45:N$49))</f>
+        <f aca="false">$B8*N$45+$C8*N$46+$D8*N$47+$E8*N$48+$F8*N$49</f>
         <v>0.0713900422567302</v>
       </c>
       <c r="O53" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$8:$F$8,TRANSPOSE(O$45:O$49))</f>
+        <f aca="false">$B8*O$45+$C8*O$46+$D8*O$47+$E8*O$48+$F8*O$49</f>
         <v>0.070577217435329</v>
       </c>
       <c r="P53" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$8:$F$8,TRANSPOSE(P$45:P$49))</f>
+        <f aca="false">$B8*P$45+$C8*P$46+$D8*P$47+$E8*P$48+$F8*P$49</f>
         <v>0.069771275719457</v>
       </c>
       <c r="Q53" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$8:$F$8,TRANSPOSE(Q$45:Q$49))</f>
+        <f aca="false">$B8*Q$45+$C8*Q$46+$D8*Q$47+$E8*Q$48+$F8*Q$49</f>
         <v>0.0689745952097068</v>
       </c>
       <c r="R53" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$8:$F$8,TRANSPOSE(R$45:R$49))</f>
+        <f aca="false">$B8*R$45+$C8*R$46+$D8*R$47+$E8*R$48+$F8*R$49</f>
         <v>0.0681899518382093</v>
       </c>
       <c r="S53" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$8:$F$8,TRANSPOSE(S$45:S$49))</f>
+        <f aca="false">$B8*S$45+$C8*S$46+$D8*S$47+$E8*S$48+$F8*S$49</f>
         <v>0.0674206171774841</v>
       </c>
       <c r="T53" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$8:$F$8,TRANSPOSE(T$45:T$49))</f>
+        <f aca="false">$B8*T$45+$C8*T$46+$D8*T$47+$E8*T$48+$F8*T$49</f>
         <v>0.0666704729800515</v>
       </c>
       <c r="U53" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$8:$F$8,TRANSPOSE(U$45:U$49))</f>
+        <f aca="false">$B8*U$45+$C8*U$46+$D8*U$47+$E8*U$48+$F8*U$49</f>
         <v>0.0659441398464553</v>
       </c>
       <c r="V53" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$8:$F$8,TRANSPOSE(V$45:V$49))</f>
+        <f aca="false">$B8*V$45+$C8*V$46+$D8*V$47+$E8*V$48+$F8*V$49</f>
         <v>0.0652471132181326</v>
       </c>
       <c r="W53" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$8:$F$8,TRANSPOSE(W$45:W$49))</f>
+        <f aca="false">$B8*W$45+$C8*W$46+$D8*W$47+$E8*W$48+$F8*W$49</f>
         <v>0.0645858935090579</v>
       </c>
       <c r="X53" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$8:$F$8,TRANSPOSE(X$45:X$49))</f>
+        <f aca="false">$B8*X$45+$C8*X$46+$D8*X$47+$E8*X$48+$F8*X$49</f>
         <v>0.0639680883760655</v>
       </c>
       <c r="Y53" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$8:$F$8,TRANSPOSE(Y$45:Y$49))</f>
-        <v>0.0634024543793252</v>
+        <f aca="false">$B8*Y$45+$C8*Y$46+$D8*Y$47+$E8*Y$48+$F8*Y$49</f>
+        <v>0.0634024543793253</v>
       </c>
       <c r="Z53" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$8:$F$8,TRANSPOSE(Z$45:Z$49))</f>
+        <f aca="false">$B8*Z$45+$C8*Z$46+$D8*Z$47+$E8*Z$48+$F8*Z$49</f>
         <v>0.0628988345471524</v>
       </c>
       <c r="AA53" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$8:$F$8,TRANSPOSE(AA$45:AA$49))</f>
+        <f aca="false">$B8*AA$45+$C8*AA$46+$D8*AA$47+$E8*AA$48+$F8*AA$49</f>
         <v>0.0624679416484595</v>
       </c>
       <c r="AB53" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$8:$F$8,TRANSPOSE(AB$45:AB$49))</f>
+        <f aca="false">$B8*AB$45+$C8*AB$46+$D8*AB$47+$E8*AB$48+$F8*AB$49</f>
         <v>0.0621209401826656</v>
       </c>
       <c r="AC53" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$8:$F$8,TRANSPOSE(AC$45:AC$49))</f>
+        <f aca="false">$B8*AC$45+$C8*AC$46+$D8*AC$47+$E8*AC$48+$F8*AC$49</f>
         <v>0.0618687990202628</v>
       </c>
       <c r="AD53" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$8:$F$8,TRANSPOSE(AD$45:AD$49))</f>
+        <f aca="false">$B8*AD$45+$C8*AD$46+$D8*AD$47+$E8*AD$48+$F8*AD$49</f>
         <v>0.0617214231521614</v>
       </c>
       <c r="AE53" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$8:$F$8,TRANSPOSE(AE$45:AE$49))</f>
+        <f aca="false">$B8*AE$45+$C8*AE$46+$D8*AE$47+$E8*AE$48+$F8*AE$49</f>
         <v>0.0616866217378462</v>
       </c>
       <c r="AF53" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$8:$F$8,TRANSPOSE(AF$45:AF$49))</f>
+        <f aca="false">$B8*AF$45+$C8*AF$46+$D8*AF$47+$E8*AF$48+$F8*AF$49</f>
         <v>0.0617690191061722</v>
       </c>
       <c r="AG53" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$8:$F$8,TRANSPOSE(AG$45:AG$49))</f>
+        <f aca="false">$B8*AG$45+$C8*AG$46+$D8*AG$47+$E8*AG$48+$F8*AG$49</f>
         <v>0.0619690545798268</v>
       </c>
       <c r="AH53" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$8:$F$8,TRANSPOSE(AH$45:AH$49))</f>
+        <f aca="false">$B8*AH$45+$C8*AH$46+$D8*AH$47+$E8*AH$48+$F8*AH$49</f>
         <v>0.0622822403500403</v>
       </c>
       <c r="AI53" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$8:$F$8,TRANSPOSE(AI$45:AI$49))</f>
+        <f aca="false">$B8*AI$45+$C8*AI$46+$D8*AI$47+$E8*AI$48+$F8*AI$49</f>
         <v>0.0626988489619953</v>
       </c>
       <c r="AJ53" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$8:$F$8,TRANSPOSE(AJ$45:AJ$49))</f>
+        <f aca="false">$B8*AJ$45+$C8*AJ$46+$D8*AJ$47+$E8*AJ$48+$F8*AJ$49</f>
         <v>0.0632041699504232</v>
       </c>
       <c r="AK53" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$8:$F$8,TRANSPOSE(AK$45:AK$49))</f>
+        <f aca="false">$B8*AK$45+$C8*AK$46+$D8*AK$47+$E8*AK$48+$F8*AK$49</f>
         <v>0.0637793926659979</v>
       </c>
       <c r="AL53" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$8:$F$8,TRANSPOSE(AL$45:AL$49))</f>
+        <f aca="false">$B8*AL$45+$C8*AL$46+$D8*AL$47+$E8*AL$48+$F8*AL$49</f>
         <v>0.0644030426356731</v>
       </c>
       <c r="AM53" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$8:$F$8,TRANSPOSE(AM$45:AM$49))</f>
+        <f aca="false">$B8*AM$45+$C8*AM$46+$D8*AM$47+$E8*AM$48+$F8*AM$49</f>
         <v>0.0650527596648829</v>
       </c>
       <c r="AN53" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$8:$F$8,TRANSPOSE(AN$45:AN$49))</f>
+        <f aca="false">$B8*AN$45+$C8*AN$46+$D8*AN$47+$E8*AN$48+$F8*AN$49</f>
         <v>0.0657071148168149</v>
       </c>
       <c r="AO53" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$8:$F$8,TRANSPOSE(AO$45:AO$49))</f>
+        <f aca="false">$B8*AO$45+$C8*AO$46+$D8*AO$47+$E8*AO$48+$F8*AO$49</f>
         <v>0.066347161693678</v>
       </c>
       <c r="AP53" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$8:$F$8,TRANSPOSE(AP$45:AP$49))</f>
+        <f aca="false">$B8*AP$45+$C8*AP$46+$D8*AP$47+$E8*AP$48+$F8*AP$49</f>
         <v>0.0669575038817295</v>
       </c>
       <c r="AQ53" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$8:$F$8,TRANSPOSE(AQ$45:AQ$49))</f>
+        <f aca="false">$B8*AQ$45+$C8*AQ$46+$D8*AQ$47+$E8*AQ$48+$F8*AQ$49</f>
         <v>0.0675267947190303</v>
       </c>
       <c r="AR53" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$8:$F$8,TRANSPOSE(AR$45:AR$49))</f>
+        <f aca="false">$B8*AR$45+$C8*AR$46+$D8*AR$47+$E8*AR$48+$F8*AR$49</f>
         <v>0.0680477147256546</v>
       </c>
       <c r="AS53" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$8:$F$8,TRANSPOSE(AS$45:AS$49))</f>
+        <f aca="false">$B8*AS$45+$C8*AS$46+$D8*AS$47+$E8*AS$48+$F8*AS$49</f>
         <v>0.0685165578021</v>
       </c>
     </row>
@@ -25503,147 +25503,147 @@
         <v>238</v>
       </c>
       <c r="J54" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$9:$F$9,TRANSPOSE(J$45:J$49))</f>
-        <v>0.0746724171146181</v>
+        <f aca="false">$B9*J$45+$C9*J$46+$D9*J$47+$E9*J$48+$F9*J$49</f>
+        <v>0.074672417114618</v>
       </c>
       <c r="K54" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$9:$F$9,TRANSPOSE(K$45:K$49))</f>
+        <f aca="false">$B9*K$45+$C9*K$46+$D9*K$47+$E9*K$48+$F9*K$49</f>
         <v>0.0738504073539834</v>
       </c>
       <c r="L54" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$9:$F$9,TRANSPOSE(L$45:L$49))</f>
+        <f aca="false">$B9*L$45+$C9*L$46+$D9*L$47+$E9*L$48+$F9*L$49</f>
         <v>0.0730283474493624</v>
       </c>
       <c r="M54" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$9:$F$9,TRANSPOSE(M$45:M$49))</f>
+        <f aca="false">$B9*M$45+$C9*M$46+$D9*M$47+$E9*M$48+$F9*M$49</f>
         <v>0.0722076889095901</v>
       </c>
       <c r="N54" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$9:$F$9,TRANSPOSE(N$45:N$49))</f>
+        <f aca="false">$B9*N$45+$C9*N$46+$D9*N$47+$E9*N$48+$F9*N$49</f>
         <v>0.0713900422567302</v>
       </c>
       <c r="O54" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$9:$F$9,TRANSPOSE(O$45:O$49))</f>
+        <f aca="false">$B9*O$45+$C9*O$46+$D9*O$47+$E9*O$48+$F9*O$49</f>
         <v>0.070577217435329</v>
       </c>
       <c r="P54" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$9:$F$9,TRANSPOSE(P$45:P$49))</f>
+        <f aca="false">$B9*P$45+$C9*P$46+$D9*P$47+$E9*P$48+$F9*P$49</f>
         <v>0.069771275719457</v>
       </c>
       <c r="Q54" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$9:$F$9,TRANSPOSE(Q$45:Q$49))</f>
+        <f aca="false">$B9*Q$45+$C9*Q$46+$D9*Q$47+$E9*Q$48+$F9*Q$49</f>
         <v>0.0689745952097068</v>
       </c>
       <c r="R54" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$9:$F$9,TRANSPOSE(R$45:R$49))</f>
+        <f aca="false">$B9*R$45+$C9*R$46+$D9*R$47+$E9*R$48+$F9*R$49</f>
         <v>0.0681899518382093</v>
       </c>
       <c r="S54" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$9:$F$9,TRANSPOSE(S$45:S$49))</f>
+        <f aca="false">$B9*S$45+$C9*S$46+$D9*S$47+$E9*S$48+$F9*S$49</f>
         <v>0.0674206171774841</v>
       </c>
       <c r="T54" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$9:$F$9,TRANSPOSE(T$45:T$49))</f>
+        <f aca="false">$B9*T$45+$C9*T$46+$D9*T$47+$E9*T$48+$F9*T$49</f>
         <v>0.0666704729800515</v>
       </c>
       <c r="U54" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$9:$F$9,TRANSPOSE(U$45:U$49))</f>
+        <f aca="false">$B9*U$45+$C9*U$46+$D9*U$47+$E9*U$48+$F9*U$49</f>
         <v>0.0659441398464553</v>
       </c>
       <c r="V54" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$9:$F$9,TRANSPOSE(V$45:V$49))</f>
+        <f aca="false">$B9*V$45+$C9*V$46+$D9*V$47+$E9*V$48+$F9*V$49</f>
         <v>0.0652471132181326</v>
       </c>
       <c r="W54" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$9:$F$9,TRANSPOSE(W$45:W$49))</f>
+        <f aca="false">$B9*W$45+$C9*W$46+$D9*W$47+$E9*W$48+$F9*W$49</f>
         <v>0.0645858935090579</v>
       </c>
       <c r="X54" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$9:$F$9,TRANSPOSE(X$45:X$49))</f>
+        <f aca="false">$B9*X$45+$C9*X$46+$D9*X$47+$E9*X$48+$F9*X$49</f>
         <v>0.0639680883760655</v>
       </c>
       <c r="Y54" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$9:$F$9,TRANSPOSE(Y$45:Y$49))</f>
-        <v>0.0634024543793252</v>
+        <f aca="false">$B9*Y$45+$C9*Y$46+$D9*Y$47+$E9*Y$48+$F9*Y$49</f>
+        <v>0.0634024543793253</v>
       </c>
       <c r="Z54" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$9:$F$9,TRANSPOSE(Z$45:Z$49))</f>
+        <f aca="false">$B9*Z$45+$C9*Z$46+$D9*Z$47+$E9*Z$48+$F9*Z$49</f>
         <v>0.0628988345471524</v>
       </c>
       <c r="AA54" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$9:$F$9,TRANSPOSE(AA$45:AA$49))</f>
+        <f aca="false">$B9*AA$45+$C9*AA$46+$D9*AA$47+$E9*AA$48+$F9*AA$49</f>
         <v>0.0624679416484595</v>
       </c>
       <c r="AB54" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$9:$F$9,TRANSPOSE(AB$45:AB$49))</f>
+        <f aca="false">$B9*AB$45+$C9*AB$46+$D9*AB$47+$E9*AB$48+$F9*AB$49</f>
         <v>0.0621209401826656</v>
       </c>
       <c r="AC54" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$9:$F$9,TRANSPOSE(AC$45:AC$49))</f>
+        <f aca="false">$B9*AC$45+$C9*AC$46+$D9*AC$47+$E9*AC$48+$F9*AC$49</f>
         <v>0.0618687990202628</v>
       </c>
       <c r="AD54" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$9:$F$9,TRANSPOSE(AD$45:AD$49))</f>
+        <f aca="false">$B9*AD$45+$C9*AD$46+$D9*AD$47+$E9*AD$48+$F9*AD$49</f>
         <v>0.0617214231521614</v>
       </c>
       <c r="AE54" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$9:$F$9,TRANSPOSE(AE$45:AE$49))</f>
+        <f aca="false">$B9*AE$45+$C9*AE$46+$D9*AE$47+$E9*AE$48+$F9*AE$49</f>
         <v>0.0616866217378462</v>
       </c>
       <c r="AF54" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$9:$F$9,TRANSPOSE(AF$45:AF$49))</f>
+        <f aca="false">$B9*AF$45+$C9*AF$46+$D9*AF$47+$E9*AF$48+$F9*AF$49</f>
         <v>0.0617690191061722</v>
       </c>
       <c r="AG54" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$9:$F$9,TRANSPOSE(AG$45:AG$49))</f>
+        <f aca="false">$B9*AG$45+$C9*AG$46+$D9*AG$47+$E9*AG$48+$F9*AG$49</f>
         <v>0.0619690545798268</v>
       </c>
       <c r="AH54" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$9:$F$9,TRANSPOSE(AH$45:AH$49))</f>
+        <f aca="false">$B9*AH$45+$C9*AH$46+$D9*AH$47+$E9*AH$48+$F9*AH$49</f>
         <v>0.0622822403500403</v>
       </c>
       <c r="AI54" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$9:$F$9,TRANSPOSE(AI$45:AI$49))</f>
+        <f aca="false">$B9*AI$45+$C9*AI$46+$D9*AI$47+$E9*AI$48+$F9*AI$49</f>
         <v>0.0626988489619953</v>
       </c>
       <c r="AJ54" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$9:$F$9,TRANSPOSE(AJ$45:AJ$49))</f>
+        <f aca="false">$B9*AJ$45+$C9*AJ$46+$D9*AJ$47+$E9*AJ$48+$F9*AJ$49</f>
         <v>0.0632041699504232</v>
       </c>
       <c r="AK54" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$9:$F$9,TRANSPOSE(AK$45:AK$49))</f>
+        <f aca="false">$B9*AK$45+$C9*AK$46+$D9*AK$47+$E9*AK$48+$F9*AK$49</f>
         <v>0.0637793926659979</v>
       </c>
       <c r="AL54" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$9:$F$9,TRANSPOSE(AL$45:AL$49))</f>
+        <f aca="false">$B9*AL$45+$C9*AL$46+$D9*AL$47+$E9*AL$48+$F9*AL$49</f>
         <v>0.0644030426356731</v>
       </c>
       <c r="AM54" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$9:$F$9,TRANSPOSE(AM$45:AM$49))</f>
+        <f aca="false">$B9*AM$45+$C9*AM$46+$D9*AM$47+$E9*AM$48+$F9*AM$49</f>
         <v>0.0650527596648829</v>
       </c>
       <c r="AN54" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$9:$F$9,TRANSPOSE(AN$45:AN$49))</f>
+        <f aca="false">$B9*AN$45+$C9*AN$46+$D9*AN$47+$E9*AN$48+$F9*AN$49</f>
         <v>0.0657071148168149</v>
       </c>
       <c r="AO54" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$9:$F$9,TRANSPOSE(AO$45:AO$49))</f>
+        <f aca="false">$B9*AO$45+$C9*AO$46+$D9*AO$47+$E9*AO$48+$F9*AO$49</f>
         <v>0.066347161693678</v>
       </c>
       <c r="AP54" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$9:$F$9,TRANSPOSE(AP$45:AP$49))</f>
+        <f aca="false">$B9*AP$45+$C9*AP$46+$D9*AP$47+$E9*AP$48+$F9*AP$49</f>
         <v>0.0669575038817295</v>
       </c>
       <c r="AQ54" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$9:$F$9,TRANSPOSE(AQ$45:AQ$49))</f>
+        <f aca="false">$B9*AQ$45+$C9*AQ$46+$D9*AQ$47+$E9*AQ$48+$F9*AQ$49</f>
         <v>0.0675267947190303</v>
       </c>
       <c r="AR54" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$9:$F$9,TRANSPOSE(AR$45:AR$49))</f>
+        <f aca="false">$B9*AR$45+$C9*AR$46+$D9*AR$47+$E9*AR$48+$F9*AR$49</f>
         <v>0.0680477147256546</v>
       </c>
       <c r="AS54" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$9:$F$9,TRANSPOSE(AS$45:AS$49))</f>
+        <f aca="false">$B9*AS$45+$C9*AS$46+$D9*AS$47+$E9*AS$48+$F9*AS$49</f>
         <v>0.0685165578021</v>
       </c>
     </row>
@@ -25652,147 +25652,147 @@
         <v>239</v>
       </c>
       <c r="J55" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$10:$F$10,TRANSPOSE(J$45:J$49))</f>
+        <f aca="false">$B10*J$45+$C10*J$46+$D10*J$47+$E10*J$48+$F10*J$49</f>
         <v>0.0692330801411735</v>
       </c>
       <c r="K55" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$10:$F$10,TRANSPOSE(K$45:K$49))</f>
+        <f aca="false">$B10*K$45+$C10*K$46+$D10*K$47+$E10*K$48+$F10*K$49</f>
         <v>0.0685226198244188</v>
       </c>
       <c r="L55" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$10:$F$10,TRANSPOSE(L$45:L$49))</f>
+        <f aca="false">$B10*L$45+$C10*L$46+$D10*L$47+$E10*L$48+$F10*L$49</f>
         <v>0.0678124978744874</v>
       </c>
       <c r="M55" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$10:$F$10,TRANSPOSE(M$45:M$49))</f>
+        <f aca="false">$B10*M$45+$C10*M$46+$D10*M$47+$E10*M$48+$F10*M$49</f>
         <v>0.0671039819102292</v>
       </c>
       <c r="N55" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$10:$F$10,TRANSPOSE(N$45:N$49))</f>
+        <f aca="false">$B10*N$45+$C10*N$46+$D10*N$47+$E10*N$48+$F10*N$49</f>
         <v>0.0663984734577139</v>
       </c>
       <c r="O55" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$10:$F$10,TRANSPOSE(O$45:O$49))</f>
+        <f aca="false">$B10*O$45+$C10*O$46+$D10*O$47+$E10*O$48+$F10*O$49</f>
         <v>0.0656975413387995</v>
       </c>
       <c r="P55" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$10:$F$10,TRANSPOSE(P$45:P$49))</f>
+        <f aca="false">$B10*P$45+$C10*P$46+$D10*P$47+$E10*P$48+$F10*P$49</f>
         <v>0.0650029644191802</v>
       </c>
       <c r="Q55" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$10:$F$10,TRANSPOSE(Q$45:Q$49))</f>
+        <f aca="false">$B10*Q$45+$C10*Q$46+$D10*Q$47+$E10*Q$48+$F10*Q$49</f>
         <v>0.0643167853477669</v>
       </c>
       <c r="R55" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$10:$F$10,TRANSPOSE(R$45:R$49))</f>
+        <f aca="false">$B10*R$45+$C10*R$46+$D10*R$47+$E10*R$48+$F10*R$49</f>
         <v>0.0636413767539967</v>
       </c>
       <c r="S55" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$10:$F$10,TRANSPOSE(S$45:S$49))</f>
+        <f aca="false">$B10*S$45+$C10*S$46+$D10*S$47+$E10*S$48+$F10*S$49</f>
         <v>0.0629795208533366</v>
       </c>
       <c r="T55" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$10:$F$10,TRANSPOSE(T$45:T$49))</f>
+        <f aca="false">$B10*T$45+$C10*T$46+$D10*T$47+$E10*T$48+$F10*T$49</f>
         <v>0.0623345023246664</v>
       </c>
       <c r="U55" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$10:$F$10,TRANSPOSE(U$45:U$49))</f>
+        <f aca="false">$B10*U$45+$C10*U$46+$D10*U$47+$E10*U$48+$F10*U$49</f>
         <v>0.0617102123693661</v>
       </c>
       <c r="V55" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$10:$F$10,TRANSPOSE(V$45:V$49))</f>
+        <f aca="false">$B10*V$45+$C10*V$46+$D10*V$47+$E10*V$48+$F10*V$49</f>
         <v>0.0611112586803716</v>
       </c>
       <c r="W55" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$10:$F$10,TRANSPOSE(W$45:W$49))</f>
+        <f aca="false">$B10*W$45+$C10*W$46+$D10*W$47+$E10*W$48+$F10*W$49</f>
         <v>0.0605430712840707</v>
       </c>
       <c r="X55" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$10:$F$10,TRANSPOSE(X$45:X$49))</f>
+        <f aca="false">$B10*X$45+$C10*X$46+$D10*X$47+$E10*X$48+$F10*X$49</f>
         <v>0.0600119876810291</v>
       </c>
       <c r="Y55" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$10:$F$10,TRANSPOSE(Y$45:Y$49))</f>
+        <f aca="false">$B10*Y$45+$C10*Y$46+$D10*Y$47+$E10*Y$48+$F10*Y$49</f>
         <v>0.0595252926853877</v>
       </c>
       <c r="Z55" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$10:$F$10,TRANSPOSE(Z$45:Z$49))</f>
+        <f aca="false">$B10*Z$45+$C10*Z$46+$D10*Z$47+$E10*Z$48+$F10*Z$49</f>
         <v>0.0590911800258756</v>
       </c>
       <c r="AA55" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$10:$F$10,TRANSPOSE(AA$45:AA$49))</f>
+        <f aca="false">$B10*AA$45+$C10*AA$46+$D10*AA$47+$E10*AA$48+$F10*AA$49</f>
         <v>0.0587185965940476</v>
       </c>
       <c r="AB55" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$10:$F$10,TRANSPOSE(AB$45:AB$49))</f>
+        <f aca="false">$B10*AB$45+$C10*AB$46+$D10*AB$47+$E10*AB$48+$F10*AB$49</f>
         <v>0.0584169299627093</v>
       </c>
       <c r="AC55" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$10:$F$10,TRANSPOSE(AC$45:AC$49))</f>
+        <f aca="false">$B10*AC$45+$C10*AC$46+$D10*AC$47+$E10*AC$48+$F10*AC$49</f>
         <v>0.0581955096188115</v>
       </c>
       <c r="AD55" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$10:$F$10,TRANSPOSE(AD$45:AD$49))</f>
+        <f aca="false">$B10*AD$45+$C10*AD$46+$D10*AD$47+$E10*AD$48+$F10*AD$49</f>
         <v>0.0580629150626762</v>
       </c>
       <c r="AE55" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$10:$F$10,TRANSPOSE(AE$45:AE$49))</f>
+        <f aca="false">$B10*AE$45+$C10*AE$46+$D10*AE$47+$E10*AE$48+$F10*AE$49</f>
         <v>0.0580261192036673</v>
       </c>
       <c r="AF55" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$10:$F$10,TRANSPOSE(AF$45:AF$49))</f>
+        <f aca="false">$B10*AF$45+$C10*AF$46+$D10*AF$47+$E10*AF$48+$F10*AF$49</f>
         <v>0.0580895395987988</v>
       </c>
       <c r="AG55" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$10:$F$10,TRANSPOSE(AG$45:AG$49))</f>
+        <f aca="false">$B10*AG$45+$C10*AG$46+$D10*AG$47+$E10*AG$48+$F10*AG$49</f>
         <v>0.0582541168021599</v>
       </c>
       <c r="AH55" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$10:$F$10,TRANSPOSE(AH$45:AH$49))</f>
+        <f aca="false">$B10*AH$45+$C10*AH$46+$D10*AH$47+$E10*AH$48+$F10*AH$49</f>
         <v>0.0585165790375695</v>
       </c>
       <c r="AI55" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$10:$F$10,TRANSPOSE(AI$45:AI$49))</f>
+        <f aca="false">$B10*AI$45+$C10*AI$46+$D10*AI$47+$E10*AI$48+$F10*AI$49</f>
         <v>0.0588690699651988</v>
       </c>
       <c r="AJ55" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$10:$F$10,TRANSPOSE(AJ$45:AJ$49))</f>
+        <f aca="false">$B10*AJ$45+$C10*AJ$46+$D10*AJ$47+$E10*AJ$48+$F10*AJ$49</f>
         <v>0.0592992904925718</v>
       </c>
       <c r="AK55" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$10:$F$10,TRANSPOSE(AK$45:AK$49))</f>
+        <f aca="false">$B10*AK$45+$C10*AK$46+$D10*AK$47+$E10*AK$48+$F10*AK$49</f>
         <v>0.0597912223870783</v>
       </c>
       <c r="AL55" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$10:$F$10,TRANSPOSE(AL$45:AL$49))</f>
+        <f aca="false">$B10*AL$45+$C10*AL$46+$D10*AL$47+$E10*AL$48+$F10*AL$49</f>
         <v>0.0603263722179093</v>
       </c>
       <c r="AM55" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$10:$F$10,TRANSPOSE(AM$45:AM$49))</f>
+        <f aca="false">$B10*AM$45+$C10*AM$46+$D10*AM$47+$E10*AM$48+$F10*AM$49</f>
         <v>0.0608853409329714</v>
       </c>
       <c r="AN55" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$10:$F$10,TRANSPOSE(AN$45:AN$49))</f>
+        <f aca="false">$B10*AN$45+$C10*AN$46+$D10*AN$47+$E10*AN$48+$F10*AN$49</f>
         <v>0.0614494410008757</v>
       </c>
       <c r="AO55" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$10:$F$10,TRANSPOSE(AO$45:AO$49))</f>
+        <f aca="false">$B10*AO$45+$C10*AO$46+$D10*AO$47+$E10*AO$48+$F10*AO$49</f>
         <v>0.0620020837990055</v>
       </c>
       <c r="AP55" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$10:$F$10,TRANSPOSE(AP$45:AP$49))</f>
+        <f aca="false">$B10*AP$45+$C10*AP$46+$D10*AP$47+$E10*AP$48+$F10*AP$49</f>
         <v>0.0625297400267074</v>
       </c>
       <c r="AQ55" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$10:$F$10,TRANSPOSE(AQ$45:AQ$49))</f>
+        <f aca="false">$B10*AQ$45+$C10*AQ$46+$D10*AQ$47+$E10*AQ$48+$F10*AQ$49</f>
         <v>0.0630223973868469</v>
       </c>
       <c r="AR55" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$10:$F$10,TRANSPOSE(AR$45:AR$49))</f>
+        <f aca="false">$B10*AR$45+$C10*AR$46+$D10*AR$47+$E10*AR$48+$F10*AR$49</f>
         <v>0.0634735552437981</v>
       </c>
       <c r="AS55" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$10:$F$10,TRANSPOSE(AS$45:AS$49))</f>
+        <f aca="false">$B10*AS$45+$C10*AS$46+$D10*AS$47+$E10*AS$48+$F10*AS$49</f>
         <v>0.0638798720606386</v>
       </c>
     </row>
@@ -25801,148 +25801,148 @@
         <v>240</v>
       </c>
       <c r="J56" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$11:$F$11,TRANSPOSE(J$45:J$49))</f>
+        <f aca="false">$B11*J$45+$C11*J$46+$D11*J$47+$E11*J$48+$F11*J$49</f>
         <v>0.0348654949452785</v>
       </c>
       <c r="K56" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$11:$F$11,TRANSPOSE(K$45:K$49))</f>
+        <f aca="false">$B11*K$45+$C11*K$46+$D11*K$47+$E11*K$48+$F11*K$49</f>
         <v>0.0347699423701346</v>
       </c>
       <c r="L56" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$11:$F$11,TRANSPOSE(L$45:L$49))</f>
+        <f aca="false">$B11*L$45+$C11*L$46+$D11*L$47+$E11*L$48+$F11*L$49</f>
         <v>0.0346758028260864</v>
       </c>
       <c r="M56" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$11:$F$11,TRANSPOSE(M$45:M$49))</f>
-        <v>0.0345832910739925</v>
+        <f aca="false">$B11*M$45+$C11*M$46+$D11*M$47+$E11*M$48+$F11*M$49</f>
+        <v>0.0345832910739926</v>
       </c>
       <c r="N56" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$11:$F$11,TRANSPOSE(N$45:N$49))</f>
+        <f aca="false">$B11*N$45+$C11*N$46+$D11*N$47+$E11*N$48+$F11*N$49</f>
         <v>0.0344926287830103</v>
       </c>
       <c r="O56" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$11:$F$11,TRANSPOSE(O$45:O$49))</f>
+        <f aca="false">$B11*O$45+$C11*O$46+$D11*O$47+$E11*O$48+$F11*O$49</f>
         <v>0.0344040441773284</v>
       </c>
       <c r="P56" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$11:$F$11,TRANSPOSE(P$45:P$49))</f>
+        <f aca="false">$B11*P$45+$C11*P$46+$D11*P$47+$E11*P$48+$F11*P$49</f>
         <v>0.034317771086303</v>
       </c>
       <c r="Q56" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$11:$F$11,TRANSPOSE(Q$45:Q$49))</f>
+        <f aca="false">$B11*Q$45+$C11*Q$46+$D11*Q$47+$E11*Q$48+$F11*Q$49</f>
         <v>0.0342340470446146</v>
       </c>
       <c r="R56" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$11:$F$11,TRANSPOSE(R$45:R$49))</f>
+        <f aca="false">$B11*R$45+$C11*R$46+$D11*R$47+$E11*R$48+$F11*R$49</f>
         <v>0.0341531100163085</v>
       </c>
       <c r="S56" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$11:$F$11,TRANSPOSE(S$45:S$49))</f>
+        <f aca="false">$B11*S$45+$C11*S$46+$D11*S$47+$E11*S$48+$F11*S$49</f>
         <v>0.0340751933113711</v>
       </c>
       <c r="T56" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$11:$F$11,TRANSPOSE(T$45:T$49))</f>
+        <f aca="false">$B11*T$45+$C11*T$46+$D11*T$47+$E11*T$48+$F11*T$49</f>
         <v>0.0340005184198271</v>
       </c>
       <c r="U56" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$11:$F$11,TRANSPOSE(U$45:U$49))</f>
+        <f aca="false">$B11*U$45+$C11*U$46+$D11*U$47+$E11*U$48+$F11*U$49</f>
         <v>0.03392928595887</v>
       </c>
       <c r="V56" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$11:$F$11,TRANSPOSE(V$45:V$49))</f>
+        <f aca="false">$B11*V$45+$C11*V$46+$D11*V$47+$E11*V$48+$F11*V$49</f>
         <v>0.0338616659247201</v>
       </c>
       <c r="W56" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$11:$F$11,TRANSPOSE(W$45:W$49))</f>
+        <f aca="false">$B11*W$45+$C11*W$46+$D11*W$47+$E11*W$48+$F11*W$49</f>
         <v>0.0337977901829834</v>
       </c>
       <c r="X56" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$11:$F$11,TRANSPOSE(X$45:X$49))</f>
+        <f aca="false">$B11*X$45+$C11*X$46+$D11*X$47+$E11*X$48+$F11*X$49</f>
         <v>0.0337377526877717</v>
       </c>
       <c r="Y56" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$11:$F$11,TRANSPOSE(Y$45:Y$49))</f>
+        <f aca="false">$B11*Y$45+$C11*Y$46+$D11*Y$47+$E11*Y$48+$F11*Y$49</f>
         <v>0.0336816258679252</v>
       </c>
       <c r="Z56" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$11:$F$11,TRANSPOSE(Z$45:Z$49))</f>
+        <f aca="false">$B11*Z$45+$C11*Z$46+$D11*Z$47+$E11*Z$48+$F11*Z$49</f>
         <v>0.0336295035351831</v>
       </c>
       <c r="AA56" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$11:$F$11,TRANSPOSE(AA$45:AA$49))</f>
+        <f aca="false">$B11*AA$45+$C11*AA$46+$D11*AA$47+$E11*AA$48+$F11*AA$49</f>
         <v>0.0335815787356708</v>
       </c>
       <c r="AB56" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$11:$F$11,TRANSPOSE(AB$45:AB$49))</f>
+        <f aca="false">$B11*AB$45+$C11*AB$46+$D11*AB$47+$E11*AB$48+$F11*AB$49</f>
         <v>0.0335382554679285</v>
       </c>
       <c r="AC56" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$11:$F$11,TRANSPOSE(AC$45:AC$49))</f>
+        <f aca="false">$B11*AC$45+$C11*AC$46+$D11*AC$47+$E11*AC$48+$F11*AC$49</f>
         <v>0.0335002739982596</v>
       </c>
       <c r="AD56" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$11:$F$11,TRANSPOSE(AD$45:AD$49))</f>
+        <f aca="false">$B11*AD$45+$C11*AD$46+$D11*AD$47+$E11*AD$48+$F11*AD$49</f>
         <v>0.0334688046141324</v>
       </c>
       <c r="AE56" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$11:$F$11,TRANSPOSE(AE$45:AE$49))</f>
+        <f aca="false">$B11*AE$45+$C11*AE$46+$D11*AE$47+$E11*AE$48+$F11*AE$49</f>
         <v>0.033445447605</v>
       </c>
       <c r="AF56" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$11:$F$11,TRANSPOSE(AF$45:AF$49))</f>
+        <f aca="false">$B11*AF$45+$C11*AF$46+$D11*AF$47+$E11*AF$48+$F11*AF$49</f>
         <v>0.0334320869512962</v>
       </c>
       <c r="AG56" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$11:$F$11,TRANSPOSE(AG$45:AG$49))</f>
+        <f aca="false">$B11*AG$45+$C11*AG$46+$D11*AG$47+$E11*AG$48+$F11*AG$49</f>
         <v>0.0334305911586873</v>
       </c>
       <c r="AH56" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$11:$F$11,TRANSPOSE(AH$45:AH$49))</f>
+        <f aca="false">$B11*AH$45+$C11*AH$46+$D11*AH$47+$E11*AH$48+$F11*AH$49</f>
         <v>0.0334424217539567</v>
       </c>
       <c r="AI56" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$11:$F$11,TRANSPOSE(AI$45:AI$49))</f>
+        <f aca="false">$B11*AI$45+$C11*AI$46+$D11*AI$47+$E11*AI$48+$F11*AI$49</f>
         <v>0.0334682614463603</v>
       </c>
       <c r="AJ56" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$11:$F$11,TRANSPOSE(AJ$45:AJ$49))</f>
+        <f aca="false">$B11*AJ$45+$C11*AJ$46+$D11*AJ$47+$E11*AJ$48+$F11*AJ$49</f>
         <v>0.0335077774033627</v>
       </c>
       <c r="AK56" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$11:$F$11,TRANSPOSE(AK$45:AK$49))</f>
+        <f aca="false">$B11*AK$45+$C11*AK$46+$D11*AK$47+$E11*AK$48+$F11*AK$49</f>
         <v>0.0335595879905559</v>
       </c>
       <c r="AL56" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$11:$F$11,TRANSPOSE(AL$45:AL$49))</f>
+        <f aca="false">$B11*AL$45+$C11*AL$46+$D11*AL$47+$E11*AL$48+$F11*AL$49</f>
         <v>0.033621431119169</v>
       </c>
       <c r="AM56" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$11:$F$11,TRANSPOSE(AM$45:AM$49))</f>
+        <f aca="false">$B11*AM$45+$C11*AM$46+$D11*AM$47+$E11*AM$48+$F11*AM$49</f>
         <v>0.0336904736417163</v>
       </c>
       <c r="AN56" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$11:$F$11,TRANSPOSE(AN$45:AN$49))</f>
+        <f aca="false">$B11*AN$45+$C11*AN$46+$D11*AN$47+$E11*AN$48+$F11*AN$49</f>
         <v>0.0337636743526417</v>
       </c>
       <c r="AO56" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$11:$F$11,TRANSPOSE(AO$45:AO$49))</f>
+        <f aca="false">$B11*AO$45+$C11*AO$46+$D11*AO$47+$E11*AO$48+$F11*AO$49</f>
         <v>0.0338381188809023</v>
       </c>
       <c r="AP56" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$11:$F$11,TRANSPOSE(AP$45:AP$49))</f>
+        <f aca="false">$B11*AP$45+$C11*AP$46+$D11*AP$47+$E11*AP$48+$F11*AP$49</f>
         <v>0.0339112714608195</v>
       </c>
       <c r="AQ56" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$11:$F$11,TRANSPOSE(AQ$45:AQ$49))</f>
+        <f aca="false">$B11*AQ$45+$C11*AQ$46+$D11*AQ$47+$E11*AQ$48+$F11*AQ$49</f>
         <v>0.0339811215467964</v>
       </c>
       <c r="AR56" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$11:$F$11,TRANSPOSE(AR$45:AR$49))</f>
+        <f aca="false">$B11*AR$45+$C11*AR$46+$D11*AR$47+$E11*AR$48+$F11*AR$49</f>
         <v>0.0340462310692238</v>
       </c>
       <c r="AS56" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$11:$F$11,TRANSPOSE(AS$45:AS$49))</f>
-        <v>0.0341057051375201</v>
+        <f aca="false">$B11*AS$45+$C11*AS$46+$D11*AS$47+$E11*AS$48+$F11*AS$49</f>
+        <v>0.03410570513752</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -25950,147 +25950,147 @@
         <v>241</v>
       </c>
       <c r="J57" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$12:$F$12,TRANSPOSE(J$45:J$49))</f>
+        <f aca="false">$B12*J$45+$C12*J$46+$D12*J$47+$E12*J$48+$F12*J$49</f>
         <v>0.0136851621182144</v>
       </c>
       <c r="K57" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$12:$F$12,TRANSPOSE(K$45:K$49))</f>
+        <f aca="false">$B12*K$45+$C12*K$46+$D12*K$47+$E12*K$48+$F12*K$49</f>
         <v>0.0140255169706881</v>
       </c>
       <c r="L57" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$12:$F$12,TRANSPOSE(L$45:L$49))</f>
+        <f aca="false">$B12*L$45+$C12*L$46+$D12*L$47+$E12*L$48+$F12*L$49</f>
         <v>0.0143672601389134</v>
       </c>
       <c r="M57" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$12:$F$12,TRANSPOSE(M$45:M$49))</f>
+        <f aca="false">$B12*M$45+$C12*M$46+$D12*M$47+$E12*M$48+$F12*M$49</f>
         <v>0.0147098357787938</v>
       </c>
       <c r="N57" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$12:$F$12,TRANSPOSE(N$45:N$49))</f>
+        <f aca="false">$B12*N$45+$C12*N$46+$D12*N$47+$E12*N$48+$F12*N$49</f>
         <v>0.0150526105849019</v>
       </c>
       <c r="O57" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$12:$F$12,TRANSPOSE(O$45:O$49))</f>
+        <f aca="false">$B12*O$45+$C12*O$46+$D12*O$47+$E12*O$48+$F12*O$49</f>
         <v>0.015394851990669</v>
       </c>
       <c r="P57" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$12:$F$12,TRANSPOSE(P$45:P$49))</f>
+        <f aca="false">$B12*P$45+$C12*P$46+$D12*P$47+$E12*P$48+$F12*P$49</f>
         <v>0.0157356996795305</v>
       </c>
       <c r="Q57" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$12:$F$12,TRANSPOSE(Q$45:Q$49))</f>
+        <f aca="false">$B12*Q$45+$C12*Q$46+$D12*Q$47+$E12*Q$48+$F12*Q$49</f>
         <v>0.0160741289478779</v>
       </c>
       <c r="R57" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$12:$F$12,TRANSPOSE(R$45:R$49))</f>
+        <f aca="false">$B12*R$45+$C12*R$46+$D12*R$47+$E12*R$48+$F12*R$49</f>
         <v>0.0164089044814076</v>
       </c>
       <c r="S57" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$12:$F$12,TRANSPOSE(S$45:S$49))</f>
+        <f aca="false">$B12*S$45+$C12*S$46+$D12*S$47+$E12*S$48+$F12*S$49</f>
         <v>0.0167385234326358</v>
       </c>
       <c r="T57" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$12:$F$12,TRANSPOSE(T$45:T$49))</f>
+        <f aca="false">$B12*T$45+$C12*T$46+$D12*T$47+$E12*T$48+$F12*T$49</f>
         <v>0.0170611475713129</v>
       </c>
       <c r="U57" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$12:$F$12,TRANSPOSE(U$45:U$49))</f>
+        <f aca="false">$B12*U$45+$C12*U$46+$D12*U$47+$E12*U$48+$F12*U$49</f>
         <v>0.0173745260934044</v>
       </c>
       <c r="V57" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$12:$F$12,TRANSPOSE(V$45:V$49))</f>
+        <f aca="false">$B12*V$45+$C12*V$46+$D12*V$47+$E12*V$48+$F12*V$49</f>
         <v>0.0176759139010456</v>
       </c>
       <c r="W57" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$12:$F$12,TRANSPOSE(W$45:W$49))</f>
+        <f aca="false">$B12*W$45+$C12*W$46+$D12*W$47+$E12*W$48+$F12*W$49</f>
         <v>0.0179619952957186</v>
       </c>
       <c r="X57" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$12:$F$12,TRANSPOSE(X$45:X$49))</f>
+        <f aca="false">$B12*X$45+$C12*X$46+$D12*X$47+$E12*X$48+$F12*X$49</f>
         <v>0.0182288302601412</v>
       </c>
       <c r="Y57" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$12:$F$12,TRANSPOSE(Y$45:Y$49))</f>
+        <f aca="false">$B12*Y$45+$C12*Y$46+$D12*Y$47+$E12*Y$48+$F12*Y$49</f>
         <v>0.0184718491515794</v>
       </c>
       <c r="Z57" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$12:$F$12,TRANSPOSE(Z$45:Z$49))</f>
+        <f aca="false">$B12*Z$45+$C12*Z$46+$D12*Z$47+$E12*Z$48+$F12*Z$49</f>
         <v>0.0186859292286242</v>
       </c>
       <c r="AA57" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$12:$F$12,TRANSPOSE(AA$45:AA$49))</f>
+        <f aca="false">$B12*AA$45+$C12*AA$46+$D12*AA$47+$E12*AA$48+$F12*AA$49</f>
         <v>0.0188655880253012</v>
       </c>
       <c r="AB57" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$12:$F$12,TRANSPOSE(AB$45:AB$49))</f>
+        <f aca="false">$B12*AB$45+$C12*AB$46+$D12*AB$47+$E12*AB$48+$F12*AB$49</f>
         <v>0.0190053173194424</v>
       </c>
       <c r="AC57" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$12:$F$12,TRANSPOSE(AC$45:AC$49))</f>
+        <f aca="false">$B12*AC$45+$C12*AC$46+$D12*AC$47+$E12*AC$48+$F12*AC$49</f>
         <v>0.0191000521128721</v>
       </c>
       <c r="AD57" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$12:$F$12,TRANSPOSE(AD$45:AD$49))</f>
+        <f aca="false">$B12*AD$45+$C12*AD$46+$D12*AD$47+$E12*AD$48+$F12*AD$49</f>
         <v>0.0191457246864335</v>
       </c>
       <c r="AE57" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$12:$F$12,TRANSPOSE(AE$45:AE$49))</f>
+        <f aca="false">$B12*AE$45+$C12*AE$46+$D12*AE$47+$E12*AE$48+$F12*AE$49</f>
         <v>0.0191398109009997</v>
       </c>
       <c r="AF57" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$12:$F$12,TRANSPOSE(AF$45:AF$49))</f>
+        <f aca="false">$B12*AF$45+$C12*AF$46+$D12*AF$47+$E12*AF$48+$F12*AF$49</f>
         <v>0.0190817595763736</v>
       </c>
       <c r="AG57" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$12:$F$12,TRANSPOSE(AG$45:AG$49))</f>
+        <f aca="false">$B12*AG$45+$C12*AG$46+$D12*AG$47+$E12*AG$48+$F12*AG$49</f>
         <v>0.0189732213408111</v>
       </c>
       <c r="AH57" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$12:$F$12,TRANSPOSE(AH$45:AH$49))</f>
+        <f aca="false">$B12*AH$45+$C12*AH$46+$D12*AH$47+$E12*AH$48+$F12*AH$49</f>
         <v>0.0188180484555107</v>
       </c>
       <c r="AI57" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$12:$F$12,TRANSPOSE(AI$45:AI$49))</f>
+        <f aca="false">$B12*AI$45+$C12*AI$46+$D12*AI$47+$E12*AI$48+$F12*AI$49</f>
         <v>0.0186220874971479</v>
       </c>
       <c r="AJ57" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$12:$F$12,TRANSPOSE(AJ$45:AJ$49))</f>
+        <f aca="false">$B12*AJ$45+$C12*AJ$46+$D12*AJ$47+$E12*AJ$48+$F12*AJ$49</f>
         <v>0.0183928068660855</v>
       </c>
       <c r="AK57" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$12:$F$12,TRANSPOSE(AK$45:AK$49))</f>
+        <f aca="false">$B12*AK$45+$C12*AK$46+$D12*AK$47+$E12*AK$48+$F12*AK$49</f>
         <v>0.0181387970724012</v>
       </c>
       <c r="AL57" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$12:$F$12,TRANSPOSE(AL$45:AL$49))</f>
+        <f aca="false">$B12*AL$45+$C12*AL$46+$D12*AL$47+$E12*AL$48+$F12*AL$49</f>
         <v>0.0178691797313749</v>
       </c>
       <c r="AM57" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$12:$F$12,TRANSPOSE(AM$45:AM$49))</f>
+        <f aca="false">$B12*AM$45+$C12*AM$46+$D12*AM$47+$E12*AM$48+$F12*AM$49</f>
         <v>0.0175929761020547</v>
       </c>
       <c r="AN57" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$12:$F$12,TRANSPOSE(AN$45:AN$49))</f>
+        <f aca="false">$B12*AN$45+$C12*AN$46+$D12*AN$47+$E12*AN$48+$F12*AN$49</f>
         <v>0.0173185076919122</v>
       </c>
       <c r="AO57" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$12:$F$12,TRANSPOSE(AO$45:AO$49))</f>
+        <f aca="false">$B12*AO$45+$C12*AO$46+$D12*AO$47+$E12*AO$48+$F12*AO$49</f>
         <v>0.0170529085857817</v>
       </c>
       <c r="AP57" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$12:$F$12,TRANSPOSE(AP$45:AP$49))</f>
+        <f aca="false">$B12*AP$45+$C12*AP$46+$D12*AP$47+$E12*AP$48+$F12*AP$49</f>
         <v>0.0168018104415079</v>
       </c>
       <c r="AQ57" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$12:$F$12,TRANSPOSE(AQ$45:AQ$49))</f>
+        <f aca="false">$B12*AQ$45+$C12*AQ$46+$D12*AQ$47+$E12*AQ$48+$F12*AQ$49</f>
         <v>0.0165692230369363</v>
       </c>
       <c r="AR57" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$12:$F$12,TRANSPOSE(AR$45:AR$49))</f>
+        <f aca="false">$B12*AR$45+$C12*AR$46+$D12*AR$47+$E12*AR$48+$F12*AR$49</f>
         <v>0.0163575925293659</v>
       </c>
       <c r="AS57" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$12:$F$12,TRANSPOSE(AS$45:AS$49))</f>
+        <f aca="false">$B12*AS$45+$C12*AS$46+$D12*AS$47+$E12*AS$48+$F12*AS$49</f>
         <v>0.0161679909443058</v>
       </c>
     </row>
@@ -26099,147 +26099,147 @@
         <v>242</v>
       </c>
       <c r="J58" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$13:$F$13,TRANSPOSE(J$45:J$49))</f>
+        <f aca="false">$B13*J$45+$C13*J$46+$D13*J$47+$E13*J$48+$F13*J$49</f>
         <v>0.0200337603599969</v>
       </c>
       <c r="K58" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$13:$F$13,TRANSPOSE(K$45:K$49))</f>
+        <f aca="false">$B13*K$45+$C13*K$46+$D13*K$47+$E13*K$48+$F13*K$49</f>
         <v>0.0205022156168808</v>
       </c>
       <c r="L58" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$13:$F$13,TRANSPOSE(L$45:L$49))</f>
+        <f aca="false">$B13*L$45+$C13*L$46+$D13*L$47+$E13*L$48+$F13*L$49</f>
         <v>0.0209709398531693</v>
       </c>
       <c r="M58" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$13:$F$13,TRANSPOSE(M$45:M$49))</f>
+        <f aca="false">$B13*M$45+$C13*M$46+$D13*M$47+$E13*M$48+$F13*M$49</f>
         <v>0.0214391148873424</v>
       </c>
       <c r="N58" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$13:$F$13,TRANSPOSE(N$45:N$49))</f>
+        <f aca="false">$B13*N$45+$C13*N$46+$D13*N$47+$E13*N$48+$F13*N$49</f>
         <v>0.0219058292371005</v>
       </c>
       <c r="O58" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$13:$F$13,TRANSPOSE(O$45:O$49))</f>
+        <f aca="false">$B13*O$45+$C13*O$46+$D13*O$47+$E13*O$48+$F13*O$49</f>
         <v>0.0223700539243917</v>
       </c>
       <c r="P58" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$13:$F$13,TRANSPOSE(P$45:P$49))</f>
+        <f aca="false">$B13*P$45+$C13*P$46+$D13*P$47+$E13*P$48+$F13*P$49</f>
         <v>0.0228306112995195</v>
       </c>
       <c r="Q58" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$13:$F$13,TRANSPOSE(Q$45:Q$49))</f>
+        <f aca="false">$B13*Q$45+$C13*Q$46+$D13*Q$47+$E13*Q$48+$F13*Q$49</f>
         <v>0.0232861355632492</v>
       </c>
       <c r="R58" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$13:$F$13,TRANSPOSE(R$45:R$49))</f>
+        <f aca="false">$B13*R$45+$C13*R$46+$D13*R$47+$E13*R$48+$F13*R$49</f>
         <v>0.0237350237550287</v>
       </c>
       <c r="S58" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$13:$F$13,TRANSPOSE(S$45:S$49))</f>
+        <f aca="false">$B13*S$45+$C13*S$46+$D13*S$47+$E13*S$48+$F13*S$49</f>
         <v>0.0241753763473686</v>
       </c>
       <c r="T58" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$13:$F$13,TRANSPOSE(T$45:T$49))</f>
+        <f aca="false">$B13*T$45+$C13*T$46+$D13*T$47+$E13*T$48+$F13*T$49</f>
         <v>0.0246049274403319</v>
       </c>
       <c r="U58" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$13:$F$13,TRANSPOSE(U$45:U$49))</f>
+        <f aca="false">$B13*U$45+$C13*U$46+$D13*U$47+$E13*U$48+$F13*U$49</f>
         <v>0.0250209661671757</v>
       </c>
       <c r="V58" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$13:$F$13,TRANSPOSE(V$45:V$49))</f>
+        <f aca="false">$B13*V$45+$C13*V$46+$D13*V$47+$E13*V$48+$F13*V$49</f>
         <v>0.0254202536552693</v>
       </c>
       <c r="W58" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$13:$F$13,TRANSPOSE(W$45:W$49))</f>
+        <f aca="false">$B13*W$45+$C13*W$46+$D13*W$47+$E13*W$48+$F13*W$49</f>
         <v>0.0257989440886475</v>
       </c>
       <c r="X58" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$13:$F$13,TRANSPOSE(X$45:X$49))</f>
+        <f aca="false">$B13*X$45+$C13*X$46+$D13*X$47+$E13*X$48+$F13*X$49</f>
         <v>0.0261525242531723</v>
       </c>
       <c r="Y58" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$13:$F$13,TRANSPOSE(Y$45:Y$49))</f>
+        <f aca="false">$B13*Y$45+$C13*Y$46+$D13*Y$47+$E13*Y$48+$F13*Y$49</f>
         <v>0.0264757930159719</v>
       </c>
       <c r="Z58" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$13:$F$13,TRANSPOSE(Z$45:Z$49))</f>
+        <f aca="false">$B13*Z$45+$C13*Z$46+$D13*Z$47+$E13*Z$48+$F13*Z$49</f>
         <v>0.0267629090061769</v>
       </c>
       <c r="AA58" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$13:$F$13,TRANSPOSE(AA$45:AA$49))</f>
+        <f aca="false">$B13*AA$45+$C13*AA$46+$D13*AA$47+$E13*AA$48+$F13*AA$49</f>
         <v>0.0270075382766069</v>
       </c>
       <c r="AB58" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$13:$F$13,TRANSPOSE(AB$45:AB$49))</f>
+        <f aca="false">$B13*AB$45+$C13*AB$46+$D13*AB$47+$E13*AB$48+$F13*AB$49</f>
         <v>0.0272031295672848</v>
       </c>
       <c r="AC58" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$13:$F$13,TRANSPOSE(AC$45:AC$49))</f>
+        <f aca="false">$B13*AC$45+$C13*AC$46+$D13*AC$47+$E13*AC$48+$F13*AC$49</f>
         <v>0.0273433290264963</v>
       </c>
       <c r="AD58" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$13:$F$13,TRANSPOSE(AD$45:AD$49))</f>
+        <f aca="false">$B13*AD$45+$C13*AD$46+$D13*AD$47+$E13*AD$48+$F13*AD$49</f>
         <v>0.0274225187131451</v>
       </c>
       <c r="AE58" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$13:$F$13,TRANSPOSE(AE$45:AE$49))</f>
+        <f aca="false">$B13*AE$45+$C13*AE$46+$D13*AE$47+$E13*AE$48+$F13*AE$49</f>
         <v>0.0274364303135935</v>
       </c>
       <c r="AF58" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$13:$F$13,TRANSPOSE(AF$45:AF$49))</f>
+        <f aca="false">$B13*AF$45+$C13*AF$46+$D13*AF$47+$E13*AF$48+$F13*AF$49</f>
         <v>0.0273827585153805</v>
       </c>
       <c r="AG58" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$13:$F$13,TRANSPOSE(AG$45:AG$49))</f>
+        <f aca="false">$B13*AG$45+$C13*AG$46+$D13*AG$47+$E13*AG$48+$F13*AG$49</f>
         <v>0.0272616860855115</v>
       </c>
       <c r="AH58" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$13:$F$13,TRANSPOSE(AH$45:AH$49))</f>
+        <f aca="false">$B13*AH$45+$C13*AH$46+$D13*AH$47+$E13*AH$48+$F13*AH$49</f>
         <v>0.0270762345492014</v>
       </c>
       <c r="AI58" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$13:$F$13,TRANSPOSE(AI$45:AI$49))</f>
+        <f aca="false">$B13*AI$45+$C13*AI$46+$D13*AI$47+$E13*AI$48+$F13*AI$49</f>
         <v>0.0268323647815438</v>
       </c>
       <c r="AJ58" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$13:$F$13,TRANSPOSE(AJ$45:AJ$49))</f>
+        <f aca="false">$B13*AJ$45+$C13*AJ$46+$D13*AJ$47+$E13*AJ$48+$F13*AJ$49</f>
         <v>0.0265387711605064</v>
       </c>
       <c r="AK58" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$13:$F$13,TRANSPOSE(AK$45:AK$49))</f>
+        <f aca="false">$B13*AK$45+$C13*AK$46+$D13*AK$47+$E13*AK$48+$F13*AK$49</f>
         <v>0.0262063504579326</v>
       </c>
       <c r="AL58" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$13:$F$13,TRANSPOSE(AL$45:AL$49))</f>
+        <f aca="false">$B13*AL$45+$C13*AL$46+$D13*AL$47+$E13*AL$48+$F13*AL$49</f>
         <v>0.0258473872120732</v>
       </c>
       <c r="AM58" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$13:$F$13,TRANSPOSE(AM$45:AM$49))</f>
+        <f aca="false">$B13*AM$45+$C13*AM$46+$D13*AM$47+$E13*AM$48+$F13*AM$49</f>
         <v>0.0254745667530096</v>
       </c>
       <c r="AN58" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$13:$F$13,TRANSPOSE(AN$45:AN$49))</f>
+        <f aca="false">$B13*AN$45+$C13*AN$46+$D13*AN$47+$E13*AN$48+$F13*AN$49</f>
         <v>0.0250999757097178</v>
       </c>
       <c r="AO58" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$13:$F$13,TRANSPOSE(AO$45:AO$49))</f>
+        <f aca="false">$B13*AO$45+$C13*AO$46+$D13*AO$47+$E13*AO$48+$F13*AO$49</f>
         <v>0.0247342529106441</v>
       </c>
       <c r="AP58" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$13:$F$13,TRANSPOSE(AP$45:AP$49))</f>
+        <f aca="false">$B13*AP$45+$C13*AP$46+$D13*AP$47+$E13*AP$48+$F13*AP$49</f>
         <v>0.0243860087379037</v>
       </c>
       <c r="AQ58" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$13:$F$13,TRANSPOSE(AQ$45:AQ$49))</f>
+        <f aca="false">$B13*AQ$45+$C13*AQ$46+$D13*AQ$47+$E13*AQ$48+$F13*AQ$49</f>
         <v>0.0240615586552323</v>
       </c>
       <c r="AR58" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$13:$F$13,TRANSPOSE(AR$45:AR$49))</f>
+        <f aca="false">$B13*AR$45+$C13*AR$46+$D13*AR$47+$E13*AR$48+$F13*AR$49</f>
         <v>0.0237649458206917</v>
       </c>
       <c r="AS58" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$13:$F$13,TRANSPOSE(AS$45:AS$49))</f>
+        <f aca="false">$B13*AS$45+$C13*AS$46+$D13*AS$47+$E13*AS$48+$F13*AS$49</f>
         <v>0.0234981801389885</v>
       </c>
     </row>
@@ -26248,147 +26248,147 @@
         <v>243</v>
       </c>
       <c r="J59" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$14:$F$14,TRANSPOSE(J$45:J$49))</f>
+        <f aca="false">$B14*J$45+$C14*J$46+$D14*J$47+$E14*J$48+$F14*J$49</f>
         <v>0.0306630866944912</v>
       </c>
       <c r="K59" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$14:$F$14,TRANSPOSE(K$45:K$49))</f>
+        <f aca="false">$B14*K$45+$C14*K$46+$D14*K$47+$E14*K$48+$F14*K$49</f>
         <v>0.0313562281860301</v>
       </c>
       <c r="L59" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$14:$F$14,TRANSPOSE(L$45:L$49))</f>
+        <f aca="false">$B14*L$45+$C14*L$46+$D14*L$47+$E14*L$48+$F14*L$49</f>
         <v>0.0320481895577625</v>
       </c>
       <c r="M59" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$14:$F$14,TRANSPOSE(M$45:M$49))</f>
+        <f aca="false">$B14*M$45+$C14*M$46+$D14*M$47+$E14*M$48+$F14*M$49</f>
         <v>0.0327377070069906</v>
       </c>
       <c r="N59" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$14:$F$14,TRANSPOSE(N$45:N$49))</f>
+        <f aca="false">$B14*N$45+$C14*N$46+$D14*N$47+$E14*N$48+$F14*N$49</f>
         <v>0.0334233927319238</v>
       </c>
       <c r="O59" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$14:$F$14,TRANSPOSE(O$45:O$49))</f>
+        <f aca="false">$B14*O$45+$C14*O$46+$D14*O$47+$E14*O$48+$F14*O$49</f>
         <v>0.0341037052571554</v>
       </c>
       <c r="P59" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$14:$F$14,TRANSPOSE(P$45:P$49))</f>
+        <f aca="false">$B14*P$45+$C14*P$46+$D14*P$47+$E14*P$48+$F14*P$49</f>
         <v>0.0347769117450992</v>
       </c>
       <c r="Q59" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$14:$F$14,TRANSPOSE(Q$45:Q$49))</f>
+        <f aca="false">$B14*Q$45+$C14*Q$46+$D14*Q$47+$E14*Q$48+$F14*Q$49</f>
         <v>0.0354410410475111</v>
       </c>
       <c r="R59" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$14:$F$14,TRANSPOSE(R$45:R$49))</f>
+        <f aca="false">$B14*R$45+$C14*R$46+$D14*R$47+$E14*R$48+$F14*R$49</f>
         <v>0.036093826443454</v>
       </c>
       <c r="S59" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$14:$F$14,TRANSPOSE(S$45:S$49))</f>
+        <f aca="false">$B14*S$45+$C14*S$46+$D14*S$47+$E14*S$48+$F14*S$49</f>
         <v>0.0367326374760029</v>
       </c>
       <c r="T59" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$14:$F$14,TRANSPOSE(T$45:T$49))</f>
+        <f aca="false">$B14*T$45+$C14*T$46+$D14*T$47+$E14*T$48+$F14*T$49</f>
         <v>0.0373544011793205</v>
       </c>
       <c r="U59" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$14:$F$14,TRANSPOSE(U$45:U$49))</f>
+        <f aca="false">$B14*U$45+$C14*U$46+$D14*U$47+$E14*U$48+$F14*U$49</f>
         <v>0.0379555144546129</v>
       </c>
       <c r="V59" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$14:$F$14,TRANSPOSE(V$45:V$49))</f>
+        <f aca="false">$B14*V$45+$C14*V$46+$D14*V$47+$E14*V$48+$F14*V$49</f>
         <v>0.0385317516034342</v>
       </c>
       <c r="W59" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$14:$F$14,TRANSPOSE(W$45:W$49))</f>
+        <f aca="false">$B14*W$45+$C14*W$46+$D14*W$47+$E14*W$48+$F14*W$49</f>
         <v>0.0390781742461804</v>
       </c>
       <c r="X59" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$14:$F$14,TRANSPOSE(X$45:X$49))</f>
+        <f aca="false">$B14*X$45+$C14*X$46+$D14*X$47+$E14*X$48+$F14*X$49</f>
         <v>0.0395890551686581</v>
       </c>
       <c r="Y59" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$14:$F$14,TRANSPOSE(Y$45:Y$49))</f>
+        <f aca="false">$B14*Y$45+$C14*Y$46+$D14*Y$47+$E14*Y$48+$F14*Y$49</f>
         <v>0.0400578330501428</v>
       </c>
       <c r="Z59" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$14:$F$14,TRANSPOSE(Z$45:Z$49))</f>
+        <f aca="false">$B14*Z$45+$C14*Z$46+$D14*Z$47+$E14*Z$48+$F14*Z$49</f>
         <v>0.0404771213288894</v>
       </c>
       <c r="AA59" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$14:$F$14,TRANSPOSE(AA$45:AA$49))</f>
+        <f aca="false">$B14*AA$45+$C14*AA$46+$D14*AA$47+$E14*AA$48+$F14*AA$49</f>
         <v>0.0408388011317055</v>
       </c>
       <c r="AB59" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$14:$F$14,TRANSPOSE(AB$45:AB$49))</f>
+        <f aca="false">$B14*AB$45+$C14*AB$46+$D14*AB$47+$E14*AB$48+$F14*AB$49</f>
         <v>0.0411342340973665</v>
       </c>
       <c r="AC59" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$14:$F$14,TRANSPOSE(AC$45:AC$49))</f>
+        <f aca="false">$B14*AC$45+$C14*AC$46+$D14*AC$47+$E14*AC$48+$F14*AC$49</f>
         <v>0.0413546336087698</v>
       </c>
       <c r="AD59" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$14:$F$14,TRANSPOSE(AD$45:AD$49))</f>
+        <f aca="false">$B14*AD$45+$C14*AD$46+$D14*AD$47+$E14*AD$48+$F14*AD$49</f>
         <v>0.0414916275293471</v>
       </c>
       <c r="AE59" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$14:$F$14,TRANSPOSE(AE$45:AE$49))</f>
+        <f aca="false">$B14*AE$45+$C14*AE$46+$D14*AE$47+$E14*AE$48+$F14*AE$49</f>
         <v>0.041538024216114</v>
       </c>
       <c r="AF59" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$14:$F$14,TRANSPOSE(AF$45:AF$49))</f>
+        <f aca="false">$B14*AF$45+$C14*AF$46+$D14*AF$47+$E14*AF$48+$F14*AF$49</f>
         <v>0.0414887483939034</v>
       </c>
       <c r="AG59" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$14:$F$14,TRANSPOSE(AG$45:AG$49))</f>
+        <f aca="false">$B14*AG$45+$C14*AG$46+$D14*AG$47+$E14*AG$48+$F14*AG$49</f>
         <v>0.0413418442817126</v>
       </c>
       <c r="AH59" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$14:$F$14,TRANSPOSE(AH$45:AH$49))</f>
+        <f aca="false">$B14*AH$45+$C14*AH$46+$D14*AH$47+$E14*AH$48+$F14*AH$49</f>
         <v>0.0410993675519153</v>
       </c>
       <c r="AI59" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$14:$F$14,TRANSPOSE(AI$45:AI$49))</f>
+        <f aca="false">$B14*AI$45+$C14*AI$46+$D14*AI$47+$E14*AI$48+$F14*AI$49</f>
         <v>0.0407679411314558</v>
       </c>
       <c r="AJ59" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$14:$F$14,TRANSPOSE(AJ$45:AJ$49))</f>
+        <f aca="false">$B14*AJ$45+$C14*AJ$46+$D14*AJ$47+$E14*AJ$48+$F14*AJ$49</f>
         <v>0.0403587707000196</v>
       </c>
       <c r="AK59" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$14:$F$14,TRANSPOSE(AK$45:AK$49))</f>
+        <f aca="false">$B14*AK$45+$C14*AK$46+$D14*AK$47+$E14*AK$48+$F14*AK$49</f>
         <v>0.0398870181099293</v>
       </c>
       <c r="AL59" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$14:$F$14,TRANSPOSE(AL$45:AL$49))</f>
+        <f aca="false">$B14*AL$45+$C14*AL$46+$D14*AL$47+$E14*AL$48+$F14*AL$49</f>
         <v>0.0393705884387936</v>
       </c>
       <c r="AM59" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$14:$F$14,TRANSPOSE(AM$45:AM$49))</f>
+        <f aca="false">$B14*AM$45+$C14*AM$46+$D14*AM$47+$E14*AM$48+$F14*AM$49</f>
         <v>0.0388285407642024</v>
       </c>
       <c r="AN59" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$14:$F$14,TRANSPOSE(AN$45:AN$49))</f>
+        <f aca="false">$B14*AN$45+$C14*AN$46+$D14*AN$47+$E14*AN$48+$F14*AN$49</f>
         <v>0.038279423660774</v>
       </c>
       <c r="AO59" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$14:$F$14,TRANSPOSE(AO$45:AO$49))</f>
+        <f aca="false">$B14*AO$45+$C14*AO$46+$D14*AO$47+$E14*AO$48+$F14*AO$49</f>
         <v>0.0377398325817727</v>
       </c>
       <c r="AP59" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$14:$F$14,TRANSPOSE(AP$45:AP$49))</f>
+        <f aca="false">$B14*AP$45+$C14*AP$46+$D14*AP$47+$E14*AP$48+$F14*AP$49</f>
         <v>0.0372233988078656</v>
       </c>
       <c r="AQ59" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$14:$F$14,TRANSPOSE(AQ$45:AQ$49))</f>
+        <f aca="false">$B14*AQ$45+$C14*AQ$46+$D14*AQ$47+$E14*AQ$48+$F14*AQ$49</f>
         <v>0.0367402912436832</v>
       </c>
       <c r="AR59" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$14:$F$14,TRANSPOSE(AR$45:AR$49))</f>
+        <f aca="false">$B14*AR$45+$C14*AR$46+$D14*AR$47+$E14*AR$48+$F14*AR$49</f>
         <v>0.0362971922734479</v>
       </c>
       <c r="AS59" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$14:$F$14,TRANSPOSE(AS$45:AS$49))</f>
+        <f aca="false">$B14*AS$45+$C14*AS$46+$D14*AS$47+$E14*AS$48+$F14*AS$49</f>
         <v>0.0358976304822583</v>
       </c>
     </row>
@@ -26397,147 +26397,147 @@
         <v>244</v>
       </c>
       <c r="J60" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$15:$F$15,TRANSPOSE(J$45:J$49))</f>
+        <f aca="false">$B15*J$45+$C15*J$46+$D15*J$47+$E15*J$48+$F15*J$49</f>
         <v>0.0342061954726559</v>
       </c>
       <c r="K60" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$15:$F$15,TRANSPOSE(K$45:K$49))</f>
+        <f aca="false">$B15*K$45+$C15*K$46+$D15*K$47+$E15*K$48+$F15*K$49</f>
         <v>0.0349742323757465</v>
       </c>
       <c r="L60" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$15:$F$15,TRANSPOSE(L$45:L$49))</f>
+        <f aca="false">$B15*L$45+$C15*L$46+$D15*L$47+$E15*L$48+$F15*L$49</f>
         <v>0.0357406061259603</v>
       </c>
       <c r="M60" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$15:$F$15,TRANSPOSE(M$45:M$49))</f>
+        <f aca="false">$B15*M$45+$C15*M$46+$D15*M$47+$E15*M$48+$F15*M$49</f>
         <v>0.0365039043802067</v>
       </c>
       <c r="N60" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$15:$F$15,TRANSPOSE(N$45:N$49))</f>
+        <f aca="false">$B15*N$45+$C15*N$46+$D15*N$47+$E15*N$48+$F15*N$49</f>
         <v>0.0372625805635316</v>
       </c>
       <c r="O60" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$15:$F$15,TRANSPOSE(O$45:O$49))</f>
+        <f aca="false">$B15*O$45+$C15*O$46+$D15*O$47+$E15*O$48+$F15*O$49</f>
         <v>0.0380149223680766</v>
       </c>
       <c r="P60" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$15:$F$15,TRANSPOSE(P$45:P$49))</f>
+        <f aca="false">$B15*P$45+$C15*P$46+$D15*P$47+$E15*P$48+$F15*P$49</f>
         <v>0.0387590118936258</v>
       </c>
       <c r="Q60" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$15:$F$15,TRANSPOSE(Q$45:Q$49))</f>
+        <f aca="false">$B15*Q$45+$C15*Q$46+$D15*Q$47+$E15*Q$48+$F15*Q$49</f>
         <v>0.0394926762089317</v>
       </c>
       <c r="R60" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$15:$F$15,TRANSPOSE(R$45:R$49))</f>
+        <f aca="false">$B15*R$45+$C15*R$46+$D15*R$47+$E15*R$48+$F15*R$49</f>
         <v>0.0402134273395958</v>
       </c>
       <c r="S60" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$15:$F$15,TRANSPOSE(S$45:S$49))</f>
+        <f aca="false">$B15*S$45+$C15*S$46+$D15*S$47+$E15*S$48+$F15*S$49</f>
         <v>0.0409183911855477</v>
       </c>
       <c r="T60" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$15:$F$15,TRANSPOSE(T$45:T$49))</f>
+        <f aca="false">$B15*T$45+$C15*T$46+$D15*T$47+$E15*T$48+$F15*T$49</f>
         <v>0.0416042257589834</v>
       </c>
       <c r="U60" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$15:$F$15,TRANSPOSE(U$45:U$49))</f>
+        <f aca="false">$B15*U$45+$C15*U$46+$D15*U$47+$E15*U$48+$F15*U$49</f>
         <v>0.0422670305504253</v>
       </c>
       <c r="V60" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$15:$F$15,TRANSPOSE(V$45:V$49))</f>
+        <f aca="false">$B15*V$45+$C15*V$46+$D15*V$47+$E15*V$48+$F15*V$49</f>
         <v>0.0429022509194891</v>
       </c>
       <c r="W60" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$15:$F$15,TRANSPOSE(W$45:W$49))</f>
+        <f aca="false">$B15*W$45+$C15*W$46+$D15*W$47+$E15*W$48+$F15*W$49</f>
         <v>0.0435045842986914</v>
       </c>
       <c r="X60" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$15:$F$15,TRANSPOSE(X$45:X$49))</f>
+        <f aca="false">$B15*X$45+$C15*X$46+$D15*X$47+$E15*X$48+$F15*X$49</f>
         <v>0.0440678988071534</v>
       </c>
       <c r="Y60" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$15:$F$15,TRANSPOSE(Y$45:Y$49))</f>
-        <v>0.0445851797281998</v>
+        <f aca="false">$B15*Y$45+$C15*Y$46+$D15*Y$47+$E15*Y$48+$F15*Y$49</f>
+        <v>0.0445851797281997</v>
       </c>
       <c r="Z60" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$15:$F$15,TRANSPOSE(Z$45:Z$49))</f>
+        <f aca="false">$B15*Z$45+$C15*Z$46+$D15*Z$47+$E15*Z$48+$F15*Z$49</f>
         <v>0.0450485254364602</v>
       </c>
       <c r="AA60" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$15:$F$15,TRANSPOSE(AA$45:AA$49))</f>
+        <f aca="false">$B15*AA$45+$C15*AA$46+$D15*AA$47+$E15*AA$48+$F15*AA$49</f>
         <v>0.0454492220834051</v>
       </c>
       <c r="AB60" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$15:$F$15,TRANSPOSE(AB$45:AB$49))</f>
+        <f aca="false">$B15*AB$45+$C15*AB$46+$D15*AB$47+$E15*AB$48+$F15*AB$49</f>
         <v>0.0457779356073937</v>
       </c>
       <c r="AC60" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$15:$F$15,TRANSPOSE(AC$45:AC$49))</f>
+        <f aca="false">$B15*AC$45+$C15*AC$46+$D15*AC$47+$E15*AC$48+$F15*AC$49</f>
         <v>0.0460250684695276</v>
       </c>
       <c r="AD60" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$15:$F$15,TRANSPOSE(AD$45:AD$49))</f>
+        <f aca="false">$B15*AD$45+$C15*AD$46+$D15*AD$47+$E15*AD$48+$F15*AD$49</f>
         <v>0.0461813304680811</v>
       </c>
       <c r="AE60" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$15:$F$15,TRANSPOSE(AE$45:AE$49))</f>
+        <f aca="false">$B15*AE$45+$C15*AE$46+$D15*AE$47+$E15*AE$48+$F15*AE$49</f>
         <v>0.0462385555169541</v>
       </c>
       <c r="AF60" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$15:$F$15,TRANSPOSE(AF$45:AF$49))</f>
+        <f aca="false">$B15*AF$45+$C15*AF$46+$D15*AF$47+$E15*AF$48+$F15*AF$49</f>
         <v>0.0461907450200777</v>
       </c>
       <c r="AG60" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$15:$F$15,TRANSPOSE(AG$45:AG$49))</f>
+        <f aca="false">$B15*AG$45+$C15*AG$46+$D15*AG$47+$E15*AG$48+$F15*AG$49</f>
         <v>0.046035230347113</v>
       </c>
       <c r="AH60" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$15:$F$15,TRANSPOSE(AH$45:AH$49))</f>
+        <f aca="false">$B15*AH$45+$C15*AH$46+$D15*AH$47+$E15*AH$48+$F15*AH$49</f>
         <v>0.0457737452194866</v>
       </c>
       <c r="AI60" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$15:$F$15,TRANSPOSE(AI$45:AI$49))</f>
+        <f aca="false">$B15*AI$45+$C15*AI$46+$D15*AI$47+$E15*AI$48+$F15*AI$49</f>
         <v>0.0454131332480931</v>
       </c>
       <c r="AJ60" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$15:$F$15,TRANSPOSE(AJ$45:AJ$49))</f>
+        <f aca="false">$B15*AJ$45+$C15*AJ$46+$D15*AJ$47+$E15*AJ$48+$F15*AJ$49</f>
         <v>0.0449654372131907</v>
       </c>
       <c r="AK60" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$15:$F$15,TRANSPOSE(AK$45:AK$49))</f>
+        <f aca="false">$B15*AK$45+$C15*AK$46+$D15*AK$47+$E15*AK$48+$F15*AK$49</f>
         <v>0.0444472406605949</v>
       </c>
       <c r="AL60" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$15:$F$15,TRANSPOSE(AL$45:AL$49))</f>
+        <f aca="false">$B15*AL$45+$C15*AL$46+$D15*AL$47+$E15*AL$48+$F15*AL$49</f>
         <v>0.0438783221810338</v>
       </c>
       <c r="AM60" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$15:$F$15,TRANSPOSE(AM$45:AM$49))</f>
+        <f aca="false">$B15*AM$45+$C15*AM$46+$D15*AM$47+$E15*AM$48+$F15*AM$49</f>
         <v>0.0432798654346001</v>
       </c>
       <c r="AN60" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$15:$F$15,TRANSPOSE(AN$45:AN$49))</f>
+        <f aca="false">$B15*AN$45+$C15*AN$46+$D15*AN$47+$E15*AN$48+$F15*AN$49</f>
         <v>0.0426725729777928</v>
       </c>
       <c r="AO60" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$15:$F$15,TRANSPOSE(AO$45:AO$49))</f>
+        <f aca="false">$B15*AO$45+$C15*AO$46+$D15*AO$47+$E15*AO$48+$F15*AO$49</f>
         <v>0.0420750258054823</v>
       </c>
       <c r="AP60" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$15:$F$15,TRANSPOSE(AP$45:AP$49))</f>
+        <f aca="false">$B15*AP$45+$C15*AP$46+$D15*AP$47+$E15*AP$48+$F15*AP$49</f>
         <v>0.0415025288311862</v>
       </c>
       <c r="AQ60" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$15:$F$15,TRANSPOSE(AQ$45:AQ$49))</f>
+        <f aca="false">$B15*AQ$45+$C15*AQ$46+$D15*AQ$47+$E15*AQ$48+$F15*AQ$49</f>
         <v>0.0409665354398335</v>
       </c>
       <c r="AR60" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$15:$F$15,TRANSPOSE(AR$45:AR$49))</f>
+        <f aca="false">$B15*AR$45+$C15*AR$46+$D15*AR$47+$E15*AR$48+$F15*AR$49</f>
         <v>0.0404746077577</v>
       </c>
       <c r="AS60" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$15:$F$15,TRANSPOSE(AS$45:AS$49))</f>
+        <f aca="false">$B15*AS$45+$C15*AS$46+$D15*AS$47+$E15*AS$48+$F15*AS$49</f>
         <v>0.0400307805966816</v>
       </c>
     </row>
@@ -26546,147 +26546,147 @@
         <v>245</v>
       </c>
       <c r="J61" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$16:$F$16,TRANSPOSE(J$45:J$49))</f>
+        <f aca="false">$B16*J$45+$C16*J$46+$D16*J$47+$E16*J$48+$F16*J$49</f>
         <v>0.0342061954726559</v>
       </c>
       <c r="K61" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$16:$F$16,TRANSPOSE(K$45:K$49))</f>
+        <f aca="false">$B16*K$45+$C16*K$46+$D16*K$47+$E16*K$48+$F16*K$49</f>
         <v>0.0349742323757465</v>
       </c>
       <c r="L61" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$16:$F$16,TRANSPOSE(L$45:L$49))</f>
+        <f aca="false">$B16*L$45+$C16*L$46+$D16*L$47+$E16*L$48+$F16*L$49</f>
         <v>0.0357406061259603</v>
       </c>
       <c r="M61" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$16:$F$16,TRANSPOSE(M$45:M$49))</f>
+        <f aca="false">$B16*M$45+$C16*M$46+$D16*M$47+$E16*M$48+$F16*M$49</f>
         <v>0.0365039043802067</v>
       </c>
       <c r="N61" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$16:$F$16,TRANSPOSE(N$45:N$49))</f>
+        <f aca="false">$B16*N$45+$C16*N$46+$D16*N$47+$E16*N$48+$F16*N$49</f>
         <v>0.0372625805635316</v>
       </c>
       <c r="O61" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$16:$F$16,TRANSPOSE(O$45:O$49))</f>
+        <f aca="false">$B16*O$45+$C16*O$46+$D16*O$47+$E16*O$48+$F16*O$49</f>
         <v>0.0380149223680766</v>
       </c>
       <c r="P61" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$16:$F$16,TRANSPOSE(P$45:P$49))</f>
+        <f aca="false">$B16*P$45+$C16*P$46+$D16*P$47+$E16*P$48+$F16*P$49</f>
         <v>0.0387590118936258</v>
       </c>
       <c r="Q61" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$16:$F$16,TRANSPOSE(Q$45:Q$49))</f>
+        <f aca="false">$B16*Q$45+$C16*Q$46+$D16*Q$47+$E16*Q$48+$F16*Q$49</f>
         <v>0.0394926762089317</v>
       </c>
       <c r="R61" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$16:$F$16,TRANSPOSE(R$45:R$49))</f>
+        <f aca="false">$B16*R$45+$C16*R$46+$D16*R$47+$E16*R$48+$F16*R$49</f>
         <v>0.0402134273395958</v>
       </c>
       <c r="S61" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$16:$F$16,TRANSPOSE(S$45:S$49))</f>
+        <f aca="false">$B16*S$45+$C16*S$46+$D16*S$47+$E16*S$48+$F16*S$49</f>
         <v>0.0409183911855477</v>
       </c>
       <c r="T61" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$16:$F$16,TRANSPOSE(T$45:T$49))</f>
+        <f aca="false">$B16*T$45+$C16*T$46+$D16*T$47+$E16*T$48+$F16*T$49</f>
         <v>0.0416042257589834</v>
       </c>
       <c r="U61" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$16:$F$16,TRANSPOSE(U$45:U$49))</f>
+        <f aca="false">$B16*U$45+$C16*U$46+$D16*U$47+$E16*U$48+$F16*U$49</f>
         <v>0.0422670305504253</v>
       </c>
       <c r="V61" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$16:$F$16,TRANSPOSE(V$45:V$49))</f>
+        <f aca="false">$B16*V$45+$C16*V$46+$D16*V$47+$E16*V$48+$F16*V$49</f>
         <v>0.0429022509194891</v>
       </c>
       <c r="W61" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$16:$F$16,TRANSPOSE(W$45:W$49))</f>
+        <f aca="false">$B16*W$45+$C16*W$46+$D16*W$47+$E16*W$48+$F16*W$49</f>
         <v>0.0435045842986914</v>
       </c>
       <c r="X61" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$16:$F$16,TRANSPOSE(X$45:X$49))</f>
+        <f aca="false">$B16*X$45+$C16*X$46+$D16*X$47+$E16*X$48+$F16*X$49</f>
         <v>0.0440678988071534</v>
       </c>
       <c r="Y61" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$16:$F$16,TRANSPOSE(Y$45:Y$49))</f>
-        <v>0.0445851797281998</v>
+        <f aca="false">$B16*Y$45+$C16*Y$46+$D16*Y$47+$E16*Y$48+$F16*Y$49</f>
+        <v>0.0445851797281997</v>
       </c>
       <c r="Z61" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$16:$F$16,TRANSPOSE(Z$45:Z$49))</f>
+        <f aca="false">$B16*Z$45+$C16*Z$46+$D16*Z$47+$E16*Z$48+$F16*Z$49</f>
         <v>0.0450485254364602</v>
       </c>
       <c r="AA61" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$16:$F$16,TRANSPOSE(AA$45:AA$49))</f>
+        <f aca="false">$B16*AA$45+$C16*AA$46+$D16*AA$47+$E16*AA$48+$F16*AA$49</f>
         <v>0.0454492220834051</v>
       </c>
       <c r="AB61" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$16:$F$16,TRANSPOSE(AB$45:AB$49))</f>
+        <f aca="false">$B16*AB$45+$C16*AB$46+$D16*AB$47+$E16*AB$48+$F16*AB$49</f>
         <v>0.0457779356073937</v>
       </c>
       <c r="AC61" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$16:$F$16,TRANSPOSE(AC$45:AC$49))</f>
+        <f aca="false">$B16*AC$45+$C16*AC$46+$D16*AC$47+$E16*AC$48+$F16*AC$49</f>
         <v>0.0460250684695276</v>
       </c>
       <c r="AD61" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$16:$F$16,TRANSPOSE(AD$45:AD$49))</f>
+        <f aca="false">$B16*AD$45+$C16*AD$46+$D16*AD$47+$E16*AD$48+$F16*AD$49</f>
         <v>0.0461813304680811</v>
       </c>
       <c r="AE61" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$16:$F$16,TRANSPOSE(AE$45:AE$49))</f>
+        <f aca="false">$B16*AE$45+$C16*AE$46+$D16*AE$47+$E16*AE$48+$F16*AE$49</f>
         <v>0.0462385555169541</v>
       </c>
       <c r="AF61" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$16:$F$16,TRANSPOSE(AF$45:AF$49))</f>
+        <f aca="false">$B16*AF$45+$C16*AF$46+$D16*AF$47+$E16*AF$48+$F16*AF$49</f>
         <v>0.0461907450200777</v>
       </c>
       <c r="AG61" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$16:$F$16,TRANSPOSE(AG$45:AG$49))</f>
+        <f aca="false">$B16*AG$45+$C16*AG$46+$D16*AG$47+$E16*AG$48+$F16*AG$49</f>
         <v>0.046035230347113</v>
       </c>
       <c r="AH61" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$16:$F$16,TRANSPOSE(AH$45:AH$49))</f>
+        <f aca="false">$B16*AH$45+$C16*AH$46+$D16*AH$47+$E16*AH$48+$F16*AH$49</f>
         <v>0.0457737452194866</v>
       </c>
       <c r="AI61" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$16:$F$16,TRANSPOSE(AI$45:AI$49))</f>
+        <f aca="false">$B16*AI$45+$C16*AI$46+$D16*AI$47+$E16*AI$48+$F16*AI$49</f>
         <v>0.0454131332480931</v>
       </c>
       <c r="AJ61" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$16:$F$16,TRANSPOSE(AJ$45:AJ$49))</f>
+        <f aca="false">$B16*AJ$45+$C16*AJ$46+$D16*AJ$47+$E16*AJ$48+$F16*AJ$49</f>
         <v>0.0449654372131907</v>
       </c>
       <c r="AK61" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$16:$F$16,TRANSPOSE(AK$45:AK$49))</f>
+        <f aca="false">$B16*AK$45+$C16*AK$46+$D16*AK$47+$E16*AK$48+$F16*AK$49</f>
         <v>0.0444472406605949</v>
       </c>
       <c r="AL61" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$16:$F$16,TRANSPOSE(AL$45:AL$49))</f>
+        <f aca="false">$B16*AL$45+$C16*AL$46+$D16*AL$47+$E16*AL$48+$F16*AL$49</f>
         <v>0.0438783221810338</v>
       </c>
       <c r="AM61" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$16:$F$16,TRANSPOSE(AM$45:AM$49))</f>
+        <f aca="false">$B16*AM$45+$C16*AM$46+$D16*AM$47+$E16*AM$48+$F16*AM$49</f>
         <v>0.0432798654346001</v>
       </c>
       <c r="AN61" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$16:$F$16,TRANSPOSE(AN$45:AN$49))</f>
+        <f aca="false">$B16*AN$45+$C16*AN$46+$D16*AN$47+$E16*AN$48+$F16*AN$49</f>
         <v>0.0426725729777928</v>
       </c>
       <c r="AO61" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$16:$F$16,TRANSPOSE(AO$45:AO$49))</f>
+        <f aca="false">$B16*AO$45+$C16*AO$46+$D16*AO$47+$E16*AO$48+$F16*AO$49</f>
         <v>0.0420750258054823</v>
       </c>
       <c r="AP61" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$16:$F$16,TRANSPOSE(AP$45:AP$49))</f>
+        <f aca="false">$B16*AP$45+$C16*AP$46+$D16*AP$47+$E16*AP$48+$F16*AP$49</f>
         <v>0.0415025288311862</v>
       </c>
       <c r="AQ61" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$16:$F$16,TRANSPOSE(AQ$45:AQ$49))</f>
+        <f aca="false">$B16*AQ$45+$C16*AQ$46+$D16*AQ$47+$E16*AQ$48+$F16*AQ$49</f>
         <v>0.0409665354398335</v>
       </c>
       <c r="AR61" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$16:$F$16,TRANSPOSE(AR$45:AR$49))</f>
+        <f aca="false">$B16*AR$45+$C16*AR$46+$D16*AR$47+$E16*AR$48+$F16*AR$49</f>
         <v>0.0404746077577</v>
       </c>
       <c r="AS61" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$16:$F$16,TRANSPOSE(AS$45:AS$49))</f>
+        <f aca="false">$B16*AS$45+$C16*AS$46+$D16*AS$47+$E16*AS$48+$F16*AS$49</f>
         <v>0.0400307805966816</v>
       </c>
     </row>
@@ -26695,147 +26695,147 @@
         <v>246</v>
       </c>
       <c r="J62" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$17:$F$17,TRANSPOSE(J$45:J$49))</f>
+        <f aca="false">$B17*J$45+$C17*J$46+$D17*J$47+$E17*J$48+$F17*J$49</f>
         <v>0.0342061954726559</v>
       </c>
       <c r="K62" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$17:$F$17,TRANSPOSE(K$45:K$49))</f>
+        <f aca="false">$B17*K$45+$C17*K$46+$D17*K$47+$E17*K$48+$F17*K$49</f>
         <v>0.0349742323757465</v>
       </c>
       <c r="L62" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$17:$F$17,TRANSPOSE(L$45:L$49))</f>
+        <f aca="false">$B17*L$45+$C17*L$46+$D17*L$47+$E17*L$48+$F17*L$49</f>
         <v>0.0357406061259603</v>
       </c>
       <c r="M62" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$17:$F$17,TRANSPOSE(M$45:M$49))</f>
+        <f aca="false">$B17*M$45+$C17*M$46+$D17*M$47+$E17*M$48+$F17*M$49</f>
         <v>0.0365039043802067</v>
       </c>
       <c r="N62" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$17:$F$17,TRANSPOSE(N$45:N$49))</f>
+        <f aca="false">$B17*N$45+$C17*N$46+$D17*N$47+$E17*N$48+$F17*N$49</f>
         <v>0.0372625805635316</v>
       </c>
       <c r="O62" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$17:$F$17,TRANSPOSE(O$45:O$49))</f>
+        <f aca="false">$B17*O$45+$C17*O$46+$D17*O$47+$E17*O$48+$F17*O$49</f>
         <v>0.0380149223680766</v>
       </c>
       <c r="P62" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$17:$F$17,TRANSPOSE(P$45:P$49))</f>
+        <f aca="false">$B17*P$45+$C17*P$46+$D17*P$47+$E17*P$48+$F17*P$49</f>
         <v>0.0387590118936258</v>
       </c>
       <c r="Q62" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$17:$F$17,TRANSPOSE(Q$45:Q$49))</f>
+        <f aca="false">$B17*Q$45+$C17*Q$46+$D17*Q$47+$E17*Q$48+$F17*Q$49</f>
         <v>0.0394926762089317</v>
       </c>
       <c r="R62" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$17:$F$17,TRANSPOSE(R$45:R$49))</f>
+        <f aca="false">$B17*R$45+$C17*R$46+$D17*R$47+$E17*R$48+$F17*R$49</f>
         <v>0.0402134273395958</v>
       </c>
       <c r="S62" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$17:$F$17,TRANSPOSE(S$45:S$49))</f>
+        <f aca="false">$B17*S$45+$C17*S$46+$D17*S$47+$E17*S$48+$F17*S$49</f>
         <v>0.0409183911855477</v>
       </c>
       <c r="T62" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$17:$F$17,TRANSPOSE(T$45:T$49))</f>
+        <f aca="false">$B17*T$45+$C17*T$46+$D17*T$47+$E17*T$48+$F17*T$49</f>
         <v>0.0416042257589834</v>
       </c>
       <c r="U62" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$17:$F$17,TRANSPOSE(U$45:U$49))</f>
+        <f aca="false">$B17*U$45+$C17*U$46+$D17*U$47+$E17*U$48+$F17*U$49</f>
         <v>0.0422670305504253</v>
       </c>
       <c r="V62" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$17:$F$17,TRANSPOSE(V$45:V$49))</f>
+        <f aca="false">$B17*V$45+$C17*V$46+$D17*V$47+$E17*V$48+$F17*V$49</f>
         <v>0.0429022509194891</v>
       </c>
       <c r="W62" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$17:$F$17,TRANSPOSE(W$45:W$49))</f>
+        <f aca="false">$B17*W$45+$C17*W$46+$D17*W$47+$E17*W$48+$F17*W$49</f>
         <v>0.0435045842986914</v>
       </c>
       <c r="X62" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$17:$F$17,TRANSPOSE(X$45:X$49))</f>
+        <f aca="false">$B17*X$45+$C17*X$46+$D17*X$47+$E17*X$48+$F17*X$49</f>
         <v>0.0440678988071534</v>
       </c>
       <c r="Y62" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$17:$F$17,TRANSPOSE(Y$45:Y$49))</f>
-        <v>0.0445851797281998</v>
+        <f aca="false">$B17*Y$45+$C17*Y$46+$D17*Y$47+$E17*Y$48+$F17*Y$49</f>
+        <v>0.0445851797281997</v>
       </c>
       <c r="Z62" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$17:$F$17,TRANSPOSE(Z$45:Z$49))</f>
+        <f aca="false">$B17*Z$45+$C17*Z$46+$D17*Z$47+$E17*Z$48+$F17*Z$49</f>
         <v>0.0450485254364602</v>
       </c>
       <c r="AA62" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$17:$F$17,TRANSPOSE(AA$45:AA$49))</f>
+        <f aca="false">$B17*AA$45+$C17*AA$46+$D17*AA$47+$E17*AA$48+$F17*AA$49</f>
         <v>0.0454492220834051</v>
       </c>
       <c r="AB62" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$17:$F$17,TRANSPOSE(AB$45:AB$49))</f>
+        <f aca="false">$B17*AB$45+$C17*AB$46+$D17*AB$47+$E17*AB$48+$F17*AB$49</f>
         <v>0.0457779356073937</v>
       </c>
       <c r="AC62" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$17:$F$17,TRANSPOSE(AC$45:AC$49))</f>
+        <f aca="false">$B17*AC$45+$C17*AC$46+$D17*AC$47+$E17*AC$48+$F17*AC$49</f>
         <v>0.0460250684695276</v>
       </c>
       <c r="AD62" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$17:$F$17,TRANSPOSE(AD$45:AD$49))</f>
+        <f aca="false">$B17*AD$45+$C17*AD$46+$D17*AD$47+$E17*AD$48+$F17*AD$49</f>
         <v>0.0461813304680811</v>
       </c>
       <c r="AE62" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$17:$F$17,TRANSPOSE(AE$45:AE$49))</f>
+        <f aca="false">$B17*AE$45+$C17*AE$46+$D17*AE$47+$E17*AE$48+$F17*AE$49</f>
         <v>0.0462385555169541</v>
       </c>
       <c r="AF62" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$17:$F$17,TRANSPOSE(AF$45:AF$49))</f>
+        <f aca="false">$B17*AF$45+$C17*AF$46+$D17*AF$47+$E17*AF$48+$F17*AF$49</f>
         <v>0.0461907450200777</v>
       </c>
       <c r="AG62" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$17:$F$17,TRANSPOSE(AG$45:AG$49))</f>
+        <f aca="false">$B17*AG$45+$C17*AG$46+$D17*AG$47+$E17*AG$48+$F17*AG$49</f>
         <v>0.046035230347113</v>
       </c>
       <c r="AH62" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$17:$F$17,TRANSPOSE(AH$45:AH$49))</f>
+        <f aca="false">$B17*AH$45+$C17*AH$46+$D17*AH$47+$E17*AH$48+$F17*AH$49</f>
         <v>0.0457737452194866</v>
       </c>
       <c r="AI62" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$17:$F$17,TRANSPOSE(AI$45:AI$49))</f>
+        <f aca="false">$B17*AI$45+$C17*AI$46+$D17*AI$47+$E17*AI$48+$F17*AI$49</f>
         <v>0.0454131332480931</v>
       </c>
       <c r="AJ62" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$17:$F$17,TRANSPOSE(AJ$45:AJ$49))</f>
+        <f aca="false">$B17*AJ$45+$C17*AJ$46+$D17*AJ$47+$E17*AJ$48+$F17*AJ$49</f>
         <v>0.0449654372131907</v>
       </c>
       <c r="AK62" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$17:$F$17,TRANSPOSE(AK$45:AK$49))</f>
+        <f aca="false">$B17*AK$45+$C17*AK$46+$D17*AK$47+$E17*AK$48+$F17*AK$49</f>
         <v>0.0444472406605949</v>
       </c>
       <c r="AL62" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$17:$F$17,TRANSPOSE(AL$45:AL$49))</f>
+        <f aca="false">$B17*AL$45+$C17*AL$46+$D17*AL$47+$E17*AL$48+$F17*AL$49</f>
         <v>0.0438783221810338</v>
       </c>
       <c r="AM62" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$17:$F$17,TRANSPOSE(AM$45:AM$49))</f>
+        <f aca="false">$B17*AM$45+$C17*AM$46+$D17*AM$47+$E17*AM$48+$F17*AM$49</f>
         <v>0.0432798654346001</v>
       </c>
       <c r="AN62" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$17:$F$17,TRANSPOSE(AN$45:AN$49))</f>
+        <f aca="false">$B17*AN$45+$C17*AN$46+$D17*AN$47+$E17*AN$48+$F17*AN$49</f>
         <v>0.0426725729777928</v>
       </c>
       <c r="AO62" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$17:$F$17,TRANSPOSE(AO$45:AO$49))</f>
+        <f aca="false">$B17*AO$45+$C17*AO$46+$D17*AO$47+$E17*AO$48+$F17*AO$49</f>
         <v>0.0420750258054823</v>
       </c>
       <c r="AP62" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$17:$F$17,TRANSPOSE(AP$45:AP$49))</f>
+        <f aca="false">$B17*AP$45+$C17*AP$46+$D17*AP$47+$E17*AP$48+$F17*AP$49</f>
         <v>0.0415025288311862</v>
       </c>
       <c r="AQ62" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$17:$F$17,TRANSPOSE(AQ$45:AQ$49))</f>
+        <f aca="false">$B17*AQ$45+$C17*AQ$46+$D17*AQ$47+$E17*AQ$48+$F17*AQ$49</f>
         <v>0.0409665354398335</v>
       </c>
       <c r="AR62" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$17:$F$17,TRANSPOSE(AR$45:AR$49))</f>
+        <f aca="false">$B17*AR$45+$C17*AR$46+$D17*AR$47+$E17*AR$48+$F17*AR$49</f>
         <v>0.0404746077577</v>
       </c>
       <c r="AS62" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$17:$F$17,TRANSPOSE(AS$45:AS$49))</f>
+        <f aca="false">$B17*AS$45+$C17*AS$46+$D17*AS$47+$E17*AS$48+$F17*AS$49</f>
         <v>0.0400307805966816</v>
       </c>
     </row>
@@ -26844,147 +26844,147 @@
         <v>247</v>
       </c>
       <c r="J63" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$18:$F$18,TRANSPOSE(J$45:J$49))</f>
+        <f aca="false">$B18*J$45+$C18*J$46+$D18*J$47+$E18*J$48+$F18*J$49</f>
         <v>0.0342061954726559</v>
       </c>
       <c r="K63" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$18:$F$18,TRANSPOSE(K$45:K$49))</f>
+        <f aca="false">$B18*K$45+$C18*K$46+$D18*K$47+$E18*K$48+$F18*K$49</f>
         <v>0.0349742323757465</v>
       </c>
       <c r="L63" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$18:$F$18,TRANSPOSE(L$45:L$49))</f>
+        <f aca="false">$B18*L$45+$C18*L$46+$D18*L$47+$E18*L$48+$F18*L$49</f>
         <v>0.0357406061259603</v>
       </c>
       <c r="M63" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$18:$F$18,TRANSPOSE(M$45:M$49))</f>
+        <f aca="false">$B18*M$45+$C18*M$46+$D18*M$47+$E18*M$48+$F18*M$49</f>
         <v>0.0365039043802067</v>
       </c>
       <c r="N63" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$18:$F$18,TRANSPOSE(N$45:N$49))</f>
+        <f aca="false">$B18*N$45+$C18*N$46+$D18*N$47+$E18*N$48+$F18*N$49</f>
         <v>0.0372625805635316</v>
       </c>
       <c r="O63" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$18:$F$18,TRANSPOSE(O$45:O$49))</f>
+        <f aca="false">$B18*O$45+$C18*O$46+$D18*O$47+$E18*O$48+$F18*O$49</f>
         <v>0.0380149223680766</v>
       </c>
       <c r="P63" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$18:$F$18,TRANSPOSE(P$45:P$49))</f>
+        <f aca="false">$B18*P$45+$C18*P$46+$D18*P$47+$E18*P$48+$F18*P$49</f>
         <v>0.0387590118936258</v>
       </c>
       <c r="Q63" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$18:$F$18,TRANSPOSE(Q$45:Q$49))</f>
+        <f aca="false">$B18*Q$45+$C18*Q$46+$D18*Q$47+$E18*Q$48+$F18*Q$49</f>
         <v>0.0394926762089317</v>
       </c>
       <c r="R63" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$18:$F$18,TRANSPOSE(R$45:R$49))</f>
+        <f aca="false">$B18*R$45+$C18*R$46+$D18*R$47+$E18*R$48+$F18*R$49</f>
         <v>0.0402134273395958</v>
       </c>
       <c r="S63" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$18:$F$18,TRANSPOSE(S$45:S$49))</f>
+        <f aca="false">$B18*S$45+$C18*S$46+$D18*S$47+$E18*S$48+$F18*S$49</f>
         <v>0.0409183911855477</v>
       </c>
       <c r="T63" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$18:$F$18,TRANSPOSE(T$45:T$49))</f>
+        <f aca="false">$B18*T$45+$C18*T$46+$D18*T$47+$E18*T$48+$F18*T$49</f>
         <v>0.0416042257589834</v>
       </c>
       <c r="U63" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$18:$F$18,TRANSPOSE(U$45:U$49))</f>
+        <f aca="false">$B18*U$45+$C18*U$46+$D18*U$47+$E18*U$48+$F18*U$49</f>
         <v>0.0422670305504253</v>
       </c>
       <c r="V63" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$18:$F$18,TRANSPOSE(V$45:V$49))</f>
+        <f aca="false">$B18*V$45+$C18*V$46+$D18*V$47+$E18*V$48+$F18*V$49</f>
         <v>0.0429022509194891</v>
       </c>
       <c r="W63" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$18:$F$18,TRANSPOSE(W$45:W$49))</f>
+        <f aca="false">$B18*W$45+$C18*W$46+$D18*W$47+$E18*W$48+$F18*W$49</f>
         <v>0.0435045842986914</v>
       </c>
       <c r="X63" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$18:$F$18,TRANSPOSE(X$45:X$49))</f>
+        <f aca="false">$B18*X$45+$C18*X$46+$D18*X$47+$E18*X$48+$F18*X$49</f>
         <v>0.0440678988071534</v>
       </c>
       <c r="Y63" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$18:$F$18,TRANSPOSE(Y$45:Y$49))</f>
-        <v>0.0445851797281998</v>
+        <f aca="false">$B18*Y$45+$C18*Y$46+$D18*Y$47+$E18*Y$48+$F18*Y$49</f>
+        <v>0.0445851797281997</v>
       </c>
       <c r="Z63" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$18:$F$18,TRANSPOSE(Z$45:Z$49))</f>
+        <f aca="false">$B18*Z$45+$C18*Z$46+$D18*Z$47+$E18*Z$48+$F18*Z$49</f>
         <v>0.0450485254364602</v>
       </c>
       <c r="AA63" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$18:$F$18,TRANSPOSE(AA$45:AA$49))</f>
+        <f aca="false">$B18*AA$45+$C18*AA$46+$D18*AA$47+$E18*AA$48+$F18*AA$49</f>
         <v>0.0454492220834051</v>
       </c>
       <c r="AB63" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$18:$F$18,TRANSPOSE(AB$45:AB$49))</f>
+        <f aca="false">$B18*AB$45+$C18*AB$46+$D18*AB$47+$E18*AB$48+$F18*AB$49</f>
         <v>0.0457779356073937</v>
       </c>
       <c r="AC63" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$18:$F$18,TRANSPOSE(AC$45:AC$49))</f>
+        <f aca="false">$B18*AC$45+$C18*AC$46+$D18*AC$47+$E18*AC$48+$F18*AC$49</f>
         <v>0.0460250684695276</v>
       </c>
       <c r="AD63" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$18:$F$18,TRANSPOSE(AD$45:AD$49))</f>
+        <f aca="false">$B18*AD$45+$C18*AD$46+$D18*AD$47+$E18*AD$48+$F18*AD$49</f>
         <v>0.0461813304680811</v>
       </c>
       <c r="AE63" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$18:$F$18,TRANSPOSE(AE$45:AE$49))</f>
+        <f aca="false">$B18*AE$45+$C18*AE$46+$D18*AE$47+$E18*AE$48+$F18*AE$49</f>
         <v>0.0462385555169541</v>
       </c>
       <c r="AF63" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$18:$F$18,TRANSPOSE(AF$45:AF$49))</f>
+        <f aca="false">$B18*AF$45+$C18*AF$46+$D18*AF$47+$E18*AF$48+$F18*AF$49</f>
         <v>0.0461907450200777</v>
       </c>
       <c r="AG63" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$18:$F$18,TRANSPOSE(AG$45:AG$49))</f>
+        <f aca="false">$B18*AG$45+$C18*AG$46+$D18*AG$47+$E18*AG$48+$F18*AG$49</f>
         <v>0.046035230347113</v>
       </c>
       <c r="AH63" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$18:$F$18,TRANSPOSE(AH$45:AH$49))</f>
+        <f aca="false">$B18*AH$45+$C18*AH$46+$D18*AH$47+$E18*AH$48+$F18*AH$49</f>
         <v>0.0457737452194866</v>
       </c>
       <c r="AI63" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$18:$F$18,TRANSPOSE(AI$45:AI$49))</f>
+        <f aca="false">$B18*AI$45+$C18*AI$46+$D18*AI$47+$E18*AI$48+$F18*AI$49</f>
         <v>0.0454131332480931</v>
       </c>
       <c r="AJ63" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$18:$F$18,TRANSPOSE(AJ$45:AJ$49))</f>
+        <f aca="false">$B18*AJ$45+$C18*AJ$46+$D18*AJ$47+$E18*AJ$48+$F18*AJ$49</f>
         <v>0.0449654372131907</v>
       </c>
       <c r="AK63" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$18:$F$18,TRANSPOSE(AK$45:AK$49))</f>
+        <f aca="false">$B18*AK$45+$C18*AK$46+$D18*AK$47+$E18*AK$48+$F18*AK$49</f>
         <v>0.0444472406605949</v>
       </c>
       <c r="AL63" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$18:$F$18,TRANSPOSE(AL$45:AL$49))</f>
+        <f aca="false">$B18*AL$45+$C18*AL$46+$D18*AL$47+$E18*AL$48+$F18*AL$49</f>
         <v>0.0438783221810338</v>
       </c>
       <c r="AM63" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$18:$F$18,TRANSPOSE(AM$45:AM$49))</f>
+        <f aca="false">$B18*AM$45+$C18*AM$46+$D18*AM$47+$E18*AM$48+$F18*AM$49</f>
         <v>0.0432798654346001</v>
       </c>
       <c r="AN63" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$18:$F$18,TRANSPOSE(AN$45:AN$49))</f>
+        <f aca="false">$B18*AN$45+$C18*AN$46+$D18*AN$47+$E18*AN$48+$F18*AN$49</f>
         <v>0.0426725729777928</v>
       </c>
       <c r="AO63" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$18:$F$18,TRANSPOSE(AO$45:AO$49))</f>
+        <f aca="false">$B18*AO$45+$C18*AO$46+$D18*AO$47+$E18*AO$48+$F18*AO$49</f>
         <v>0.0420750258054823</v>
       </c>
       <c r="AP63" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$18:$F$18,TRANSPOSE(AP$45:AP$49))</f>
+        <f aca="false">$B18*AP$45+$C18*AP$46+$D18*AP$47+$E18*AP$48+$F18*AP$49</f>
         <v>0.0415025288311862</v>
       </c>
       <c r="AQ63" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$18:$F$18,TRANSPOSE(AQ$45:AQ$49))</f>
+        <f aca="false">$B18*AQ$45+$C18*AQ$46+$D18*AQ$47+$E18*AQ$48+$F18*AQ$49</f>
         <v>0.0409665354398335</v>
       </c>
       <c r="AR63" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$18:$F$18,TRANSPOSE(AR$45:AR$49))</f>
+        <f aca="false">$B18*AR$45+$C18*AR$46+$D18*AR$47+$E18*AR$48+$F18*AR$49</f>
         <v>0.0404746077577</v>
       </c>
       <c r="AS63" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$18:$F$18,TRANSPOSE(AS$45:AS$49))</f>
+        <f aca="false">$B18*AS$45+$C18*AS$46+$D18*AS$47+$E18*AS$48+$F18*AS$49</f>
         <v>0.0400307805966816</v>
       </c>
     </row>
@@ -26993,147 +26993,147 @@
         <v>248</v>
       </c>
       <c r="J64" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$19:$F$19,TRANSPOSE(J$45:J$49))</f>
+        <f aca="false">$B19*J$45+$C19*J$46+$D19*J$47+$E19*J$48+$F19*J$49</f>
         <v>0.0306630866944912</v>
       </c>
       <c r="K64" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$19:$F$19,TRANSPOSE(K$45:K$49))</f>
+        <f aca="false">$B19*K$45+$C19*K$46+$D19*K$47+$E19*K$48+$F19*K$49</f>
         <v>0.0313562281860301</v>
       </c>
       <c r="L64" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$19:$F$19,TRANSPOSE(L$45:L$49))</f>
+        <f aca="false">$B19*L$45+$C19*L$46+$D19*L$47+$E19*L$48+$F19*L$49</f>
         <v>0.0320481895577625</v>
       </c>
       <c r="M64" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$19:$F$19,TRANSPOSE(M$45:M$49))</f>
+        <f aca="false">$B19*M$45+$C19*M$46+$D19*M$47+$E19*M$48+$F19*M$49</f>
         <v>0.0327377070069906</v>
       </c>
       <c r="N64" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$19:$F$19,TRANSPOSE(N$45:N$49))</f>
+        <f aca="false">$B19*N$45+$C19*N$46+$D19*N$47+$E19*N$48+$F19*N$49</f>
         <v>0.0334233927319238</v>
       </c>
       <c r="O64" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$19:$F$19,TRANSPOSE(O$45:O$49))</f>
+        <f aca="false">$B19*O$45+$C19*O$46+$D19*O$47+$E19*O$48+$F19*O$49</f>
         <v>0.0341037052571554</v>
       </c>
       <c r="P64" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$19:$F$19,TRANSPOSE(P$45:P$49))</f>
+        <f aca="false">$B19*P$45+$C19*P$46+$D19*P$47+$E19*P$48+$F19*P$49</f>
         <v>0.0347769117450992</v>
       </c>
       <c r="Q64" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$19:$F$19,TRANSPOSE(Q$45:Q$49))</f>
+        <f aca="false">$B19*Q$45+$C19*Q$46+$D19*Q$47+$E19*Q$48+$F19*Q$49</f>
         <v>0.0354410410475111</v>
       </c>
       <c r="R64" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$19:$F$19,TRANSPOSE(R$45:R$49))</f>
+        <f aca="false">$B19*R$45+$C19*R$46+$D19*R$47+$E19*R$48+$F19*R$49</f>
         <v>0.036093826443454</v>
       </c>
       <c r="S64" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$19:$F$19,TRANSPOSE(S$45:S$49))</f>
+        <f aca="false">$B19*S$45+$C19*S$46+$D19*S$47+$E19*S$48+$F19*S$49</f>
         <v>0.0367326374760029</v>
       </c>
       <c r="T64" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$19:$F$19,TRANSPOSE(T$45:T$49))</f>
+        <f aca="false">$B19*T$45+$C19*T$46+$D19*T$47+$E19*T$48+$F19*T$49</f>
         <v>0.0373544011793205</v>
       </c>
       <c r="U64" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$19:$F$19,TRANSPOSE(U$45:U$49))</f>
+        <f aca="false">$B19*U$45+$C19*U$46+$D19*U$47+$E19*U$48+$F19*U$49</f>
         <v>0.0379555144546129</v>
       </c>
       <c r="V64" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$19:$F$19,TRANSPOSE(V$45:V$49))</f>
+        <f aca="false">$B19*V$45+$C19*V$46+$D19*V$47+$E19*V$48+$F19*V$49</f>
         <v>0.0385317516034342</v>
       </c>
       <c r="W64" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$19:$F$19,TRANSPOSE(W$45:W$49))</f>
+        <f aca="false">$B19*W$45+$C19*W$46+$D19*W$47+$E19*W$48+$F19*W$49</f>
         <v>0.0390781742461804</v>
       </c>
       <c r="X64" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$19:$F$19,TRANSPOSE(X$45:X$49))</f>
+        <f aca="false">$B19*X$45+$C19*X$46+$D19*X$47+$E19*X$48+$F19*X$49</f>
         <v>0.0395890551686581</v>
       </c>
       <c r="Y64" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$19:$F$19,TRANSPOSE(Y$45:Y$49))</f>
+        <f aca="false">$B19*Y$45+$C19*Y$46+$D19*Y$47+$E19*Y$48+$F19*Y$49</f>
         <v>0.0400578330501428</v>
       </c>
       <c r="Z64" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$19:$F$19,TRANSPOSE(Z$45:Z$49))</f>
+        <f aca="false">$B19*Z$45+$C19*Z$46+$D19*Z$47+$E19*Z$48+$F19*Z$49</f>
         <v>0.0404771213288894</v>
       </c>
       <c r="AA64" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$19:$F$19,TRANSPOSE(AA$45:AA$49))</f>
+        <f aca="false">$B19*AA$45+$C19*AA$46+$D19*AA$47+$E19*AA$48+$F19*AA$49</f>
         <v>0.0408388011317055</v>
       </c>
       <c r="AB64" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$19:$F$19,TRANSPOSE(AB$45:AB$49))</f>
+        <f aca="false">$B19*AB$45+$C19*AB$46+$D19*AB$47+$E19*AB$48+$F19*AB$49</f>
         <v>0.0411342340973665</v>
       </c>
       <c r="AC64" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$19:$F$19,TRANSPOSE(AC$45:AC$49))</f>
+        <f aca="false">$B19*AC$45+$C19*AC$46+$D19*AC$47+$E19*AC$48+$F19*AC$49</f>
         <v>0.0413546336087698</v>
       </c>
       <c r="AD64" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$19:$F$19,TRANSPOSE(AD$45:AD$49))</f>
+        <f aca="false">$B19*AD$45+$C19*AD$46+$D19*AD$47+$E19*AD$48+$F19*AD$49</f>
         <v>0.0414916275293471</v>
       </c>
       <c r="AE64" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$19:$F$19,TRANSPOSE(AE$45:AE$49))</f>
+        <f aca="false">$B19*AE$45+$C19*AE$46+$D19*AE$47+$E19*AE$48+$F19*AE$49</f>
         <v>0.041538024216114</v>
       </c>
       <c r="AF64" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$19:$F$19,TRANSPOSE(AF$45:AF$49))</f>
+        <f aca="false">$B19*AF$45+$C19*AF$46+$D19*AF$47+$E19*AF$48+$F19*AF$49</f>
         <v>0.0414887483939034</v>
       </c>
       <c r="AG64" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$19:$F$19,TRANSPOSE(AG$45:AG$49))</f>
+        <f aca="false">$B19*AG$45+$C19*AG$46+$D19*AG$47+$E19*AG$48+$F19*AG$49</f>
         <v>0.0413418442817126</v>
       </c>
       <c r="AH64" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$19:$F$19,TRANSPOSE(AH$45:AH$49))</f>
+        <f aca="false">$B19*AH$45+$C19*AH$46+$D19*AH$47+$E19*AH$48+$F19*AH$49</f>
         <v>0.0410993675519153</v>
       </c>
       <c r="AI64" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$19:$F$19,TRANSPOSE(AI$45:AI$49))</f>
+        <f aca="false">$B19*AI$45+$C19*AI$46+$D19*AI$47+$E19*AI$48+$F19*AI$49</f>
         <v>0.0407679411314558</v>
       </c>
       <c r="AJ64" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$19:$F$19,TRANSPOSE(AJ$45:AJ$49))</f>
+        <f aca="false">$B19*AJ$45+$C19*AJ$46+$D19*AJ$47+$E19*AJ$48+$F19*AJ$49</f>
         <v>0.0403587707000196</v>
       </c>
       <c r="AK64" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$19:$F$19,TRANSPOSE(AK$45:AK$49))</f>
+        <f aca="false">$B19*AK$45+$C19*AK$46+$D19*AK$47+$E19*AK$48+$F19*AK$49</f>
         <v>0.0398870181099293</v>
       </c>
       <c r="AL64" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$19:$F$19,TRANSPOSE(AL$45:AL$49))</f>
+        <f aca="false">$B19*AL$45+$C19*AL$46+$D19*AL$47+$E19*AL$48+$F19*AL$49</f>
         <v>0.0393705884387936</v>
       </c>
       <c r="AM64" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$19:$F$19,TRANSPOSE(AM$45:AM$49))</f>
+        <f aca="false">$B19*AM$45+$C19*AM$46+$D19*AM$47+$E19*AM$48+$F19*AM$49</f>
         <v>0.0388285407642024</v>
       </c>
       <c r="AN64" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$19:$F$19,TRANSPOSE(AN$45:AN$49))</f>
+        <f aca="false">$B19*AN$45+$C19*AN$46+$D19*AN$47+$E19*AN$48+$F19*AN$49</f>
         <v>0.038279423660774</v>
       </c>
       <c r="AO64" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$19:$F$19,TRANSPOSE(AO$45:AO$49))</f>
+        <f aca="false">$B19*AO$45+$C19*AO$46+$D19*AO$47+$E19*AO$48+$F19*AO$49</f>
         <v>0.0377398325817727</v>
       </c>
       <c r="AP64" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$19:$F$19,TRANSPOSE(AP$45:AP$49))</f>
+        <f aca="false">$B19*AP$45+$C19*AP$46+$D19*AP$47+$E19*AP$48+$F19*AP$49</f>
         <v>0.0372233988078656</v>
       </c>
       <c r="AQ64" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$19:$F$19,TRANSPOSE(AQ$45:AQ$49))</f>
+        <f aca="false">$B19*AQ$45+$C19*AQ$46+$D19*AQ$47+$E19*AQ$48+$F19*AQ$49</f>
         <v>0.0367402912436832</v>
       </c>
       <c r="AR64" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$19:$F$19,TRANSPOSE(AR$45:AR$49))</f>
+        <f aca="false">$B19*AR$45+$C19*AR$46+$D19*AR$47+$E19*AR$48+$F19*AR$49</f>
         <v>0.0362971922734479</v>
       </c>
       <c r="AS64" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$19:$F$19,TRANSPOSE(AS$45:AS$49))</f>
+        <f aca="false">$B19*AS$45+$C19*AS$46+$D19*AS$47+$E19*AS$48+$F19*AS$49</f>
         <v>0.0358976304822583</v>
       </c>
     </row>
@@ -27142,147 +27142,147 @@
         <v>249</v>
       </c>
       <c r="J65" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$20:$F$20,TRANSPOSE(J$45:J$49))</f>
+        <f aca="false">$B20*J$45+$C20*J$46+$D20*J$47+$E20*J$48+$F20*J$49</f>
         <v>0.0200337603599969</v>
       </c>
       <c r="K65" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$20:$F$20,TRANSPOSE(K$45:K$49))</f>
+        <f aca="false">$B20*K$45+$C20*K$46+$D20*K$47+$E20*K$48+$F20*K$49</f>
         <v>0.0205022156168808</v>
       </c>
       <c r="L65" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$20:$F$20,TRANSPOSE(L$45:L$49))</f>
+        <f aca="false">$B20*L$45+$C20*L$46+$D20*L$47+$E20*L$48+$F20*L$49</f>
         <v>0.0209709398531693</v>
       </c>
       <c r="M65" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$20:$F$20,TRANSPOSE(M$45:M$49))</f>
+        <f aca="false">$B20*M$45+$C20*M$46+$D20*M$47+$E20*M$48+$F20*M$49</f>
         <v>0.0214391148873424</v>
       </c>
       <c r="N65" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$20:$F$20,TRANSPOSE(N$45:N$49))</f>
+        <f aca="false">$B20*N$45+$C20*N$46+$D20*N$47+$E20*N$48+$F20*N$49</f>
         <v>0.0219058292371005</v>
       </c>
       <c r="O65" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$20:$F$20,TRANSPOSE(O$45:O$49))</f>
+        <f aca="false">$B20*O$45+$C20*O$46+$D20*O$47+$E20*O$48+$F20*O$49</f>
         <v>0.0223700539243917</v>
       </c>
       <c r="P65" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$20:$F$20,TRANSPOSE(P$45:P$49))</f>
+        <f aca="false">$B20*P$45+$C20*P$46+$D20*P$47+$E20*P$48+$F20*P$49</f>
         <v>0.0228306112995195</v>
       </c>
       <c r="Q65" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$20:$F$20,TRANSPOSE(Q$45:Q$49))</f>
+        <f aca="false">$B20*Q$45+$C20*Q$46+$D20*Q$47+$E20*Q$48+$F20*Q$49</f>
         <v>0.0232861355632492</v>
       </c>
       <c r="R65" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$20:$F$20,TRANSPOSE(R$45:R$49))</f>
+        <f aca="false">$B20*R$45+$C20*R$46+$D20*R$47+$E20*R$48+$F20*R$49</f>
         <v>0.0237350237550287</v>
       </c>
       <c r="S65" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$20:$F$20,TRANSPOSE(S$45:S$49))</f>
+        <f aca="false">$B20*S$45+$C20*S$46+$D20*S$47+$E20*S$48+$F20*S$49</f>
         <v>0.0241753763473686</v>
       </c>
       <c r="T65" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$20:$F$20,TRANSPOSE(T$45:T$49))</f>
+        <f aca="false">$B20*T$45+$C20*T$46+$D20*T$47+$E20*T$48+$F20*T$49</f>
         <v>0.0246049274403319</v>
       </c>
       <c r="U65" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$20:$F$20,TRANSPOSE(U$45:U$49))</f>
+        <f aca="false">$B20*U$45+$C20*U$46+$D20*U$47+$E20*U$48+$F20*U$49</f>
         <v>0.0250209661671757</v>
       </c>
       <c r="V65" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$20:$F$20,TRANSPOSE(V$45:V$49))</f>
+        <f aca="false">$B20*V$45+$C20*V$46+$D20*V$47+$E20*V$48+$F20*V$49</f>
         <v>0.0254202536552693</v>
       </c>
       <c r="W65" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$20:$F$20,TRANSPOSE(W$45:W$49))</f>
+        <f aca="false">$B20*W$45+$C20*W$46+$D20*W$47+$E20*W$48+$F20*W$49</f>
         <v>0.0257989440886475</v>
       </c>
       <c r="X65" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$20:$F$20,TRANSPOSE(X$45:X$49))</f>
+        <f aca="false">$B20*X$45+$C20*X$46+$D20*X$47+$E20*X$48+$F20*X$49</f>
         <v>0.0261525242531723</v>
       </c>
       <c r="Y65" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$20:$F$20,TRANSPOSE(Y$45:Y$49))</f>
+        <f aca="false">$B20*Y$45+$C20*Y$46+$D20*Y$47+$E20*Y$48+$F20*Y$49</f>
         <v>0.0264757930159719</v>
       </c>
       <c r="Z65" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$20:$F$20,TRANSPOSE(Z$45:Z$49))</f>
+        <f aca="false">$B20*Z$45+$C20*Z$46+$D20*Z$47+$E20*Z$48+$F20*Z$49</f>
         <v>0.0267629090061769</v>
       </c>
       <c r="AA65" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$20:$F$20,TRANSPOSE(AA$45:AA$49))</f>
+        <f aca="false">$B20*AA$45+$C20*AA$46+$D20*AA$47+$E20*AA$48+$F20*AA$49</f>
         <v>0.0270075382766069</v>
       </c>
       <c r="AB65" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$20:$F$20,TRANSPOSE(AB$45:AB$49))</f>
+        <f aca="false">$B20*AB$45+$C20*AB$46+$D20*AB$47+$E20*AB$48+$F20*AB$49</f>
         <v>0.0272031295672848</v>
       </c>
       <c r="AC65" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$20:$F$20,TRANSPOSE(AC$45:AC$49))</f>
+        <f aca="false">$B20*AC$45+$C20*AC$46+$D20*AC$47+$E20*AC$48+$F20*AC$49</f>
         <v>0.0273433290264963</v>
       </c>
       <c r="AD65" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$20:$F$20,TRANSPOSE(AD$45:AD$49))</f>
+        <f aca="false">$B20*AD$45+$C20*AD$46+$D20*AD$47+$E20*AD$48+$F20*AD$49</f>
         <v>0.0274225187131451</v>
       </c>
       <c r="AE65" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$20:$F$20,TRANSPOSE(AE$45:AE$49))</f>
+        <f aca="false">$B20*AE$45+$C20*AE$46+$D20*AE$47+$E20*AE$48+$F20*AE$49</f>
         <v>0.0274364303135935</v>
       </c>
       <c r="AF65" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$20:$F$20,TRANSPOSE(AF$45:AF$49))</f>
+        <f aca="false">$B20*AF$45+$C20*AF$46+$D20*AF$47+$E20*AF$48+$F20*AF$49</f>
         <v>0.0273827585153805</v>
       </c>
       <c r="AG65" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$20:$F$20,TRANSPOSE(AG$45:AG$49))</f>
+        <f aca="false">$B20*AG$45+$C20*AG$46+$D20*AG$47+$E20*AG$48+$F20*AG$49</f>
         <v>0.0272616860855115</v>
       </c>
       <c r="AH65" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$20:$F$20,TRANSPOSE(AH$45:AH$49))</f>
+        <f aca="false">$B20*AH$45+$C20*AH$46+$D20*AH$47+$E20*AH$48+$F20*AH$49</f>
         <v>0.0270762345492014</v>
       </c>
       <c r="AI65" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$20:$F$20,TRANSPOSE(AI$45:AI$49))</f>
+        <f aca="false">$B20*AI$45+$C20*AI$46+$D20*AI$47+$E20*AI$48+$F20*AI$49</f>
         <v>0.0268323647815438</v>
       </c>
       <c r="AJ65" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$20:$F$20,TRANSPOSE(AJ$45:AJ$49))</f>
+        <f aca="false">$B20*AJ$45+$C20*AJ$46+$D20*AJ$47+$E20*AJ$48+$F20*AJ$49</f>
         <v>0.0265387711605064</v>
       </c>
       <c r="AK65" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$20:$F$20,TRANSPOSE(AK$45:AK$49))</f>
+        <f aca="false">$B20*AK$45+$C20*AK$46+$D20*AK$47+$E20*AK$48+$F20*AK$49</f>
         <v>0.0262063504579326</v>
       </c>
       <c r="AL65" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$20:$F$20,TRANSPOSE(AL$45:AL$49))</f>
+        <f aca="false">$B20*AL$45+$C20*AL$46+$D20*AL$47+$E20*AL$48+$F20*AL$49</f>
         <v>0.0258473872120732</v>
       </c>
       <c r="AM65" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$20:$F$20,TRANSPOSE(AM$45:AM$49))</f>
+        <f aca="false">$B20*AM$45+$C20*AM$46+$D20*AM$47+$E20*AM$48+$F20*AM$49</f>
         <v>0.0254745667530096</v>
       </c>
       <c r="AN65" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$20:$F$20,TRANSPOSE(AN$45:AN$49))</f>
+        <f aca="false">$B20*AN$45+$C20*AN$46+$D20*AN$47+$E20*AN$48+$F20*AN$49</f>
         <v>0.0250999757097178</v>
       </c>
       <c r="AO65" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$20:$F$20,TRANSPOSE(AO$45:AO$49))</f>
+        <f aca="false">$B20*AO$45+$C20*AO$46+$D20*AO$47+$E20*AO$48+$F20*AO$49</f>
         <v>0.0247342529106441</v>
       </c>
       <c r="AP65" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$20:$F$20,TRANSPOSE(AP$45:AP$49))</f>
+        <f aca="false">$B20*AP$45+$C20*AP$46+$D20*AP$47+$E20*AP$48+$F20*AP$49</f>
         <v>0.0243860087379037</v>
       </c>
       <c r="AQ65" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$20:$F$20,TRANSPOSE(AQ$45:AQ$49))</f>
+        <f aca="false">$B20*AQ$45+$C20*AQ$46+$D20*AQ$47+$E20*AQ$48+$F20*AQ$49</f>
         <v>0.0240615586552323</v>
       </c>
       <c r="AR65" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$20:$F$20,TRANSPOSE(AR$45:AR$49))</f>
+        <f aca="false">$B20*AR$45+$C20*AR$46+$D20*AR$47+$E20*AR$48+$F20*AR$49</f>
         <v>0.0237649458206917</v>
       </c>
       <c r="AS65" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$20:$F$20,TRANSPOSE(AS$45:AS$49))</f>
+        <f aca="false">$B20*AS$45+$C20*AS$46+$D20*AS$47+$E20*AS$48+$F20*AS$49</f>
         <v>0.0234981801389885</v>
       </c>
     </row>
@@ -27291,147 +27291,147 @@
         <v>250</v>
       </c>
       <c r="J66" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$21:$F$21,TRANSPOSE(J$45:J$49))</f>
+        <f aca="false">$B21*J$45+$C21*J$46+$D21*J$47+$E21*J$48+$F21*J$49</f>
         <v>0.0147190971927498</v>
       </c>
       <c r="K66" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$21:$F$21,TRANSPOSE(K$45:K$49))</f>
+        <f aca="false">$B21*K$45+$C21*K$46+$D21*K$47+$E21*K$48+$F21*K$49</f>
         <v>0.0150752093323061</v>
       </c>
       <c r="L66" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$21:$F$21,TRANSPOSE(L$45:L$49))</f>
+        <f aca="false">$B21*L$45+$C21*L$46+$D21*L$47+$E21*L$48+$F21*L$49</f>
         <v>0.0154323150008726</v>
       </c>
       <c r="M66" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$21:$F$21,TRANSPOSE(M$45:M$49))</f>
+        <f aca="false">$B21*M$45+$C21*M$46+$D21*M$47+$E21*M$48+$F21*M$49</f>
         <v>0.0157898188275183</v>
       </c>
       <c r="N66" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$21:$F$21,TRANSPOSE(N$45:N$49))</f>
+        <f aca="false">$B21*N$45+$C21*N$46+$D21*N$47+$E21*N$48+$F21*N$49</f>
         <v>0.0161470474896889</v>
       </c>
       <c r="O66" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$21:$F$21,TRANSPOSE(O$45:O$49))</f>
+        <f aca="false">$B21*O$45+$C21*O$46+$D21*O$47+$E21*O$48+$F21*O$49</f>
         <v>0.0165032282580099</v>
       </c>
       <c r="P66" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$21:$F$21,TRANSPOSE(P$45:P$49))</f>
+        <f aca="false">$B21*P$45+$C21*P$46+$D21*P$47+$E21*P$48+$F21*P$49</f>
         <v>0.0168574610767297</v>
       </c>
       <c r="Q66" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$21:$F$21,TRANSPOSE(Q$45:Q$49))</f>
+        <f aca="false">$B21*Q$45+$C21*Q$46+$D21*Q$47+$E21*Q$48+$F21*Q$49</f>
         <v>0.0172086828211183</v>
       </c>
       <c r="R66" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$21:$F$21,TRANSPOSE(R$45:R$49))</f>
+        <f aca="false">$B21*R$45+$C21*R$46+$D21*R$47+$E21*R$48+$F21*R$49</f>
         <v>0.017555622410816</v>
       </c>
       <c r="S66" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$21:$F$21,TRANSPOSE(S$45:S$49))</f>
+        <f aca="false">$B21*S$45+$C21*S$46+$D21*S$47+$E21*S$48+$F21*S$49</f>
         <v>0.0178967457830514</v>
       </c>
       <c r="T66" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$21:$F$21,TRANSPOSE(T$45:T$49))</f>
+        <f aca="false">$B21*T$45+$C21*T$46+$D21*T$47+$E21*T$48+$F21*T$49</f>
         <v>0.0182301905708375</v>
       </c>
       <c r="U66" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$21:$F$21,TRANSPOSE(U$45:U$49))</f>
+        <f aca="false">$B21*U$45+$C21*U$46+$D21*U$47+$E21*U$48+$F21*U$49</f>
         <v>0.0185536920234571</v>
       </c>
       <c r="V66" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$21:$F$21,TRANSPOSE(V$45:V$49))</f>
+        <f aca="false">$B21*V$45+$C21*V$46+$D21*V$47+$E21*V$48+$F21*V$49</f>
         <v>0.0188645046811869</v>
       </c>
       <c r="W66" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$21:$F$21,TRANSPOSE(W$45:W$49))</f>
+        <f aca="false">$B21*W$45+$C21*W$46+$D21*W$47+$E21*W$48+$F21*W$49</f>
         <v>0.019159329009881</v>
       </c>
       <c r="X66" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$21:$F$21,TRANSPOSE(X$45:X$49))</f>
+        <f aca="false">$B21*X$45+$C21*X$46+$D21*X$47+$E21*X$48+$F21*X$49</f>
         <v>0.0194342587954293</v>
       </c>
       <c r="Y66" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$21:$F$21,TRANSPOSE(Y$45:Y$49))</f>
+        <f aca="false">$B21*Y$45+$C21*Y$46+$D21*Y$47+$E21*Y$48+$F21*Y$49</f>
         <v>0.0196847729988864</v>
       </c>
       <c r="Z66" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$21:$F$21,TRANSPOSE(Z$45:Z$49))</f>
+        <f aca="false">$B21*Z$45+$C21*Z$46+$D21*Z$47+$E21*Z$48+$F21*Z$49</f>
         <v>0.0199058028448207</v>
       </c>
       <c r="AA66" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$21:$F$21,TRANSPOSE(AA$45:AA$49))</f>
+        <f aca="false">$B21*AA$45+$C21*AA$46+$D21*AA$47+$E21*AA$48+$F21*AA$49</f>
         <v>0.0200919068490576</v>
       </c>
       <c r="AB66" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$21:$F$21,TRANSPOSE(AB$45:AB$49))</f>
+        <f aca="false">$B21*AB$45+$C21*AB$46+$D21*AB$47+$E21*AB$48+$F21*AB$49</f>
         <v>0.0202375773022439</v>
       </c>
       <c r="AC66" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$21:$F$21,TRANSPOSE(AC$45:AC$49))</f>
+        <f aca="false">$B21*AC$45+$C21*AC$46+$D21*AC$47+$E21*AC$48+$F21*AC$49</f>
         <v>0.0203376767353596</v>
       </c>
       <c r="AD66" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$21:$F$21,TRANSPOSE(AD$45:AD$49))</f>
+        <f aca="false">$B21*AD$45+$C21*AD$46+$D21*AD$47+$E21*AD$48+$F21*AD$49</f>
         <v>0.0203879643050441</v>
       </c>
       <c r="AE66" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$21:$F$21,TRANSPOSE(AE$45:AE$49))</f>
+        <f aca="false">$B21*AE$45+$C21*AE$46+$D21*AE$47+$E21*AE$48+$F21*AE$49</f>
         <v>0.0203856333623333</v>
       </c>
       <c r="AF66" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$21:$F$21,TRANSPOSE(AF$45:AF$49))</f>
+        <f aca="false">$B21*AF$45+$C21*AF$46+$D21*AF$47+$E21*AF$48+$F21*AF$49</f>
         <v>0.0203297635761191</v>
       </c>
       <c r="AG66" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$21:$F$21,TRANSPOSE(AG$45:AG$49))</f>
+        <f aca="false">$B21*AG$45+$C21*AG$46+$D21*AG$47+$E21*AG$48+$F21*AG$49</f>
         <v>0.0202216069874109</v>
       </c>
       <c r="AH66" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$21:$F$21,TRANSPOSE(AH$45:AH$49))</f>
+        <f aca="false">$B21*AH$45+$C21*AH$46+$D21*AH$47+$E21*AH$48+$F21*AH$49</f>
         <v>0.0200646680478445</v>
       </c>
       <c r="AI66" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$21:$F$21,TRANSPOSE(AI$45:AI$49))</f>
+        <f aca="false">$B21*AI$45+$C21*AI$46+$D21*AI$47+$E21*AI$48+$F21*AI$49</f>
         <v>0.0198645766065878</v>
       </c>
       <c r="AJ66" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$21:$F$21,TRANSPOSE(AJ$45:AJ$49))</f>
-        <v>0.0196287713907498</v>
+        <f aca="false">$B21*AJ$45+$C21*AJ$46+$D21*AJ$47+$E21*AJ$48+$F21*AJ$49</f>
+        <v>0.0196287713907499</v>
       </c>
       <c r="AK66" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$21:$F$21,TRANSPOSE(AK$45:AK$49))</f>
+        <f aca="false">$B21*AK$45+$C21*AK$46+$D21*AK$47+$E21*AK$48+$F21*AK$49</f>
         <v>0.0193660166319343</v>
       </c>
       <c r="AL66" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$21:$F$21,TRANSPOSE(AL$45:AL$49))</f>
+        <f aca="false">$B21*AL$45+$C21*AL$46+$D21*AL$47+$E21*AL$48+$F21*AL$49</f>
         <v>0.019085786598713</v>
       </c>
       <c r="AM66" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$21:$F$21,TRANSPOSE(AM$45:AM$49))</f>
+        <f aca="false">$B21*AM$45+$C21*AM$46+$D21*AM$47+$E21*AM$48+$F21*AM$49</f>
         <v>0.0187975797474132</v>
       </c>
       <c r="AN66" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$21:$F$21,TRANSPOSE(AN$45:AN$49))</f>
+        <f aca="false">$B21*AN$45+$C21*AN$46+$D21*AN$47+$E21*AN$48+$F21*AN$49</f>
         <v>0.0185102517341896</v>
       </c>
       <c r="AO66" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$21:$F$21,TRANSPOSE(AO$45:AO$49))</f>
+        <f aca="false">$B21*AO$45+$C21*AO$46+$D21*AO$47+$E21*AO$48+$F21*AO$49</f>
         <v>0.0182314630750797</v>
       </c>
       <c r="AP66" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$21:$F$21,TRANSPOSE(AP$45:AP$49))</f>
+        <f aca="false">$B21*AP$45+$C21*AP$46+$D21*AP$47+$E21*AP$48+$F21*AP$49</f>
         <v>0.0179673137029228</v>
       </c>
       <c r="AQ66" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$21:$F$21,TRANSPOSE(AQ$45:AQ$49))</f>
+        <f aca="false">$B21*AQ$45+$C21*AQ$46+$D21*AQ$47+$E21*AQ$48+$F21*AQ$49</f>
         <v>0.0177221923610068</v>
       </c>
       <c r="AR66" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$21:$F$21,TRANSPOSE(AR$45:AR$49))</f>
+        <f aca="false">$B21*AR$45+$C21*AR$46+$D21*AR$47+$E21*AR$48+$F21*AR$49</f>
         <v>0.0174988225943135</v>
       </c>
       <c r="AS66" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$21:$F$21,TRANSPOSE(AS$45:AS$49))</f>
+        <f aca="false">$B21*AS$45+$C21*AS$46+$D21*AS$47+$E21*AS$48+$F21*AS$49</f>
         <v>0.0172984549673536</v>
       </c>
     </row>
@@ -27440,147 +27440,147 @@
         <v>251</v>
       </c>
       <c r="J67" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$22:$F$22,TRANSPOSE(J$45:J$49))</f>
+        <f aca="false">$B22*J$45+$C22*J$46+$D22*J$47+$E22*J$48+$F22*J$49</f>
         <v>0.0129475428036674</v>
       </c>
       <c r="K67" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$22:$F$22,TRANSPOSE(K$45:K$49))</f>
+        <f aca="false">$B22*K$45+$C22*K$46+$D22*K$47+$E22*K$48+$F22*K$49</f>
         <v>0.0132662072374479</v>
       </c>
       <c r="L67" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$22:$F$22,TRANSPOSE(L$45:L$49))</f>
+        <f aca="false">$B22*L$45+$C22*L$46+$D22*L$47+$E22*L$48+$F22*L$49</f>
         <v>0.0135861067167738</v>
       </c>
       <c r="M67" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$22:$F$22,TRANSPOSE(M$45:M$49))</f>
+        <f aca="false">$B22*M$45+$C22*M$46+$D22*M$47+$E22*M$48+$F22*M$49</f>
         <v>0.0139067201409103</v>
       </c>
       <c r="N67" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$22:$F$22,TRANSPOSE(N$45:N$49))</f>
+        <f aca="false">$B22*N$45+$C22*N$46+$D22*N$47+$E22*N$48+$F22*N$49</f>
         <v>0.014227453573885</v>
       </c>
       <c r="O67" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$22:$F$22,TRANSPOSE(O$45:O$49))</f>
+        <f aca="false">$B22*O$45+$C22*O$46+$D22*O$47+$E22*O$48+$F22*O$49</f>
         <v>0.0145476197025493</v>
       </c>
       <c r="P67" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$22:$F$22,TRANSPOSE(P$45:P$49))</f>
+        <f aca="false">$B22*P$45+$C22*P$46+$D22*P$47+$E22*P$48+$F22*P$49</f>
         <v>0.0148664110024664</v>
       </c>
       <c r="Q67" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$22:$F$22,TRANSPOSE(Q$45:Q$49))</f>
+        <f aca="false">$B22*Q$45+$C22*Q$46+$D22*Q$47+$E22*Q$48+$F22*Q$49</f>
         <v>0.015182865240408</v>
       </c>
       <c r="R67" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$22:$F$22,TRANSPOSE(R$45:R$49))</f>
+        <f aca="false">$B22*R$45+$C22*R$46+$D22*R$47+$E22*R$48+$F22*R$49</f>
         <v>0.0154958219627451</v>
       </c>
       <c r="S67" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$22:$F$22,TRANSPOSE(S$45:S$49))</f>
+        <f aca="false">$B22*S$45+$C22*S$46+$D22*S$47+$E22*S$48+$F22*S$49</f>
         <v>0.015803868928279</v>
       </c>
       <c r="T67" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$22:$F$22,TRANSPOSE(T$45:T$49))</f>
+        <f aca="false">$B22*T$45+$C22*T$46+$D22*T$47+$E22*T$48+$F22*T$49</f>
         <v>0.0161052782810061</v>
       </c>
       <c r="U67" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$22:$F$22,TRANSPOSE(U$45:U$49))</f>
+        <f aca="false">$B22*U$45+$C22*U$46+$D22*U$47+$E22*U$48+$F22*U$49</f>
         <v>0.0163979339755509</v>
       </c>
       <c r="V67" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$22:$F$22,TRANSPOSE(V$45:V$49))</f>
+        <f aca="false">$B22*V$45+$C22*V$46+$D22*V$47+$E22*V$48+$F22*V$49</f>
         <v>0.0166792550231594</v>
       </c>
       <c r="W67" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$22:$F$22,TRANSPOSE(W$45:W$49))</f>
+        <f aca="false">$B22*W$45+$C22*W$46+$D22*W$47+$E22*W$48+$F22*W$49</f>
         <v>0.0169461239836256</v>
       </c>
       <c r="X67" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$22:$F$22,TRANSPOSE(X$45:X$49))</f>
+        <f aca="false">$B22*X$45+$C22*X$46+$D22*X$47+$E22*X$48+$F22*X$49</f>
         <v>0.0171948369761817</v>
       </c>
       <c r="Y67" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$22:$F$22,TRANSPOSE(Y$45:Y$49))</f>
+        <f aca="false">$B22*Y$45+$C22*Y$46+$D22*Y$47+$E22*Y$48+$F22*Y$49</f>
         <v>0.0174210996598579</v>
       </c>
       <c r="Z67" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$22:$F$22,TRANSPOSE(Z$45:Z$49))</f>
+        <f aca="false">$B22*Z$45+$C22*Z$46+$D22*Z$47+$E22*Z$48+$F22*Z$49</f>
         <v>0.0176201007910353</v>
       </c>
       <c r="AA67" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$22:$F$22,TRANSPOSE(AA$45:AA$49))</f>
+        <f aca="false">$B22*AA$45+$C22*AA$46+$D22*AA$47+$E22*AA$48+$F22*AA$49</f>
         <v>0.0177866963732078</v>
       </c>
       <c r="AB67" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$22:$F$22,TRANSPOSE(AB$45:AB$49))</f>
+        <f aca="false">$B22*AB$45+$C22*AB$46+$D22*AB$47+$E22*AB$48+$F22*AB$49</f>
         <v>0.0179157265472303</v>
       </c>
       <c r="AC67" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$22:$F$22,TRANSPOSE(AC$45:AC$49))</f>
+        <f aca="false">$B22*AC$45+$C22*AC$46+$D22*AC$47+$E22*AC$48+$F22*AC$49</f>
         <v>0.0180024593049807</v>
       </c>
       <c r="AD67" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$22:$F$22,TRANSPOSE(AD$45:AD$49))</f>
+        <f aca="false">$B22*AD$45+$C22*AD$46+$D22*AD$47+$E22*AD$48+$F22*AD$49</f>
         <v>0.0180431128356771</v>
       </c>
       <c r="AE67" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$22:$F$22,TRANSPOSE(AE$45:AE$49))</f>
+        <f aca="false">$B22*AE$45+$C22*AE$46+$D22*AE$47+$E22*AE$48+$F22*AE$49</f>
         <v>0.0180353677119133</v>
       </c>
       <c r="AF67" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$22:$F$22,TRANSPOSE(AF$45:AF$49))</f>
+        <f aca="false">$B22*AF$45+$C22*AF$46+$D22*AF$47+$E22*AF$48+$F22*AF$49</f>
         <v>0.0179787652630319</v>
       </c>
       <c r="AG67" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$22:$F$22,TRANSPOSE(AG$45:AG$49))</f>
+        <f aca="false">$B22*AG$45+$C22*AG$46+$D22*AG$47+$E22*AG$48+$F22*AG$49</f>
         <v>0.0178749139547108</v>
       </c>
       <c r="AH67" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$22:$F$22,TRANSPOSE(AH$45:AH$49))</f>
+        <f aca="false">$B22*AH$45+$C22*AH$46+$D22*AH$47+$E22*AH$48+$F22*AH$49</f>
         <v>0.0177274792140589</v>
       </c>
       <c r="AI67" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$22:$F$22,TRANSPOSE(AI$45:AI$49))</f>
+        <f aca="false">$B22*AI$45+$C22*AI$46+$D22*AI$47+$E22*AI$48+$F22*AI$49</f>
         <v>0.0175419805482691</v>
       </c>
       <c r="AJ67" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$22:$F$22,TRANSPOSE(AJ$45:AJ$49))</f>
+        <f aca="false">$B22*AJ$45+$C22*AJ$46+$D22*AJ$47+$E22*AJ$48+$F22*AJ$49</f>
         <v>0.0173254381341643</v>
       </c>
       <c r="AK67" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$22:$F$22,TRANSPOSE(AK$45:AK$49))</f>
+        <f aca="false">$B22*AK$45+$C22*AK$46+$D22*AK$47+$E22*AK$48+$F22*AK$49</f>
         <v>0.0170859053566015</v>
       </c>
       <c r="AL67" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$22:$F$22,TRANSPOSE(AL$45:AL$49))</f>
+        <f aca="false">$B22*AL$45+$C22*AL$46+$D22*AL$47+$E22*AL$48+$F22*AL$49</f>
         <v>0.016831919727593</v>
       </c>
       <c r="AM67" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$22:$F$22,TRANSPOSE(AM$45:AM$49))</f>
+        <f aca="false">$B22*AM$45+$C22*AM$46+$D22*AM$47+$E22*AM$48+$F22*AM$49</f>
         <v>0.0165719174122144</v>
       </c>
       <c r="AN67" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$22:$F$22,TRANSPOSE(AN$45:AN$49))</f>
+        <f aca="false">$B22*AN$45+$C22*AN$46+$D22*AN$47+$E22*AN$48+$F22*AN$49</f>
         <v>0.0163136770756803</v>
       </c>
       <c r="AO67" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$22:$F$22,TRANSPOSE(AO$45:AO$49))</f>
+        <f aca="false">$B22*AO$45+$C22*AO$46+$D22*AO$47+$E22*AO$48+$F22*AO$49</f>
         <v>0.016063866463225</v>
       </c>
       <c r="AP67" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$22:$F$22,TRANSPOSE(AP$45:AP$49))</f>
+        <f aca="false">$B22*AP$45+$C22*AP$46+$D22*AP$47+$E22*AP$48+$F22*AP$49</f>
         <v>0.0158277486912625</v>
       </c>
       <c r="AQ67" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$22:$F$22,TRANSPOSE(AQ$45:AQ$49))</f>
+        <f aca="false">$B22*AQ$45+$C22*AQ$46+$D22*AQ$47+$E22*AQ$48+$F22*AQ$49</f>
         <v>0.0156090702629317</v>
       </c>
       <c r="AR67" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$22:$F$22,TRANSPOSE(AR$45:AR$49))</f>
+        <f aca="false">$B22*AR$45+$C22*AR$46+$D22*AR$47+$E22*AR$48+$F22*AR$49</f>
         <v>0.0154101148521875</v>
       </c>
       <c r="AS67" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$22:$F$22,TRANSPOSE(AS$45:AS$49))</f>
+        <f aca="false">$B22*AS$45+$C22*AS$46+$D22*AS$47+$E22*AS$48+$F22*AS$49</f>
         <v>0.0152318799101419</v>
       </c>
     </row>
@@ -27589,147 +27589,147 @@
         <v>252</v>
       </c>
       <c r="J68" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$23:$F$23,TRANSPOSE(J$45:J$49))</f>
+        <f aca="false">$B23*J$45+$C23*J$46+$D23*J$47+$E23*J$48+$F23*J$49</f>
         <v>0.0116847098188549</v>
       </c>
       <c r="K68" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$23:$F$23,TRANSPOSE(K$45:K$49))</f>
+        <f aca="false">$B23*K$45+$C23*K$46+$D23*K$47+$E23*K$48+$F23*K$49</f>
         <v>0.0119752826173231</v>
       </c>
       <c r="L68" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$23:$F$23,TRANSPOSE(L$45:L$49))</f>
+        <f aca="false">$B23*L$45+$C23*L$46+$D23*L$47+$E23*L$48+$F23*L$49</f>
         <v>0.0122670164224821</v>
       </c>
       <c r="M68" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$23:$F$23,TRANSPOSE(M$45:M$49))</f>
+        <f aca="false">$B23*M$45+$C23*M$46+$D23*M$47+$E23*M$48+$F23*M$49</f>
         <v>0.0125594356385628</v>
       </c>
       <c r="N68" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$23:$F$23,TRANSPOSE(N$45:N$49))</f>
+        <f aca="false">$B23*N$45+$C23*N$46+$D23*N$47+$E23*N$48+$F23*N$49</f>
         <v>0.0128519988928814</v>
       </c>
       <c r="O68" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$23:$F$23,TRANSPOSE(O$45:O$49))</f>
+        <f aca="false">$B23*O$45+$C23*O$46+$D23*O$47+$E23*O$48+$F23*O$49</f>
         <v>0.0131440805785073</v>
       </c>
       <c r="P68" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$23:$F$23,TRANSPOSE(P$45:P$49))</f>
+        <f aca="false">$B23*P$45+$C23*P$46+$D23*P$47+$E23*P$48+$F23*P$49</f>
         <v>0.0134349467412762</v>
       </c>
       <c r="Q68" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$23:$F$23,TRANSPOSE(Q$45:Q$49))</f>
+        <f aca="false">$B23*Q$45+$C23*Q$46+$D23*Q$47+$E23*Q$48+$F23*Q$49</f>
         <v>0.0137237240816508</v>
       </c>
       <c r="R68" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$23:$F$23,TRANSPOSE(R$45:R$49))</f>
+        <f aca="false">$B23*R$45+$C23*R$46+$D23*R$47+$E23*R$48+$F23*R$49</f>
         <v>0.0140093608607786</v>
       </c>
       <c r="S68" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$23:$F$23,TRANSPOSE(S$45:S$49))</f>
+        <f aca="false">$B23*S$45+$C23*S$46+$D23*S$47+$E23*S$48+$F23*S$49</f>
         <v>0.0142905787761246</v>
       </c>
       <c r="T68" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$23:$F$23,TRANSPOSE(T$45:T$49))</f>
+        <f aca="false">$B23*T$45+$C23*T$46+$D23*T$47+$E23*T$48+$F23*T$49</f>
         <v>0.014565815616908</v>
       </c>
       <c r="U68" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$23:$F$23,TRANSPOSE(U$45:U$49))</f>
+        <f aca="false">$B23*U$45+$C23*U$46+$D23*U$47+$E23*U$48+$F23*U$49</f>
         <v>0.0148331600350709</v>
       </c>
       <c r="V68" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$23:$F$23,TRANSPOSE(V$45:V$49))</f>
+        <f aca="false">$B23*V$45+$C23*V$46+$D23*V$47+$E23*V$48+$F23*V$49</f>
         <v>0.0150902824778992</v>
       </c>
       <c r="W68" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$23:$F$23,TRANSPOSE(W$45:W$49))</f>
+        <f aca="false">$B23*W$45+$C23*W$46+$D23*W$47+$E23*W$48+$F23*W$49</f>
         <v>0.0153343706341148</v>
       </c>
       <c r="X68" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$23:$F$23,TRANSPOSE(X$45:X$49))</f>
+        <f aca="false">$B23*X$45+$C23*X$46+$D23*X$47+$E23*X$48+$F23*X$49</f>
         <v>0.0155620838147107</v>
       </c>
       <c r="Y68" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$23:$F$23,TRANSPOSE(Y$45:Y$49))</f>
+        <f aca="false">$B23*Y$45+$C23*Y$46+$D23*Y$47+$E23*Y$48+$F23*Y$49</f>
         <v>0.0157695479495167</v>
       </c>
       <c r="Z68" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$23:$F$23,TRANSPOSE(Z$45:Z$49))</f>
+        <f aca="false">$B23*Z$45+$C23*Z$46+$D23*Z$47+$E23*Z$48+$F23*Z$49</f>
         <v>0.0159524192793437</v>
       </c>
       <c r="AA68" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$23:$F$23,TRANSPOSE(AA$45:AA$49))</f>
+        <f aca="false">$B23*AA$45+$C23*AA$46+$D23*AA$47+$E23*AA$48+$F23*AA$49</f>
         <v>0.0161060462276199</v>
       </c>
       <c r="AB68" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$23:$F$23,TRANSPOSE(AB$45:AB$49))</f>
+        <f aca="false">$B23*AB$45+$C23*AB$46+$D23*AB$47+$E23*AB$48+$F23*AB$49</f>
         <v>0.016225749628683</v>
       </c>
       <c r="AC68" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$23:$F$23,TRANSPOSE(AC$45:AC$49))</f>
+        <f aca="false">$B23*AC$45+$C23*AC$46+$D23*AC$47+$E23*AC$48+$F23*AC$49</f>
         <v>0.016307217111409</v>
       </c>
       <c r="AD68" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$23:$F$23,TRANSPOSE(AD$45:AD$49))</f>
+        <f aca="false">$B23*AD$45+$C23*AD$46+$D23*AD$47+$E23*AD$48+$F23*AD$49</f>
         <v>0.0163469704555422</v>
       </c>
       <c r="AE68" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$23:$F$23,TRANSPOSE(AE$45:AE$49))</f>
+        <f aca="false">$B23*AE$45+$C23*AE$46+$D23*AE$47+$E23*AE$48+$F23*AE$49</f>
         <v>0.0163428287846071</v>
       </c>
       <c r="AF68" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$23:$F$23,TRANSPOSE(AF$45:AF$49))</f>
+        <f aca="false">$B23*AF$45+$C23*AF$46+$D23*AF$47+$E23*AF$48+$F23*AF$49</f>
         <v>0.0162942763270315</v>
       </c>
       <c r="AG68" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$23:$F$23,TRANSPOSE(AG$45:AG$49))</f>
+        <f aca="false">$B23*AG$45+$C23*AG$46+$D23*AG$47+$E23*AG$48+$F23*AG$49</f>
         <v>0.016202663951266</v>
       </c>
       <c r="AH68" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$23:$F$23,TRANSPOSE(AH$45:AH$49))</f>
+        <f aca="false">$B23*AH$45+$C23*AH$46+$D23*AH$47+$E23*AH$48+$F23*AH$49</f>
         <v>0.0160712187050596</v>
       </c>
       <c r="AI68" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$23:$F$23,TRANSPOSE(AI$45:AI$49))</f>
+        <f aca="false">$B23*AI$45+$C23*AI$46+$D23*AI$47+$E23*AI$48+$F23*AI$49</f>
         <v>0.0159048770553981</v>
       </c>
       <c r="AJ68" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$23:$F$23,TRANSPOSE(AJ$45:AJ$49))</f>
+        <f aca="false">$B23*AJ$45+$C23*AJ$46+$D23*AJ$47+$E23*AJ$48+$F23*AJ$49</f>
         <v>0.0157099745776435</v>
       </c>
       <c r="AK68" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$23:$F$23,TRANSPOSE(AK$45:AK$49))</f>
+        <f aca="false">$B23*AK$45+$C23*AK$46+$D23*AK$47+$E23*AK$48+$F23*AK$49</f>
         <v>0.0154938227374416</v>
       </c>
       <c r="AL68" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$23:$F$23,TRANSPOSE(AL$45:AL$49))</f>
+        <f aca="false">$B23*AL$45+$C23*AL$46+$D23*AL$47+$E23*AL$48+$F23*AL$49</f>
         <v>0.0152642034986534</v>
       </c>
       <c r="AM68" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$23:$F$23,TRANSPOSE(AM$45:AM$49))</f>
+        <f aca="false">$B23*AM$45+$C23*AM$46+$D23*AM$47+$E23*AM$48+$F23*AM$49</f>
         <v>0.0150288265187033</v>
       </c>
       <c r="AN68" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$23:$F$23,TRANSPOSE(AN$45:AN$49))</f>
+        <f aca="false">$B23*AN$45+$C23*AN$46+$D23*AN$47+$E23*AN$48+$F23*AN$49</f>
         <v>0.0147948125933885</v>
       </c>
       <c r="AO68" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$23:$F$23,TRANSPOSE(AO$45:AO$49))</f>
+        <f aca="false">$B23*AO$45+$C23*AO$46+$D23*AO$47+$E23*AO$48+$F23*AO$49</f>
         <v>0.0145682727629646</v>
       </c>
       <c r="AP68" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$23:$F$23,TRANSPOSE(AP$45:AP$49))</f>
+        <f aca="false">$B23*AP$45+$C23*AP$46+$D23*AP$47+$E23*AP$48+$F23*AP$49</f>
         <v>0.0143540358828895</v>
       </c>
       <c r="AQ68" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$23:$F$23,TRANSPOSE(AQ$45:AQ$49))</f>
+        <f aca="false">$B23*AQ$45+$C23*AQ$46+$D23*AQ$47+$E23*AQ$48+$F23*AQ$49</f>
         <v>0.0141555444018322</v>
       </c>
       <c r="AR68" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$23:$F$23,TRANSPOSE(AR$45:AR$49))</f>
+        <f aca="false">$B23*AR$45+$C23*AR$46+$D23*AR$47+$E23*AR$48+$F23*AR$49</f>
         <v>0.0139749029644125</v>
       </c>
       <c r="AS68" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$23:$F$23,TRANSPOSE(AS$45:AS$49))</f>
+        <f aca="false">$B23*AS$45+$C23*AS$46+$D23*AS$47+$E23*AS$48+$F23*AS$49</f>
         <v>0.0138130398532565</v>
       </c>
     </row>
@@ -27738,147 +27738,147 @@
         <v>253</v>
       </c>
       <c r="J69" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$24:$F$24,TRANSPOSE(J$45:J$49))</f>
+        <f aca="false">$B24*J$45+$C24*J$46+$D24*J$47+$E24*J$48+$F24*J$49</f>
         <v>0.0141950768690166</v>
       </c>
       <c r="K69" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$24:$F$24,TRANSPOSE(K$45:K$49))</f>
+        <f aca="false">$B24*K$45+$C24*K$46+$D24*K$47+$E24*K$48+$F24*K$49</f>
         <v>0.0143121866833888</v>
       </c>
       <c r="L69" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$24:$F$24,TRANSPOSE(L$45:L$49))</f>
+        <f aca="false">$B24*L$45+$C24*L$46+$D24*L$47+$E24*L$48+$F24*L$49</f>
         <v>0.0144304683009802</v>
       </c>
       <c r="M69" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$24:$F$24,TRANSPOSE(M$45:M$49))</f>
+        <f aca="false">$B24*M$45+$C24*M$46+$D24*M$47+$E24*M$48+$F24*M$49</f>
         <v>0.0145497528093984</v>
       </c>
       <c r="N69" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$24:$F$24,TRANSPOSE(N$45:N$49))</f>
+        <f aca="false">$B24*N$45+$C24*N$46+$D24*N$47+$E24*N$48+$F24*N$49</f>
         <v>0.0146698390844353</v>
       </c>
       <c r="O69" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$24:$F$24,TRANSPOSE(O$45:O$49))</f>
+        <f aca="false">$B24*O$45+$C24*O$46+$D24*O$47+$E24*O$48+$F24*O$49</f>
         <v>0.0147904838633419</v>
       </c>
       <c r="P69" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$24:$F$24,TRANSPOSE(P$45:P$49))</f>
+        <f aca="false">$B24*P$45+$C24*P$46+$D24*P$47+$E24*P$48+$F24*P$49</f>
         <v>0.0149113885854377</v>
       </c>
       <c r="Q69" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$24:$F$24,TRANSPOSE(Q$45:Q$49))</f>
+        <f aca="false">$B24*Q$45+$C24*Q$46+$D24*Q$47+$E24*Q$48+$F24*Q$49</f>
         <v>0.0150321822101497</v>
       </c>
       <c r="R69" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$24:$F$24,TRANSPOSE(R$45:R$49))</f>
+        <f aca="false">$B24*R$45+$C24*R$46+$D24*R$47+$E24*R$48+$F24*R$49</f>
         <v>0.0151523992041807</v>
       </c>
       <c r="S69" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$24:$F$24,TRANSPOSE(S$45:S$49))</f>
+        <f aca="false">$B24*S$45+$C24*S$46+$D24*S$47+$E24*S$48+$F24*S$49</f>
         <v>0.0152714520337151</v>
       </c>
       <c r="T69" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$24:$F$24,TRANSPOSE(T$45:T$49))</f>
+        <f aca="false">$B24*T$45+$C24*T$46+$D24*T$47+$E24*T$48+$F24*T$49</f>
         <v>0.0153885979531051</v>
       </c>
       <c r="U69" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$24:$F$24,TRANSPOSE(U$45:U$49))</f>
+        <f aca="false">$B24*U$45+$C24*U$46+$D24*U$47+$E24*U$48+$F24*U$49</f>
         <v>0.0155029008729552</v>
       </c>
       <c r="V69" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$24:$F$24,TRANSPOSE(V$45:V$49))</f>
+        <f aca="false">$B24*V$45+$C24*V$46+$D24*V$47+$E24*V$48+$F24*V$49</f>
         <v>0.0156131909143882</v>
       </c>
       <c r="W69" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$24:$F$24,TRANSPOSE(W$45:W$49))</f>
+        <f aca="false">$B24*W$45+$C24*W$46+$D24*W$47+$E24*W$48+$F24*W$49</f>
         <v>0.015718027215693</v>
       </c>
       <c r="X69" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$24:$F$24,TRANSPOSE(X$45:X$49))</f>
+        <f aca="false">$B24*X$45+$C24*X$46+$D24*X$47+$E24*X$48+$F24*X$49</f>
         <v>0.0158156737685909</v>
       </c>
       <c r="Y69" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$24:$F$24,TRANSPOSE(Y$45:Y$49))</f>
+        <f aca="false">$B24*Y$45+$C24*Y$46+$D24*Y$47+$E24*Y$48+$F24*Y$49</f>
         <v>0.0159041030562605</v>
       </c>
       <c r="Z69" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$24:$F$24,TRANSPOSE(Z$45:Z$49))</f>
+        <f aca="false">$B24*Z$45+$C24*Z$46+$D24*Z$47+$E24*Z$48+$F24*Z$49</f>
         <v>0.0159810464050286</v>
       </c>
       <c r="AA69" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$24:$F$24,TRANSPOSE(AA$45:AA$49))</f>
+        <f aca="false">$B24*AA$45+$C24*AA$46+$D24*AA$47+$E24*AA$48+$F24*AA$49</f>
         <v>0.0160441099619602</v>
       </c>
       <c r="AB69" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$24:$F$24,TRANSPOSE(AB$45:AB$49))</f>
+        <f aca="false">$B24*AB$45+$C24*AB$46+$D24*AB$47+$E24*AB$48+$F24*AB$49</f>
         <v>0.0160909666003501</v>
       </c>
       <c r="AC69" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$24:$F$24,TRANSPOSE(AC$45:AC$49))</f>
+        <f aca="false">$B24*AC$45+$C24*AC$46+$D24*AC$47+$E24*AC$48+$F24*AC$49</f>
         <v>0.0161196136946339</v>
       </c>
       <c r="AD69" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$24:$F$24,TRANSPOSE(AD$45:AD$49))</f>
+        <f aca="false">$B24*AD$45+$C24*AD$46+$D24*AD$47+$E24*AD$48+$F24*AD$49</f>
         <v>0.0161286574490073</v>
       </c>
       <c r="AE69" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$24:$F$24,TRANSPOSE(AE$45:AE$49))</f>
+        <f aca="false">$B24*AE$45+$C24*AE$46+$D24*AE$47+$E24*AE$48+$F24*AE$49</f>
         <v>0.0161175587767581</v>
       </c>
       <c r="AF69" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$24:$F$24,TRANSPOSE(AF$45:AF$49))</f>
+        <f aca="false">$B24*AF$45+$C24*AF$46+$D24*AF$47+$E24*AF$48+$F24*AF$49</f>
         <v>0.0160867719567675</v>
       </c>
       <c r="AG69" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$24:$F$24,TRANSPOSE(AG$45:AG$49))</f>
+        <f aca="false">$B24*AG$45+$C24*AG$46+$D24*AG$47+$E24*AG$48+$F24*AG$49</f>
         <v>0.0160377359148686</v>
       </c>
       <c r="AH69" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$24:$F$24,TRANSPOSE(AH$45:AH$49))</f>
+        <f aca="false">$B24*AH$45+$C24*AH$46+$D24*AH$47+$E24*AH$48+$F24*AH$49</f>
         <v>0.0159727278123382</v>
       </c>
       <c r="AI69" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$24:$F$24,TRANSPOSE(AI$45:AI$49))</f>
+        <f aca="false">$B24*AI$45+$C24*AI$46+$D24*AI$47+$E24*AI$48+$F24*AI$49</f>
         <v>0.0158946305691077</v>
       </c>
       <c r="AJ69" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$24:$F$24,TRANSPOSE(AJ$45:AJ$49))</f>
+        <f aca="false">$B24*AJ$45+$C24*AJ$46+$D24*AJ$47+$E24*AJ$48+$F24*AJ$49</f>
         <v>0.0158066763846068</v>
       </c>
       <c r="AK69" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$24:$F$24,TRANSPOSE(AK$45:AK$49))</f>
+        <f aca="false">$B24*AK$45+$C24*AK$46+$D24*AK$47+$E24*AK$48+$F24*AK$49</f>
         <v>0.0157122090411444</v>
       </c>
       <c r="AL69" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$24:$F$24,TRANSPOSE(AL$45:AL$49))</f>
+        <f aca="false">$B24*AL$45+$C24*AL$46+$D24*AL$47+$E24*AL$48+$F24*AL$49</f>
         <v>0.0156144806894988</v>
       </c>
       <c r="AM69" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$24:$F$24,TRANSPOSE(AM$45:AM$49))</f>
+        <f aca="false">$B24*AM$45+$C24*AM$46+$D24*AM$47+$E24*AM$48+$F24*AM$49</f>
         <v>0.0155164835230861</v>
       </c>
       <c r="AN69" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$24:$F$24,TRANSPOSE(AN$45:AN$49))</f>
+        <f aca="false">$B24*AN$45+$C24*AN$46+$D24*AN$47+$E24*AN$48+$F24*AN$49</f>
         <v>0.0154208163072589</v>
       </c>
       <c r="AO69" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$24:$F$24,TRANSPOSE(AO$45:AO$49))</f>
+        <f aca="false">$B24*AO$45+$C24*AO$46+$D24*AO$47+$E24*AO$48+$F24*AO$49</f>
         <v>0.0153295909260373</v>
       </c>
       <c r="AP69" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$24:$F$24,TRANSPOSE(AP$45:AP$49))</f>
+        <f aca="false">$B24*AP$45+$C24*AP$46+$D24*AP$47+$E24*AP$48+$F24*AP$49</f>
         <v>0.0152443855852999</v>
       </c>
       <c r="AQ69" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$24:$F$24,TRANSPOSE(AQ$45:AQ$49))</f>
+        <f aca="false">$B24*AQ$45+$C24*AQ$46+$D24*AQ$47+$E24*AQ$48+$F24*AQ$49</f>
         <v>0.0151662465318646</v>
       </c>
       <c r="AR69" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$24:$F$24,TRANSPOSE(AR$45:AR$49))</f>
+        <f aca="false">$B24*AR$45+$C24*AR$46+$D24*AR$47+$E24*AR$48+$F24*AR$49</f>
         <v>0.0150957323126206</v>
       </c>
       <c r="AS69" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$24:$F$24,TRANSPOSE(AS$45:AS$49))</f>
+        <f aca="false">$B24*AS$45+$C24*AS$46+$D24*AS$47+$E24*AS$48+$F24*AS$49</f>
         <v>0.0150329881667946</v>
       </c>
     </row>
@@ -27887,147 +27887,147 @@
         <v>254</v>
       </c>
       <c r="J70" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$25:$F$25,TRANSPOSE(J$45:J$49))</f>
+        <f aca="false">$B25*J$45+$C25*J$46+$D25*J$47+$E25*J$48+$F25*J$49</f>
         <v>0.0351638798645322</v>
       </c>
       <c r="K70" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$25:$F$25,TRANSPOSE(K$45:K$49))</f>
+        <f aca="false">$B25*K$45+$C25*K$46+$D25*K$47+$E25*K$48+$F25*K$49</f>
         <v>0.034828414110687</v>
       </c>
       <c r="L70" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$25:$F$25,TRANSPOSE(L$45:L$49))</f>
+        <f aca="false">$B25*L$45+$C25*L$46+$D25*L$47+$E25*L$48+$F25*L$49</f>
         <v>0.0344936660531978</v>
       </c>
       <c r="M70" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$25:$F$25,TRANSPOSE(M$45:M$49))</f>
+        <f aca="false">$B25*M$45+$C25*M$46+$D25*M$47+$E25*M$48+$F25*M$49</f>
         <v>0.0341602538919439</v>
       </c>
       <c r="N70" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$25:$F$25,TRANSPOSE(N$45:N$49))</f>
+        <f aca="false">$B25*N$45+$C25*N$46+$D25*N$47+$E25*N$48+$F25*N$49</f>
         <v>0.0338288535871166</v>
       </c>
       <c r="O70" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$25:$F$25,TRANSPOSE(O$45:O$49))</f>
+        <f aca="false">$B25*O$45+$C25*O$46+$D25*O$47+$E25*O$48+$F25*O$49</f>
         <v>0.0335002122433239</v>
       </c>
       <c r="P70" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$25:$F$25,TRANSPOSE(P$45:P$49))</f>
+        <f aca="false">$B25*P$45+$C25*P$46+$D25*P$47+$E25*P$48+$F25*P$49</f>
         <v>0.0331751650243898</v>
       </c>
       <c r="Q70" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$25:$F$25,TRANSPOSE(Q$45:Q$49))</f>
+        <f aca="false">$B25*Q$45+$C25*Q$46+$D25*Q$47+$E25*Q$48+$F25*Q$49</f>
         <v>0.03285465609952</v>
       </c>
       <c r="R70" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$25:$F$25,TRANSPOSE(R$45:R$49))</f>
+        <f aca="false">$B25*R$45+$C25*R$46+$D25*R$47+$E25*R$48+$F25*R$49</f>
         <v>0.0325397640213805</v>
       </c>
       <c r="S70" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$25:$F$25,TRANSPOSE(S$45:S$49))</f>
+        <f aca="false">$B25*S$45+$C25*S$46+$D25*S$47+$E25*S$48+$F25*S$49</f>
         <v>0.0322317317268079</v>
       </c>
       <c r="T70" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$25:$F$25,TRANSPOSE(T$45:T$49))</f>
+        <f aca="false">$B25*T$45+$C25*T$46+$D25*T$47+$E25*T$48+$F25*T$49</f>
         <v>0.0319320009877522</v>
       </c>
       <c r="U70" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$25:$F$25,TRANSPOSE(U$45:U$49))</f>
+        <f aca="false">$B25*U$45+$C25*U$46+$D25*U$47+$E25*U$48+$F25*U$49</f>
         <v>0.0316422505768869</v>
       </c>
       <c r="V70" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$25:$F$25,TRANSPOSE(V$45:V$49))</f>
+        <f aca="false">$B25*V$45+$C25*V$46+$D25*V$47+$E25*V$48+$F25*V$49</f>
         <v>0.0313644366050165</v>
       </c>
       <c r="W70" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$25:$F$25,TRANSPOSE(W$45:W$49))</f>
+        <f aca="false">$B25*W$45+$C25*W$46+$D25*W$47+$E25*W$48+$F25*W$49</f>
         <v>0.0311008323975005</v>
       </c>
       <c r="X70" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$25:$F$25,TRANSPOSE(X$45:X$49))</f>
+        <f aca="false">$B25*X$45+$C25*X$46+$D25*X$47+$E25*X$48+$F25*X$49</f>
         <v>0.0308540638593659</v>
       </c>
       <c r="Y70" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$25:$F$25,TRANSPOSE(Y$45:Y$49))</f>
+        <f aca="false">$B25*Y$45+$C25*Y$46+$D25*Y$47+$E25*Y$48+$F25*Y$49</f>
         <v>0.0306271344376703</v>
       </c>
       <c r="Z70" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$25:$F$25,TRANSPOSE(Z$45:Z$49))</f>
+        <f aca="false">$B25*Z$45+$C25*Z$46+$D25*Z$47+$E25*Z$48+$F25*Z$49</f>
         <v>0.0304234313014433</v>
       </c>
       <c r="AA70" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$25:$F$25,TRANSPOSE(AA$45:AA$49))</f>
+        <f aca="false">$B25*AA$45+$C25*AA$46+$D25*AA$47+$E25*AA$48+$F25*AA$49</f>
         <v>0.0302467008409158</v>
       </c>
       <c r="AB70" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$25:$F$25,TRANSPOSE(AB$45:AB$49))</f>
+        <f aca="false">$B25*AB$45+$C25*AB$46+$D25*AB$47+$E25*AB$48+$F25*AB$49</f>
         <v>0.0301009767429884</v>
       </c>
       <c r="AC70" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$25:$F$25,TRANSPOSE(AC$45:AC$49))</f>
+        <f aca="false">$B25*AC$45+$C25*AC$46+$D25*AC$47+$E25*AC$48+$F25*AC$49</f>
         <v>0.0299904383979088</v>
       </c>
       <c r="AD70" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$25:$F$25,TRANSPOSE(AD$45:AD$49))</f>
+        <f aca="false">$B25*AD$45+$C25*AD$46+$D25*AD$47+$E25*AD$48+$F25*AD$49</f>
         <v>0.0299191743900083</v>
       </c>
       <c r="AE70" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$25:$F$25,TRANSPOSE(AE$45:AE$49))</f>
+        <f aca="false">$B25*AE$45+$C25*AE$46+$D25*AE$47+$E25*AE$48+$F25*AE$49</f>
         <v>0.0298908319332184</v>
       </c>
       <c r="AF70" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$25:$F$25,TRANSPOSE(AF$45:AF$49))</f>
+        <f aca="false">$B25*AF$45+$C25*AF$46+$D25*AF$47+$E25*AF$48+$F25*AF$49</f>
         <v>0.0299081561683424</v>
       </c>
       <c r="AG70" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$25:$F$25,TRANSPOSE(AG$45:AG$49))</f>
+        <f aca="false">$B25*AG$45+$C25*AG$46+$D25*AG$47+$E25*AG$48+$F25*AG$49</f>
         <v>0.0299724653238702</v>
       </c>
       <c r="AH70" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$25:$F$25,TRANSPOSE(AH$45:AH$49))</f>
+        <f aca="false">$B25*AH$45+$C25*AH$46+$D25*AH$47+$E25*AH$48+$F25*AH$49</f>
         <v>0.0300831573293143</v>
       </c>
       <c r="AI70" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$25:$F$25,TRANSPOSE(AI$45:AI$49))</f>
+        <f aca="false">$B25*AI$45+$C25*AI$46+$D25*AI$47+$E25*AI$48+$F25*AI$49</f>
         <v>0.0302373758088298</v>
       </c>
       <c r="AJ70" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$25:$F$25,TRANSPOSE(AJ$45:AJ$49))</f>
+        <f aca="false">$B25*AJ$45+$C25*AJ$46+$D25*AJ$47+$E25*AJ$48+$F25*AJ$49</f>
         <v>0.0304299538477394</v>
       </c>
       <c r="AK70" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$25:$F$25,TRANSPOSE(AK$45:AK$49))</f>
+        <f aca="false">$B25*AK$45+$C25*AK$46+$D25*AK$47+$E25*AK$48+$F25*AK$49</f>
         <v>0.0306536959041037</v>
       </c>
       <c r="AL70" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$25:$F$25,TRANSPOSE(AL$45:AL$49))</f>
+        <f aca="false">$B25*AL$45+$C25*AL$46+$D25*AL$47+$E25*AL$48+$F25*AL$49</f>
         <v>0.0308999704377946</v>
       </c>
       <c r="AM70" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$25:$F$25,TRANSPOSE(AM$45:AM$49))</f>
+        <f aca="false">$B25*AM$45+$C25*AM$46+$D25*AM$47+$E25*AM$48+$F25*AM$49</f>
         <v>0.0311595028155087</v>
       </c>
       <c r="AN70" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$25:$F$25,TRANSPOSE(AN$45:AN$49))</f>
+        <f aca="false">$B25*AN$45+$C25*AN$46+$D25*AN$47+$E25*AN$48+$F25*AN$49</f>
         <v>0.0314232116585947</v>
       </c>
       <c r="AO70" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$25:$F$25,TRANSPOSE(AO$45:AO$49))</f>
+        <f aca="false">$B25*AO$45+$C25*AO$46+$D25*AO$47+$E25*AO$48+$F25*AO$49</f>
         <v>0.0316829358925009</v>
       </c>
       <c r="AP70" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$25:$F$25,TRANSPOSE(AP$45:AP$49))</f>
+        <f aca="false">$B25*AP$45+$C25*AP$46+$D25*AP$47+$E25*AP$48+$F25*AP$49</f>
         <v>0.0319319461457716</v>
       </c>
       <c r="AQ70" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$25:$F$25,TRANSPOSE(AQ$45:AQ$49))</f>
+        <f aca="false">$B25*AQ$45+$C25*AQ$46+$D25*AQ$47+$E25*AQ$48+$F25*AQ$49</f>
         <v>0.0321651999236756</v>
       </c>
       <c r="AR70" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$25:$F$25,TRANSPOSE(AR$45:AR$49))</f>
+        <f aca="false">$B25*AR$45+$C25*AR$46+$D25*AR$47+$E25*AR$48+$F25*AR$49</f>
         <v>0.0323793603541716</v>
       </c>
       <c r="AS70" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$25:$F$25,TRANSPOSE(AS$45:AS$49))</f>
+        <f aca="false">$B25*AS$45+$C25*AS$46+$D25*AS$47+$E25*AS$48+$F25*AS$49</f>
         <v>0.0325726371658256</v>
       </c>
     </row>
@@ -28036,147 +28036,147 @@
         <v>255</v>
       </c>
       <c r="J71" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$26:$F$26,TRANSPOSE(J$45:J$49))</f>
+        <f aca="false">$B26*J$45+$C26*J$46+$D26*J$47+$E26*J$48+$F26*J$49</f>
         <v>0.0572597266063935</v>
       </c>
       <c r="K71" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$26:$F$26,TRANSPOSE(K$45:K$49))</f>
+        <f aca="false">$B26*K$45+$C26*K$46+$D26*K$47+$E26*K$48+$F26*K$49</f>
         <v>0.0567328363683345</v>
       </c>
       <c r="L71" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$26:$F$26,TRANSPOSE(L$45:L$49))</f>
+        <f aca="false">$B26*L$45+$C26*L$46+$D26*L$47+$E26*L$48+$F26*L$49</f>
         <v>0.0562059644928294</v>
       </c>
       <c r="M71" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$26:$F$26,TRANSPOSE(M$45:M$49))</f>
+        <f aca="false">$B26*M$45+$C26*M$46+$D26*M$47+$E26*M$48+$F26*M$49</f>
         <v>0.0556800420378488</v>
       </c>
       <c r="N71" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$26:$F$26,TRANSPOSE(N$45:N$49))</f>
+        <f aca="false">$B26*N$45+$C26*N$46+$D26*N$47+$E26*N$48+$F26*N$49</f>
         <v>0.0551561021431618</v>
       </c>
       <c r="O71" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$26:$F$26,TRANSPOSE(O$45:O$49))</f>
+        <f aca="false">$B26*O$45+$C26*O$46+$D26*O$47+$E26*O$48+$F26*O$49</f>
         <v>0.0546353059978923</v>
       </c>
       <c r="P71" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$26:$F$26,TRANSPOSE(P$45:P$49))</f>
+        <f aca="false">$B26*P$45+$C26*P$46+$D26*P$47+$E26*P$48+$F26*P$49</f>
         <v>0.0541189761890273</v>
       </c>
       <c r="Q71" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$26:$F$26,TRANSPOSE(Q$45:Q$49))</f>
+        <f aca="false">$B26*Q$45+$C26*Q$46+$D26*Q$47+$E26*Q$48+$F26*Q$49</f>
         <v>0.0536086387726139</v>
       </c>
       <c r="R71" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$26:$F$26,TRANSPOSE(R$45:R$49))</f>
+        <f aca="false">$B26*R$45+$C26*R$46+$D26*R$47+$E26*R$48+$F26*R$49</f>
         <v>0.0531060752968071</v>
       </c>
       <c r="S71" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$26:$F$26,TRANSPOSE(S$45:S$49))</f>
+        <f aca="false">$B26*S$45+$C26*S$46+$D26*S$47+$E26*S$48+$F26*S$49</f>
         <v>0.0526133856047626</v>
       </c>
       <c r="T71" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$26:$F$26,TRANSPOSE(T$45:T$49))</f>
+        <f aca="false">$B26*T$45+$C26*T$46+$D26*T$47+$E26*T$48+$F26*T$49</f>
         <v>0.0521330613630584</v>
       </c>
       <c r="U71" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$26:$F$26,TRANSPOSE(U$45:U$49))</f>
+        <f aca="false">$B26*U$45+$C26*U$46+$D26*U$47+$E26*U$48+$F26*U$49</f>
         <v>0.05166806863078</v>
       </c>
       <c r="V71" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$26:$F$26,TRANSPOSE(V$45:V$49))</f>
+        <f aca="false">$B26*V$45+$C26*V$46+$D26*V$47+$E26*V$48+$F26*V$49</f>
         <v>0.051221935075188</v>
       </c>
       <c r="W71" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$26:$F$26,TRANSPOSE(W$45:W$49))</f>
+        <f aca="false">$B26*W$45+$C26*W$46+$D26*W$47+$E26*W$48+$F26*W$49</f>
         <v>0.050798833323166</v>
       </c>
       <c r="X71" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$26:$F$26,TRANSPOSE(X$45:X$49))</f>
+        <f aca="false">$B26*X$45+$C26*X$46+$D26*X$47+$E26*X$48+$F26*X$49</f>
         <v>0.0504036462532539</v>
       </c>
       <c r="Y71" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$26:$F$26,TRANSPOSE(Y$45:Y$49))</f>
+        <f aca="false">$B26*Y$45+$C26*Y$46+$D26*Y$47+$E26*Y$48+$F26*Y$49</f>
         <v>0.0500419931075598</v>
       </c>
       <c r="Z71" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$26:$F$26,TRANSPOSE(Z$45:Z$49))</f>
+        <f aca="false">$B26*Z$45+$C26*Z$46+$D26*Z$47+$E26*Z$48+$F26*Z$49</f>
         <v>0.049720188406311</v>
       </c>
       <c r="AA71" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$26:$F$26,TRANSPOSE(AA$45:AA$49))</f>
+        <f aca="false">$B26*AA$45+$C26*AA$46+$D26*AA$47+$E26*AA$48+$F26*AA$49</f>
         <v>0.0494451013974396</v>
       </c>
       <c r="AB71" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$26:$F$26,TRANSPOSE(AB$45:AB$49))</f>
+        <f aca="false">$B26*AB$45+$C26*AB$46+$D26*AB$47+$E26*AB$48+$F26*AB$49</f>
         <v>0.0492238859995294</v>
       </c>
       <c r="AC71" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$26:$F$26,TRANSPOSE(AC$45:AC$49))</f>
+        <f aca="false">$B26*AC$45+$C26*AC$46+$D26*AC$47+$E26*AC$48+$F26*AC$49</f>
         <v>0.0490635636389027</v>
       </c>
       <c r="AD71" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$26:$F$26,TRANSPOSE(AD$45:AD$49))</f>
+        <f aca="false">$B26*AD$45+$C26*AD$46+$D26*AD$47+$E26*AD$48+$F26*AD$49</f>
         <v>0.0489704651663652</v>
       </c>
       <c r="AE71" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$26:$F$26,TRANSPOSE(AE$45:AE$49))</f>
+        <f aca="false">$B26*AE$45+$C26*AE$46+$D26*AE$47+$E26*AE$48+$F26*AE$49</f>
         <v>0.0489495694725399</v>
       </c>
       <c r="AF71" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$26:$F$26,TRANSPOSE(AF$45:AF$49))</f>
+        <f aca="false">$B26*AF$45+$C26*AF$46+$D26*AF$47+$E26*AF$48+$F26*AF$49</f>
         <v>0.049003807846166</v>
       </c>
       <c r="AG71" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$26:$F$26,TRANSPOSE(AG$45:AG$49))</f>
+        <f aca="false">$B26*AG$45+$C26*AG$46+$D26*AG$47+$E26*AG$48+$F26*AG$49</f>
         <v>0.0491334274012455</v>
       </c>
       <c r="AH71" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$26:$F$26,TRANSPOSE(AH$45:AH$49))</f>
+        <f aca="false">$B26*AH$45+$C26*AH$46+$D26*AH$47+$E26*AH$48+$F26*AH$49</f>
         <v>0.0493355207915685</v>
       </c>
       <c r="AI71" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$26:$F$26,TRANSPOSE(AI$45:AI$49))</f>
+        <f aca="false">$B26*AI$45+$C26*AI$46+$D26*AI$47+$E26*AI$48+$F26*AI$49</f>
         <v>0.0496038303191449</v>
       </c>
       <c r="AJ71" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$26:$F$26,TRANSPOSE(AJ$45:AJ$49))</f>
+        <f aca="false">$B26*AJ$45+$C26*AJ$46+$D26*AJ$47+$E26*AJ$48+$F26*AJ$49</f>
         <v>0.0499289143739622</v>
       </c>
       <c r="AK71" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$26:$F$26,TRANSPOSE(AK$45:AK$49))</f>
+        <f aca="false">$B26*AK$45+$C26*AK$46+$D26*AK$47+$E26*AK$48+$F26*AK$49</f>
         <v>0.0502987124081099</v>
       </c>
       <c r="AL71" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$26:$F$26,TRANSPOSE(AL$45:AL$49))</f>
+        <f aca="false">$B26*AL$45+$C26*AL$46+$D26*AL$47+$E26*AL$48+$F26*AL$49</f>
         <v>0.0506994627247016</v>
       </c>
       <c r="AM71" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$26:$F$26,TRANSPOSE(AM$45:AM$49))</f>
+        <f aca="false">$B26*AM$45+$C26*AM$46+$D26*AM$47+$E26*AM$48+$F26*AM$49</f>
         <v>0.0511168387711027</v>
       </c>
       <c r="AN71" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$26:$F$26,TRANSPOSE(AN$45:AN$49))</f>
+        <f aca="false">$B26*AN$45+$C26*AN$46+$D26*AN$47+$E26*AN$48+$F26*AN$49</f>
         <v>0.0515371110526836</v>
       </c>
       <c r="AO71" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$26:$F$26,TRANSPOSE(AO$45:AO$49))</f>
-        <v>0.0519481400236641</v>
+        <f aca="false">$B26*AO$45+$C26*AO$46+$D26*AO$47+$E26*AO$48+$F26*AO$49</f>
+        <v>0.0519481400236642</v>
       </c>
       <c r="AP71" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$26:$F$26,TRANSPOSE(AP$45:AP$49))</f>
+        <f aca="false">$B26*AP$45+$C26*AP$46+$D26*AP$47+$E26*AP$48+$F26*AP$49</f>
         <v>0.0523400600518275</v>
       </c>
       <c r="AQ71" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$26:$F$26,TRANSPOSE(AQ$45:AQ$49))</f>
+        <f aca="false">$B26*AQ$45+$C26*AQ$46+$D26*AQ$47+$E26*AQ$48+$F26*AQ$49</f>
         <v>0.052705600261976</v>
       </c>
       <c r="AR71" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$26:$F$26,TRANSPOSE(AR$45:AR$49))</f>
+        <f aca="false">$B26*AR$45+$C26*AR$46+$D26*AR$47+$E26*AR$48+$F26*AR$49</f>
         <v>0.0530400708155401</v>
       </c>
       <c r="AS71" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$26:$F$26,TRANSPOSE(AS$45:AS$49))</f>
+        <f aca="false">$B26*AS$45+$C26*AS$46+$D26*AS$47+$E26*AS$48+$F26*AS$49</f>
         <v>0.0533410983067031</v>
       </c>
     </row>
@@ -28185,147 +28185,147 @@
         <v>256</v>
       </c>
       <c r="J72" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$27:$F$27,TRANSPOSE(J$45:J$49))</f>
-        <v>0.0648111859762688</v>
+        <f aca="false">$B27*J$45+$C27*J$46+$D27*J$47+$E27*J$48+$F27*J$49</f>
+        <v>0.0648111859762687</v>
       </c>
       <c r="K72" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$27:$F$27,TRANSPOSE(K$45:K$49))</f>
+        <f aca="false">$B27*K$45+$C27*K$46+$D27*K$47+$E27*K$48+$F27*K$49</f>
         <v>0.0642309872443211</v>
       </c>
       <c r="L72" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$27:$F$27,TRANSPOSE(L$45:L$49))</f>
+        <f aca="false">$B27*L$45+$C27*L$46+$D27*L$47+$E27*L$48+$F27*L$49</f>
         <v>0.063650884279227</v>
       </c>
       <c r="M72" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$27:$F$27,TRANSPOSE(M$45:M$49))</f>
+        <f aca="false">$B27*M$45+$C27*M$46+$D27*M$47+$E27*M$48+$F27*M$49</f>
         <v>0.0630719032793893</v>
       </c>
       <c r="N72" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$27:$F$27,TRANSPOSE(N$45:N$49))</f>
+        <f aca="false">$B27*N$45+$C27*N$46+$D27*N$47+$E27*N$48+$F27*N$49</f>
         <v>0.0624951831282982</v>
       </c>
       <c r="O72" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$27:$F$27,TRANSPOSE(O$45:O$49))</f>
+        <f aca="false">$B27*O$45+$C27*O$46+$D27*O$47+$E27*O$48+$F27*O$49</f>
         <v>0.0619220041051071</v>
       </c>
       <c r="P72" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$27:$F$27,TRANSPOSE(P$45:P$49))</f>
+        <f aca="false">$B27*P$45+$C27*P$46+$D27*P$47+$E27*P$48+$F27*P$49</f>
         <v>0.0613538247450495</v>
       </c>
       <c r="Q72" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$27:$F$27,TRANSPOSE(Q$45:Q$49))</f>
-        <v>0.0607923283297332</v>
+        <f aca="false">$B27*Q$45+$C27*Q$46+$D27*Q$47+$E27*Q$48+$F27*Q$49</f>
+        <v>0.0607923283297331</v>
       </c>
       <c r="R72" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$27:$F$27,TRANSPOSE(R$45:R$49))</f>
+        <f aca="false">$B27*R$45+$C27*R$46+$D27*R$47+$E27*R$48+$F27*R$49</f>
         <v>0.0602394803619929</v>
       </c>
       <c r="S72" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$27:$F$27,TRANSPOSE(S$45:S$49))</f>
+        <f aca="false">$B27*S$45+$C27*S$46+$D27*S$47+$E27*S$48+$F27*S$49</f>
         <v>0.0596975979344251</v>
       </c>
       <c r="T72" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$27:$F$27,TRANSPOSE(T$45:T$49))</f>
+        <f aca="false">$B27*T$45+$C27*T$46+$D27*T$47+$E27*T$48+$F27*T$49</f>
         <v>0.0591694309207481</v>
       </c>
       <c r="U72" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$27:$F$27,TRANSPOSE(U$45:U$49))</f>
+        <f aca="false">$B27*U$45+$C27*U$46+$D27*U$47+$E27*U$48+$F27*U$49</f>
         <v>0.0586582531071293</v>
       </c>
       <c r="V72" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$27:$F$27,TRANSPOSE(V$45:V$49))</f>
+        <f aca="false">$B27*V$45+$C27*V$46+$D27*V$47+$E27*V$48+$F27*V$49</f>
         <v>0.0581679583681452</v>
       </c>
       <c r="W72" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$27:$F$27,TRANSPOSE(W$45:W$49))</f>
+        <f aca="false">$B27*W$45+$C27*W$46+$D27*W$47+$E27*W$48+$F27*W$49</f>
         <v>0.0577031524125731</v>
       </c>
       <c r="X72" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$27:$F$27,TRANSPOSE(X$45:X$49))</f>
+        <f aca="false">$B27*X$45+$C27*X$46+$D27*X$47+$E27*X$48+$F27*X$49</f>
         <v>0.057269224301546</v>
       </c>
       <c r="Y72" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$27:$F$27,TRANSPOSE(Y$45:Y$49))</f>
+        <f aca="false">$B27*Y$45+$C27*Y$46+$D27*Y$47+$E27*Y$48+$F27*Y$49</f>
         <v>0.0568723742488248</v>
       </c>
       <c r="Z72" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$27:$F$27,TRANSPOSE(Z$45:Z$49))</f>
+        <f aca="false">$B27*Z$45+$C27*Z$46+$D27*Z$47+$E27*Z$48+$F27*Z$49</f>
         <v>0.0565195665887864</v>
       </c>
       <c r="AA72" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$27:$F$27,TRANSPOSE(AA$45:AA$49))</f>
+        <f aca="false">$B27*AA$45+$C27*AA$46+$D27*AA$47+$E27*AA$48+$F27*AA$49</f>
         <v>0.0562183722001594</v>
       </c>
       <c r="AB72" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$27:$F$27,TRANSPOSE(AB$45:AB$49))</f>
+        <f aca="false">$B27*AB$45+$C27*AB$46+$D27*AB$47+$E27*AB$48+$F27*AB$49</f>
         <v>0.0559766674156857</v>
       </c>
       <c r="AC72" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$27:$F$27,TRANSPOSE(AC$45:AC$49))</f>
+        <f aca="false">$B27*AC$45+$C27*AC$46+$D27*AC$47+$E27*AC$48+$F27*AC$49</f>
         <v>0.0558021706909746</v>
       </c>
       <c r="AD72" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$27:$F$27,TRANSPOSE(AD$45:AD$49))</f>
+        <f aca="false">$B27*AD$45+$C27*AD$46+$D27*AD$47+$E27*AD$48+$F27*AD$49</f>
         <v>0.0557018251516552</v>
       </c>
       <c r="AE72" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$27:$F$27,TRANSPOSE(AE$45:AE$49))</f>
+        <f aca="false">$B27*AE$45+$C27*AE$46+$D27*AE$47+$E27*AE$48+$F27*AE$49</f>
         <v>0.0556810701157162</v>
       </c>
       <c r="AF72" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$27:$F$27,TRANSPOSE(AF$45:AF$49))</f>
+        <f aca="false">$B27*AF$45+$C27*AF$46+$D27*AF$47+$E27*AF$48+$F27*AF$49</f>
         <v>0.0557430788455989</v>
       </c>
       <c r="AG72" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$27:$F$27,TRANSPOSE(AG$45:AG$49))</f>
+        <f aca="false">$B27*AG$45+$C27*AG$46+$D27*AG$47+$E27*AG$48+$F27*AG$49</f>
         <v>0.0558880650830038</v>
       </c>
       <c r="AH72" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$27:$F$27,TRANSPOSE(AH$45:AH$49))</f>
+        <f aca="false">$B27*AH$45+$C27*AH$46+$D27*AH$47+$E27*AH$48+$F27*AH$49</f>
         <v>0.0561127743746714</v>
       </c>
       <c r="AI72" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$27:$F$27,TRANSPOSE(AI$45:AI$49))</f>
+        <f aca="false">$B27*AI$45+$C27*AI$46+$D27*AI$47+$E27*AI$48+$F27*AI$49</f>
         <v>0.0564102760992975</v>
       </c>
       <c r="AJ72" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$27:$F$27,TRANSPOSE(AJ$45:AJ$49))</f>
+        <f aca="false">$B27*AJ$45+$C27*AJ$46+$D27*AJ$47+$E27*AJ$48+$F27*AJ$49</f>
         <v>0.0567701504348498</v>
       </c>
       <c r="AK72" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$27:$F$27,TRANSPOSE(AK$45:AK$49))</f>
+        <f aca="false">$B27*AK$45+$C27*AK$46+$D27*AK$47+$E27*AK$48+$F27*AK$49</f>
         <v>0.0571791094205046</v>
       </c>
       <c r="AL72" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$27:$F$27,TRANSPOSE(AL$45:AL$49))</f>
+        <f aca="false">$B27*AL$45+$C27*AL$46+$D27*AL$47+$E27*AL$48+$F27*AL$49</f>
         <v>0.0576220030845064</v>
       </c>
       <c r="AM72" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$27:$F$27,TRANSPOSE(AM$45:AM$49))</f>
+        <f aca="false">$B27*AM$45+$C27*AM$46+$D27*AM$47+$E27*AM$48+$F27*AM$49</f>
         <v>0.0580830650844356</v>
       </c>
       <c r="AN72" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$27:$F$27,TRANSPOSE(AN$45:AN$49))</f>
+        <f aca="false">$B27*AN$45+$C27*AN$46+$D27*AN$47+$E27*AN$48+$F27*AN$49</f>
         <v>0.0585471875373717</v>
       </c>
       <c r="AO72" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$27:$F$27,TRANSPOSE(AO$45:AO$49))</f>
+        <f aca="false">$B27*AO$45+$C27*AO$46+$D27*AO$47+$E27*AO$48+$F27*AO$49</f>
         <v>0.0590010117275218</v>
       </c>
       <c r="AP72" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$27:$F$27,TRANSPOSE(AP$45:AP$49))</f>
+        <f aca="false">$B27*AP$45+$C27*AP$46+$D27*AP$47+$E27*AP$48+$F27*AP$49</f>
         <v>0.0594336805782601</v>
       </c>
       <c r="AQ72" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$27:$F$27,TRANSPOSE(AQ$45:AQ$49))</f>
+        <f aca="false">$B27*AQ$45+$C27*AQ$46+$D27*AQ$47+$E27*AQ$48+$F27*AQ$49</f>
         <v>0.0598371925286149</v>
       </c>
       <c r="AR72" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$27:$F$27,TRANSPOSE(AR$45:AR$49))</f>
+        <f aca="false">$B27*AR$45+$C27*AR$46+$D27*AR$47+$E27*AR$48+$F27*AR$49</f>
         <v>0.0602063874706438</v>
       </c>
       <c r="AS72" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$27:$F$27,TRANSPOSE(AS$45:AS$49))</f>
+        <f aca="false">$B27*AS$45+$C27*AS$46+$D27*AS$47+$E27*AS$48+$F27*AS$49</f>
         <v>0.0605386563198295</v>
       </c>
     </row>
@@ -28334,147 +28334,147 @@
         <v>257</v>
       </c>
       <c r="J73" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$28:$F$28,TRANSPOSE(J$45:J$49))</f>
+        <f aca="false">$B28*J$45+$C28*J$46+$D28*J$47+$E28*J$48+$F28*J$49</f>
         <v>0.0598805704070941</v>
       </c>
       <c r="K73" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$28:$F$28,TRANSPOSE(K$45:K$49))</f>
+        <f aca="false">$B28*K$45+$C28*K$46+$D28*K$47+$E28*K$48+$F28*K$49</f>
         <v>0.05942127718949</v>
       </c>
       <c r="L73" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$28:$F$28,TRANSPOSE(L$45:L$49))</f>
+        <f aca="false">$B28*L$45+$C28*L$46+$D28*L$47+$E28*L$48+$F28*L$49</f>
         <v>0.0589621526941593</v>
       </c>
       <c r="M73" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$28:$F$28,TRANSPOSE(M$45:M$49))</f>
+        <f aca="false">$B28*M$45+$C28*M$46+$D28*M$47+$E28*M$48+$F28*M$49</f>
         <v>0.0585040104642889</v>
       </c>
       <c r="N73" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$28:$F$28,TRANSPOSE(N$45:N$49))</f>
+        <f aca="false">$B28*N$45+$C28*N$46+$D28*N$47+$E28*N$48+$F28*N$49</f>
         <v>0.0580477535640822</v>
       </c>
       <c r="O73" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$28:$F$28,TRANSPOSE(O$45:O$49))</f>
+        <f aca="false">$B28*O$45+$C28*O$46+$D28*O$47+$E28*O$48+$F28*O$49</f>
         <v>0.0575943974399962</v>
       </c>
       <c r="P73" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$28:$F$28,TRANSPOSE(P$45:P$49))</f>
+        <f aca="false">$B28*P$45+$C28*P$46+$D28*P$47+$E28*P$48+$F28*P$49</f>
         <v>0.0571450992578457</v>
       </c>
       <c r="Q73" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$28:$F$28,TRANSPOSE(Q$45:Q$49))</f>
+        <f aca="false">$B28*Q$45+$C28*Q$46+$D28*Q$47+$E28*Q$48+$F28*Q$49</f>
         <v>0.0567011948897463</v>
       </c>
       <c r="R73" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$28:$F$28,TRANSPOSE(R$45:R$49))</f>
+        <f aca="false">$B28*R$45+$C28*R$46+$D28*R$47+$E28*R$48+$F28*R$49</f>
         <v>0.0562642446238846</v>
       </c>
       <c r="S73" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$28:$F$28,TRANSPOSE(S$45:S$49))</f>
+        <f aca="false">$B28*S$45+$C28*S$46+$D28*S$47+$E28*S$48+$F28*S$49</f>
         <v>0.0558360883128956</v>
       </c>
       <c r="T73" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$28:$F$28,TRANSPOSE(T$45:T$49))</f>
+        <f aca="false">$B28*T$45+$C28*T$46+$D28*T$47+$E28*T$48+$F28*T$49</f>
         <v>0.0554189098910963</v>
       </c>
       <c r="U73" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$28:$F$28,TRANSPOSE(U$45:U$49))</f>
+        <f aca="false">$B28*U$45+$C28*U$46+$D28*U$47+$E28*U$48+$F28*U$49</f>
         <v>0.0550153097374664</v>
       </c>
       <c r="V73" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$28:$F$28,TRANSPOSE(V$45:V$49))</f>
+        <f aca="false">$B28*V$45+$C28*V$46+$D28*V$47+$E28*V$48+$F28*V$49</f>
         <v>0.0546283809431515</v>
       </c>
       <c r="W73" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$28:$F$28,TRANSPOSE(W$45:W$49))</f>
+        <f aca="false">$B28*W$45+$C28*W$46+$D28*W$47+$E28*W$48+$F28*W$49</f>
         <v>0.0542617818643306</v>
       </c>
       <c r="X73" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$28:$F$28,TRANSPOSE(X$45:X$49))</f>
+        <f aca="false">$B28*X$45+$C28*X$46+$D28*X$47+$E28*X$48+$F28*X$49</f>
         <v>0.0539197922642863</v>
       </c>
       <c r="Y73" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$28:$F$28,TRANSPOSE(Y$45:Y$49))</f>
+        <f aca="false">$B28*Y$45+$C28*Y$46+$D28*Y$47+$E28*Y$48+$F28*Y$49</f>
         <v>0.0536073341835746</v>
       </c>
       <c r="Z73" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$28:$F$28,TRANSPOSE(Z$45:Z$49))</f>
+        <f aca="false">$B28*Z$45+$C28*Z$46+$D28*Z$47+$E28*Z$48+$F28*Z$49</f>
         <v>0.0533299326096034</v>
       </c>
       <c r="AA73" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$28:$F$28,TRANSPOSE(AA$45:AA$49))</f>
+        <f aca="false">$B28*AA$45+$C28*AA$46+$D28*AA$47+$E28*AA$48+$F28*AA$49</f>
         <v>0.0530935874760094</v>
       </c>
       <c r="AB73" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$28:$F$28,TRANSPOSE(AB$45:AB$49))</f>
+        <f aca="false">$B28*AB$45+$C28*AB$46+$D28*AB$47+$E28*AB$48+$F28*AB$49</f>
         <v>0.0529045310321958</v>
       </c>
       <c r="AC73" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$28:$F$28,TRANSPOSE(AC$45:AC$49))</f>
+        <f aca="false">$B28*AC$45+$C28*AC$46+$D28*AC$47+$E28*AC$48+$F28*AC$49</f>
         <v>0.0527688565263306</v>
       </c>
       <c r="AD73" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$28:$F$28,TRANSPOSE(AD$45:AD$49))</f>
+        <f aca="false">$B28*AD$45+$C28*AD$46+$D28*AD$47+$E28*AD$48+$F28*AD$49</f>
         <v>0.0526920261514022</v>
       </c>
       <c r="AE73" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$28:$F$28,TRANSPOSE(AE$45:AE$49))</f>
+        <f aca="false">$B28*AE$45+$C28*AE$46+$D28*AE$47+$E28*AE$48+$F28*AE$49</f>
         <v>0.0526782943046512</v>
       </c>
       <c r="AF73" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$28:$F$28,TRANSPOSE(AF$45:AF$49))</f>
+        <f aca="false">$B28*AF$45+$C28*AF$46+$D28*AF$47+$E28*AF$48+$F28*AF$49</f>
         <v>0.0527301087153123</v>
       </c>
       <c r="AG73" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$28:$F$28,TRANSPOSE(AG$45:AG$49))</f>
+        <f aca="false">$B28*AG$45+$C28*AG$46+$D28*AG$47+$E28*AG$48+$F28*AG$49</f>
         <v>0.0528475703345923</v>
       </c>
       <c r="AH73" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$28:$F$28,TRANSPOSE(AH$45:AH$49))</f>
+        <f aca="false">$B28*AH$45+$C28*AH$46+$D28*AH$47+$E28*AH$48+$F28*AH$49</f>
         <v>0.0530280413869869</v>
       </c>
       <c r="AI73" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$28:$F$28,TRANSPOSE(AI$45:AI$49))</f>
-        <v>0.0532659896679485</v>
+        <f aca="false">$B28*AI$45+$C28*AI$46+$D28*AI$47+$E28*AI$48+$F28*AI$49</f>
+        <v>0.0532659896679486</v>
       </c>
       <c r="AJ73" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$28:$F$28,TRANSPOSE(AJ$45:AJ$49))</f>
+        <f aca="false">$B28*AJ$45+$C28*AJ$46+$D28*AJ$47+$E28*AJ$48+$F28*AJ$49</f>
         <v>0.0535531406770631</v>
       </c>
       <c r="AK73" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$28:$F$28,TRANSPOSE(AK$45:AK$49))</f>
+        <f aca="false">$B28*AK$45+$C28*AK$46+$D28*AK$47+$E28*AK$48+$F28*AK$49</f>
         <v>0.0538789677977579</v>
       </c>
       <c r="AL73" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$28:$F$28,TRANSPOSE(AL$45:AL$49))</f>
+        <f aca="false">$B28*AL$45+$C28*AL$46+$D28*AL$47+$E28*AL$48+$F28*AL$49</f>
         <v>0.0542314833089231</v>
       </c>
       <c r="AM73" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$28:$F$28,TRANSPOSE(AM$45:AM$49))</f>
+        <f aca="false">$B28*AM$45+$C28*AM$46+$D28*AM$47+$E28*AM$48+$F28*AM$49</f>
         <v>0.054598217794212</v>
       </c>
       <c r="AN73" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$28:$F$28,TRANSPOSE(AN$45:AN$49))</f>
+        <f aca="false">$B28*AN$45+$C28*AN$46+$D28*AN$47+$E28*AN$48+$F28*AN$49</f>
         <v>0.0549672238976501</v>
       </c>
       <c r="AO73" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$28:$F$28,TRANSPOSE(AO$45:AO$49))</f>
+        <f aca="false">$B28*AO$45+$C28*AO$46+$D28*AO$47+$E28*AO$48+$F28*AO$49</f>
         <v>0.0553279367444437</v>
       </c>
       <c r="AP73" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$28:$F$28,TRANSPOSE(AP$45:AP$49))</f>
+        <f aca="false">$B28*AP$45+$C28*AP$46+$D28*AP$47+$E28*AP$48+$F28*AP$49</f>
         <v>0.0556717689265254</v>
       </c>
       <c r="AQ73" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$28:$F$28,TRANSPOSE(AQ$45:AQ$49))</f>
+        <f aca="false">$B28*AQ$45+$C28*AQ$46+$D28*AQ$47+$E28*AQ$48+$F28*AQ$49</f>
         <v>0.0559923914334072</v>
       </c>
       <c r="AR73" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$28:$F$28,TRANSPOSE(AR$45:AR$49))</f>
+        <f aca="false">$B28*AR$45+$C28*AR$46+$D28*AR$47+$E28*AR$48+$F28*AR$49</f>
         <v>0.0562857238431384</v>
       </c>
       <c r="AS73" s="64" t="n">
-        <f aca="false">SUMPRODUCT($B$28:$F$28,TRANSPOSE(AS$45:AS$49))</f>
+        <f aca="false">$B28*AS$45+$C28*AS$46+$D28*AS$47+$E28*AS$48+$F28*AS$49</f>
         <v>0.0565497055786942</v>
       </c>
     </row>
@@ -28809,7 +28809,7 @@
       </c>
       <c r="U4" s="42" t="n">
         <f aca="false">J4*Assumptions!$B$59*1000/8760/'Load profile'!J75</f>
-        <v>0.075032304307236</v>
+        <v>0.0750323043072359</v>
       </c>
       <c r="V4" s="42" t="n">
         <f aca="false">(D4+E4)*Assumptions!$B$64*Assumptions!$B$65*Assumptions!$B$66/1000000</f>
